--- a/YCharts/Portfolio.xlsx
+++ b/YCharts/Portfolio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Desktop\Portfolio Management\YCharts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3031D4E9-8666-4C91-9DB8-1E786F2A62D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7740AB75-6CDC-44DC-A9A1-7F236028EB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1073" yWindow="1073" windowWidth="28799" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="473" yWindow="667" windowWidth="28717" windowHeight="15488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1430,11 +1430,11 @@
       </c>
       <c r="H3" s="4" cm="1">
         <f t="array" aca="1" ref="H3" ca="1">_xll.YCP($B3,H$2)</f>
-        <v>1.8006999999999999E-3</v>
+        <v>1.79598E-3</v>
       </c>
       <c r="I3" s="4" cm="1">
         <f t="array" aca="1" ref="I3" ca="1">_xll.YCP($B3,I$2)</f>
-        <v>3.3564999999999998E-2</v>
+        <v>3.3868000000000002E-2</v>
       </c>
       <c r="J3" s="5" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">_xll.YCP($B3,J$2)</f>
@@ -1442,23 +1442,23 @@
       </c>
       <c r="K3" s="4" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">_xll.YCP($B3,K$2)</f>
-        <v>0.76423478</v>
+        <v>0.76431444000000004</v>
       </c>
       <c r="L3" s="4" cm="1">
         <f t="array" aca="1" ref="L3" ca="1">_xll.YCP($B3,L$2)</f>
-        <v>8.0210000000000004E-3</v>
+        <v>-1.1677E-2</v>
       </c>
       <c r="M3" s="4" cm="1">
         <f t="array" aca="1" ref="M3" ca="1">_xll.YCP($B3,M$2)</f>
-        <v>2.8156E-2</v>
+        <v>6.4720000000000003E-3</v>
       </c>
       <c r="N3" s="4" cm="1">
         <f t="array" aca="1" ref="N3" ca="1">_xll.YCP($B3,N$2)</f>
-        <v>3.7512999999999998E-2</v>
+        <v>2.879E-2</v>
       </c>
       <c r="O3" s="4" cm="1">
         <f t="array" aca="1" ref="O3" ca="1">_xll.YCP($B3,O$2)</f>
-        <v>8.4311999999999998E-2</v>
+        <v>7.0385000000000003E-2</v>
       </c>
       <c r="P3" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P3" ca="1">_xll.YCP($B3,P$2)</f>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="R3" s="4" cm="1">
         <f t="array" aca="1" ref="R3" ca="1">_xll.YCP($B3,R$2)</f>
-        <v>8.7337999999999999E-2</v>
+        <v>8.0985000000000001E-2</v>
       </c>
       <c r="S3" s="3" cm="1">
         <f t="array" aca="1" ref="S3" ca="1">_xll.YCP($B3,S$2)</f>
@@ -1614,279 +1614,279 @@
       </c>
       <c r="BB3" s="4" cm="1">
         <f t="array" aca="1" ref="BB3" ca="1">_xll.YCP($B3,BB$2)</f>
-        <v>0.90124630999999999</v>
+        <v>0.90201960999999997</v>
       </c>
       <c r="BC3" s="4" cm="1">
         <f t="array" aca="1" ref="BC3" ca="1">_xll.YCP($B3,BC$2)</f>
-        <v>4.8440899999999997E-3</v>
+        <v>4.9227400000000001E-3</v>
       </c>
       <c r="BD3" s="4" cm="1">
         <f t="array" aca="1" ref="BD3" ca="1">_xll.YCP($B3,BD$2)</f>
-        <v>1.6230399999999999E-2</v>
+        <v>1.6348109999999999E-2</v>
       </c>
       <c r="BE3" s="4" cm="1">
         <f t="array" aca="1" ref="BE3" ca="1">_xll.YCP($B3,BE$2)</f>
-        <v>4.7881E-2</v>
+        <v>4.8625069999999999E-2</v>
       </c>
       <c r="BF3" s="4" cm="1">
         <f t="array" aca="1" ref="BF3" ca="1">_xll.YCP($B3,BF$2)</f>
-        <v>1.5693700000000001E-3</v>
+        <v>1.5596E-3</v>
       </c>
       <c r="BG3" s="4" cm="1">
         <f t="array" aca="1" ref="BG3" ca="1">_xll.YCP($B3,BG$2)</f>
-        <v>3.3722299999999999E-3</v>
+        <v>3.49117E-3</v>
       </c>
       <c r="BH3" s="4" cm="1">
         <f t="array" aca="1" ref="BH3" ca="1">_xll.YCP($B3,BH$2)</f>
-        <v>9.5558399999999995E-3</v>
+        <v>8.8140300000000005E-3</v>
       </c>
       <c r="BI3" s="4" cm="1">
         <f t="array" aca="1" ref="BI3" ca="1">_xll.YCP($B3,BI$2)</f>
-        <v>1.111886E-2</v>
+        <v>1.164257E-2</v>
       </c>
       <c r="BJ3" s="4" cm="1">
         <f t="array" aca="1" ref="BJ3" ca="1">_xll.YCP($B3,BJ$2)</f>
-        <v>0.22034859000000001</v>
+        <v>0.24811554</v>
       </c>
       <c r="BK3" s="4" cm="1">
         <f t="array" aca="1" ref="BK3" ca="1">_xll.YCP($B3,BK$2)</f>
-        <v>0.28472626000000001</v>
+        <v>0.25245456999999999</v>
       </c>
       <c r="BL3" s="4" cm="1">
         <f t="array" aca="1" ref="BL3" ca="1">_xll.YCP($B3,BL$2)</f>
-        <v>0.18966366000000001</v>
+        <v>0.18588595999999999</v>
       </c>
       <c r="BM3" s="4" cm="1">
         <f t="array" aca="1" ref="BM3" ca="1">_xll.YCP($B3,BM$2)</f>
-        <v>8.3320400000000003E-2</v>
+        <v>8.7551770000000001E-2</v>
       </c>
       <c r="BN3" s="4" cm="1">
         <f t="array" aca="1" ref="BN3" ca="1">_xll.YCP($B3,BN$2)</f>
-        <v>0.10362067</v>
+        <v>0.10874735000000001</v>
       </c>
       <c r="BO3" s="4" cm="1">
         <f t="array" aca="1" ref="BO3" ca="1">_xll.YCP($B3,BO$2)</f>
-        <v>4.5706719999999999E-2</v>
+        <v>4.4611159999999997E-2</v>
       </c>
       <c r="BP3" s="4" cm="1">
         <f t="array" aca="1" ref="BP3" ca="1">_xll.YCP($B3,BP$2)</f>
-        <v>2.4915090000000001E-2</v>
+        <v>2.562708E-2</v>
       </c>
       <c r="BQ3" s="4" cm="1">
         <f t="array" aca="1" ref="BQ3" ca="1">_xll.YCP($B3,BQ$2)</f>
-        <v>2.4157809999999998E-2</v>
+        <v>2.3969790000000001E-2</v>
       </c>
       <c r="BR3" s="4" cm="1">
         <f t="array" aca="1" ref="BR3" ca="1">_xll.YCP($B3,BR$2)</f>
-        <v>2.3540789999999999E-2</v>
+        <v>2.3036770000000002E-2</v>
       </c>
       <c r="BS3" s="4" cm="1">
         <f t="array" aca="1" ref="BS3" ca="1">_xll.YCP($B3,BS$2)</f>
-        <v>3.1069860000000001E-2</v>
+        <v>3.165722E-2</v>
       </c>
       <c r="BT3" s="4" cm="1">
         <f t="array" aca="1" ref="BT3" ca="1">_xll.YCP($B3,BT$2)</f>
-        <v>9.1815859999999999E-2</v>
+        <v>9.0006520000000007E-2</v>
       </c>
       <c r="BU3" s="4" cm="1">
         <f t="array" aca="1" ref="BU3" ca="1">_xll.YCP($B3,BU$2)</f>
-        <v>8.3669850000000004E-2</v>
+        <v>8.2939719999999995E-2</v>
       </c>
       <c r="BV3" s="4" cm="1">
         <f t="array" aca="1" ref="BV3" ca="1">_xll.YCP($B3,BV$2)</f>
-        <v>3.7088070000000001E-2</v>
+        <v>3.7326970000000001E-2</v>
       </c>
       <c r="BW3" s="4" cm="1">
         <f t="array" aca="1" ref="BW3" ca="1">_xll.YCP($B3,BW$2)</f>
-        <v>3.8142130000000003E-2</v>
+        <v>3.7538009999999997E-2</v>
       </c>
       <c r="BX3" s="4" cm="1">
         <f t="array" aca="1" ref="BX3" ca="1">_xll.YCP($B3,BX$2)</f>
-        <v>0.13285565999999999</v>
+        <v>0.13664299999999999</v>
       </c>
       <c r="BY3" s="4" cm="1">
         <f t="array" aca="1" ref="BY3" ca="1">_xll.YCP($B3,BY$2)</f>
-        <v>9.6557030000000002E-2</v>
+        <v>9.7928009999999996E-2</v>
       </c>
       <c r="BZ3" s="4" cm="1">
         <f t="array" aca="1" ref="BZ3" ca="1">_xll.YCP($B3,BZ$2)</f>
-        <v>0.10571089</v>
+        <v>0.10694461</v>
       </c>
       <c r="CA3" s="4" cm="1">
         <f t="array" aca="1" ref="CA3" ca="1">_xll.YCP($B3,CA$2)</f>
-        <v>1.9756949999999999E-2</v>
+        <v>1.9732929999999999E-2</v>
       </c>
       <c r="CB3" s="4" cm="1">
         <f t="array" aca="1" ref="CB3" ca="1">_xll.YCP($B3,CB$2)</f>
-        <v>0.33459505</v>
+        <v>0.33030310000000002</v>
       </c>
       <c r="CC3" s="4" cm="1">
         <f t="array" aca="1" ref="CC3" ca="1">_xll.YCP($B3,CC$2)</f>
-        <v>2.6261090000000001E-2</v>
+        <v>2.666106E-2</v>
       </c>
       <c r="CD3" s="4" cm="1">
         <f t="array" aca="1" ref="CD3" ca="1">_xll.YCP($B3,CD$2)</f>
-        <v>6.0117199999999999E-3</v>
+        <v>4.9528799999999998E-3</v>
       </c>
       <c r="CE3" s="4" cm="1">
         <f t="array" aca="1" ref="CE3" ca="1">_xll.YCP($B3,CE$2)</f>
-        <v>0.33403157</v>
+        <v>0.33165280000000003</v>
       </c>
       <c r="CF3" s="4" cm="1">
         <f t="array" aca="1" ref="CF3" ca="1">_xll.YCP($B3,CF$2)</f>
-        <v>0.65914269999999997</v>
+        <v>0.66255465000000002</v>
       </c>
       <c r="CG3" s="4" cm="1">
         <f t="array" aca="1" ref="CG3" ca="1">_xll.YCP($B3,CG$2)</f>
-        <v>4.4740000000000002E-5</v>
+        <v>4.4530000000000002E-5</v>
       </c>
       <c r="CH3" s="4" cm="1">
         <f t="array" aca="1" ref="CH3" ca="1">_xll.YCP($B3,CH$2)</f>
-        <v>5.1447999999999999E-4</v>
+        <v>5.0916000000000004E-4</v>
       </c>
       <c r="CI3" s="4" cm="1">
         <f t="array" aca="1" ref="CI3" ca="1">_xll.YCP($B3,CI$2)</f>
-        <v>2.5472E-4</v>
+        <v>2.8592999999999999E-4</v>
       </c>
       <c r="CJ3" s="4" cm="1">
         <f t="array" aca="1" ref="CJ3" ca="1">_xll.YCP($B3,CJ$2)</f>
-        <v>5.6580409999999998E-2</v>
+        <v>5.6416830000000001E-2</v>
       </c>
       <c r="CK3" s="4" cm="1">
         <f t="array" aca="1" ref="CK3" ca="1">_xll.YCP($B3,CK$2)</f>
-        <v>0.42899654999999998</v>
+        <v>0.43199387</v>
       </c>
       <c r="CL3" s="4" cm="1">
         <f t="array" aca="1" ref="CL3" ca="1">_xll.YCP($B3,CL$2)</f>
-        <v>0.15980437</v>
+        <v>0.15994591</v>
       </c>
       <c r="CM3" s="4" cm="1">
         <f t="array" aca="1" ref="CM3" ca="1">_xll.YCP($B3,CM$2)</f>
-        <v>0.16261517</v>
+        <v>0.16277080999999999</v>
       </c>
       <c r="CN3" s="4" cm="1">
         <f t="array" aca="1" ref="CN3" ca="1">_xll.YCP($B3,CN$2)</f>
-        <v>6.4661339999999998E-2</v>
+        <v>6.5298410000000001E-2</v>
       </c>
       <c r="CO3" s="4" cm="1">
         <f t="array" aca="1" ref="CO3" ca="1">_xll.YCP($B3,CO$2)</f>
-        <v>3.4857800000000001E-2</v>
+        <v>3.610273E-2</v>
       </c>
       <c r="CP3" s="4" cm="1">
         <f t="array" aca="1" ref="CP3" ca="1">_xll.YCP($B3,CP$2)</f>
-        <v>5.8175700000000002E-3</v>
+        <v>5.4148599999999996E-3</v>
       </c>
       <c r="CQ3" s="4" cm="1">
         <f t="array" aca="1" ref="CQ3" ca="1">_xll.YCP($B3,CQ$2)</f>
-        <v>3.9949409999999998E-2</v>
+        <v>3.9989190000000001E-2</v>
       </c>
       <c r="CR3" s="4" cm="1">
         <f t="array" aca="1" ref="CR3" ca="1">_xll.YCP($B3,CR$2)</f>
-        <v>8.1328460000000005E-2</v>
+        <v>8.0075729999999998E-2</v>
       </c>
       <c r="CS3" s="4" cm="1">
         <f t="array" aca="1" ref="CS3" ca="1">_xll.YCP($B3,CS$2)</f>
-        <v>0.15077668</v>
+        <v>0.14957323</v>
       </c>
       <c r="CT3" s="4" cm="1">
         <f t="array" aca="1" ref="CT3" ca="1">_xll.YCP($B3,CT$2)</f>
-        <v>0.48862280000000002</v>
+        <v>0.48886881999999998</v>
       </c>
       <c r="CU3" s="4" cm="1">
         <f t="array" aca="1" ref="CU3" ca="1">_xll.YCP($B3,CU$2)</f>
-        <v>0.12004123999999999</v>
+        <v>0.12081253</v>
       </c>
       <c r="CV3" s="4" cm="1">
         <f t="array" aca="1" ref="CV3" ca="1">_xll.YCP($B3,CV$2)</f>
-        <v>0.1094132</v>
+        <v>0.10892959000000001</v>
       </c>
       <c r="CW3" s="4" cm="1">
         <f t="array" aca="1" ref="CW3" ca="1">_xll.YCP($B3,CW$2)</f>
-        <v>1.825094E-2</v>
+        <v>1.801695E-2</v>
       </c>
       <c r="CX3" s="3" cm="1">
         <f t="array" aca="1" ref="CX3" ca="1">_xll.YCP($B3,CX$2)</f>
-        <v>5.6579470000000001</v>
+        <v>5.6439060000000003</v>
       </c>
       <c r="CY3" s="20" cm="1">
         <f t="array" aca="1" ref="CY3" ca="1">_xll.YCP($B3,CY$2)</f>
-        <v>7.4706359999999998</v>
+        <v>7.4938269999999996</v>
       </c>
       <c r="CZ3" s="4" cm="1">
         <f t="array" aca="1" ref="CZ3" ca="1">_xll.YCP($B3,CZ$2)</f>
-        <v>4.922882E-2</v>
+        <v>4.9867689999999999E-2</v>
       </c>
       <c r="DA3" s="4" cm="1">
         <f t="array" aca="1" ref="DA3" ca="1">_xll.YCP($B3,DA$2)</f>
-        <v>4.5799630000000001E-2</v>
+        <v>4.5894490000000003E-2</v>
       </c>
       <c r="DB3" s="4" cm="1">
         <f t="array" aca="1" ref="DB3" ca="1">_xll.YCP($B3,DB$2)</f>
-        <v>4.6101049999999998E-2</v>
+        <v>4.6240440000000001E-2</v>
       </c>
       <c r="DC3" s="4" cm="1">
         <f t="array" aca="1" ref="DC3" ca="1">_xll.YCP($B3,DC$2)</f>
-        <v>0.41233871999999999</v>
+        <v>0.41188894999999998</v>
       </c>
       <c r="DD3" s="4" cm="1">
         <f t="array" aca="1" ref="DD3" ca="1">_xll.YCP($B3,DD$2)</f>
-        <v>0.46580716999999999</v>
+        <v>0.46594182000000001</v>
       </c>
       <c r="DE3" s="4" cm="1">
         <f t="array" aca="1" ref="DE3" ca="1">_xll.YCP($B3,DE$2)</f>
-        <v>0.10711751</v>
+        <v>0.10705654000000001</v>
       </c>
       <c r="DF3" s="4" cm="1">
         <f t="array" aca="1" ref="DF3" ca="1">_xll.YCP($B3,DF$2)</f>
-        <v>7.3355900000000003E-3</v>
+        <v>7.3788899999999999E-3</v>
       </c>
       <c r="DG3" s="4" cm="1">
         <f t="array" aca="1" ref="DG3" ca="1">_xll.YCP($B3,DG$2)</f>
-        <v>7.4010100000000004E-3</v>
+        <v>7.7337899999999999E-3</v>
       </c>
       <c r="DH3" s="4" cm="1">
         <f t="array" aca="1" ref="DH3" ca="1">_xll.YCP($B3,DH$2)</f>
-        <v>0.33403157</v>
+        <v>0.33165905000000001</v>
       </c>
       <c r="DI3" s="4" cm="1">
         <f t="array" aca="1" ref="DI3" ca="1">_xll.YCP($B3,DI$2)</f>
-        <v>0.66162993999999997</v>
+        <v>0.66500800000000004</v>
       </c>
       <c r="DJ3" s="4" cm="1">
         <f t="array" aca="1" ref="DJ3" ca="1">_xll.YCP($B3,DJ$2)</f>
-        <v>6.0117199999999999E-3</v>
+        <v>4.9528799999999998E-3</v>
       </c>
       <c r="DK3" s="4" cm="1">
         <f t="array" aca="1" ref="DK3" ca="1">_xll.YCP($B3,DK$2)</f>
-        <v>1.459099E-2</v>
+        <v>1.6287940000000001E-2</v>
       </c>
       <c r="DL3" s="4" cm="1">
         <f t="array" aca="1" ref="DL3" ca="1">_xll.YCP($B3,DL$2)</f>
-        <v>0.23211586000000001</v>
+        <v>0.23095308000000001</v>
       </c>
       <c r="DM3" s="4" cm="1">
         <f t="array" aca="1" ref="DM3" ca="1">_xll.YCP($B3,DM$2)</f>
-        <v>5.9844969999999997E-2</v>
+        <v>5.9880969999999999E-2</v>
       </c>
       <c r="DN3" s="4" cm="1">
         <f t="array" aca="1" ref="DN3" ca="1">_xll.YCP($B3,DN$2)</f>
-        <v>4.1806709999999997E-2</v>
+        <v>4.0567079999999998E-2</v>
       </c>
       <c r="DO3" s="4" cm="1">
         <f t="array" aca="1" ref="DO3" ca="1">_xll.YCP($B3,DO$2)</f>
-        <v>0.52408288000000003</v>
+        <v>0.52717698000000002</v>
       </c>
       <c r="DP3" s="4" cm="1">
         <f t="array" aca="1" ref="DP3" ca="1">_xll.YCP($B3,DP$2)</f>
-        <v>6.8323519999999999E-2</v>
+        <v>6.942305E-2</v>
       </c>
       <c r="DQ3" s="4" cm="1">
         <f t="array" aca="1" ref="DQ3" ca="1">_xll.YCP($B3,DQ$2)</f>
-        <v>7.7298899999999997E-3</v>
+        <v>8.0772599999999993E-3</v>
       </c>
       <c r="DR3" s="4" cm="1">
         <f t="array" aca="1" ref="DR3" ca="1">_xll.YCP($B3,DR$2)</f>
-        <v>0.98540901000000003</v>
+        <v>0.98371206</v>
       </c>
     </row>
     <row r="4" spans="2:122" x14ac:dyDescent="0.45">
@@ -1915,11 +1915,11 @@
       </c>
       <c r="H4" s="4" cm="1">
         <f t="array" aca="1" ref="H4" ca="1">_xll.YCP($B4,H$2)</f>
-        <v>2.1716800000000001E-3</v>
+        <v>2.1537599999999998E-3</v>
       </c>
       <c r="I4" s="4" cm="1">
         <f t="array" aca="1" ref="I4" ca="1">_xll.YCP($B4,I$2)</f>
-        <v>2.7362999999999998E-2</v>
+        <v>2.7674000000000001E-2</v>
       </c>
       <c r="J4" s="5" cm="1">
         <f t="array" aca="1" ref="J4" ca="1">_xll.YCP($B4,J$2)</f>
@@ -1927,23 +1927,23 @@
       </c>
       <c r="K4" s="4" cm="1">
         <f t="array" aca="1" ref="K4" ca="1">_xll.YCP($B4,K$2)</f>
-        <v>0.72971954000000006</v>
+        <v>0.73171403000000002</v>
       </c>
       <c r="L4" s="4" cm="1">
         <f t="array" aca="1" ref="L4" ca="1">_xll.YCP($B4,L$2)</f>
-        <v>1.2813E-2</v>
+        <v>-1.7399999999999999E-2</v>
       </c>
       <c r="M4" s="4" cm="1">
         <f t="array" aca="1" ref="M4" ca="1">_xll.YCP($B4,M$2)</f>
-        <v>4.6337999999999997E-2</v>
+        <v>1.4218E-2</v>
       </c>
       <c r="N4" s="4" cm="1">
         <f t="array" aca="1" ref="N4" ca="1">_xll.YCP($B4,N$2)</f>
-        <v>6.3339999999999994E-2</v>
+        <v>5.1936000000000003E-2</v>
       </c>
       <c r="O4" s="4" cm="1">
         <f t="array" aca="1" ref="O4" ca="1">_xll.YCP($B4,O$2)</f>
-        <v>0.12241200000000001</v>
+        <v>0.103792</v>
       </c>
       <c r="P4" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P4" ca="1">_xll.YCP($B4,P$2)</f>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="R4" s="4" cm="1">
         <f t="array" aca="1" ref="R4" ca="1">_xll.YCP($B4,R$2)</f>
-        <v>0.101734</v>
+        <v>9.3181E-2</v>
       </c>
       <c r="S4" s="3" cm="1">
         <f t="array" aca="1" ref="S4" ca="1">_xll.YCP($B4,S$2)</f>
@@ -2099,279 +2099,279 @@
       </c>
       <c r="BB4" s="4" cm="1">
         <f t="array" aca="1" ref="BB4" ca="1">_xll.YCP($B4,BB$2)</f>
-        <v>0.84532953</v>
+        <v>0.84478913</v>
       </c>
       <c r="BC4" s="4" cm="1">
         <f t="array" aca="1" ref="BC4" ca="1">_xll.YCP($B4,BC$2)</f>
-        <v>5.8748899999999998E-3</v>
+        <v>5.9974E-3</v>
       </c>
       <c r="BD4" s="4" cm="1">
         <f t="array" aca="1" ref="BD4" ca="1">_xll.YCP($B4,BD$2)</f>
-        <v>2.114075E-2</v>
+        <v>2.1343150000000002E-2</v>
       </c>
       <c r="BE4" s="4" cm="1">
         <f t="array" aca="1" ref="BE4" ca="1">_xll.YCP($B4,BE$2)</f>
-        <v>6.7893229999999999E-2</v>
+        <v>6.9377720000000004E-2</v>
       </c>
       <c r="BF4" s="4" cm="1">
         <f t="array" aca="1" ref="BF4" ca="1">_xll.YCP($B4,BF$2)</f>
-        <v>1.48672E-3</v>
+        <v>1.4848400000000001E-3</v>
       </c>
       <c r="BG4" s="4" cm="1">
         <f t="array" aca="1" ref="BG4" ca="1">_xll.YCP($B4,BG$2)</f>
-        <v>4.0978000000000004E-3</v>
+        <v>4.2882800000000002E-3</v>
       </c>
       <c r="BH4" s="4" cm="1">
         <f t="array" aca="1" ref="BH4" ca="1">_xll.YCP($B4,BH$2)</f>
-        <v>1.751395E-2</v>
+        <v>1.5961550000000001E-2</v>
       </c>
       <c r="BI4" s="4" cm="1">
         <f t="array" aca="1" ref="BI4" ca="1">_xll.YCP($B4,BI$2)</f>
-        <v>1.5468579999999999E-2</v>
+        <v>1.6552919999999999E-2</v>
       </c>
       <c r="BJ4" s="4" cm="1">
         <f t="array" aca="1" ref="BJ4" ca="1">_xll.YCP($B4,BJ$2)</f>
-        <v>0.19088316999999999</v>
+        <v>0.20889614000000001</v>
       </c>
       <c r="BK4" s="4" cm="1">
         <f t="array" aca="1" ref="BK4" ca="1">_xll.YCP($B4,BK$2)</f>
-        <v>0.25493885999999999</v>
+        <v>0.23705841999999999</v>
       </c>
       <c r="BL4" s="4" cm="1">
         <f t="array" aca="1" ref="BL4" ca="1">_xll.YCP($B4,BL$2)</f>
-        <v>0.17971297999999999</v>
+        <v>0.17072436999999999</v>
       </c>
       <c r="BM4" s="4" cm="1">
         <f t="array" aca="1" ref="BM4" ca="1">_xll.YCP($B4,BM$2)</f>
-        <v>0.10101102000000001</v>
+        <v>0.10656981</v>
       </c>
       <c r="BN4" s="4" cm="1">
         <f t="array" aca="1" ref="BN4" ca="1">_xll.YCP($B4,BN$2)</f>
-        <v>0.10473567</v>
+        <v>0.10989392000000001</v>
       </c>
       <c r="BO4" s="4" cm="1">
         <f t="array" aca="1" ref="BO4" ca="1">_xll.YCP($B4,BO$2)</f>
-        <v>6.2169259999999997E-2</v>
+        <v>6.0234879999999998E-2</v>
       </c>
       <c r="BP4" s="4" cm="1">
         <f t="array" aca="1" ref="BP4" ca="1">_xll.YCP($B4,BP$2)</f>
-        <v>3.4306700000000002E-2</v>
+        <v>3.5550270000000002E-2</v>
       </c>
       <c r="BQ4" s="4" cm="1">
         <f t="array" aca="1" ref="BQ4" ca="1">_xll.YCP($B4,BQ$2)</f>
-        <v>3.8197979999999999E-2</v>
+        <v>3.8536899999999999E-2</v>
       </c>
       <c r="BR4" s="4" cm="1">
         <f t="array" aca="1" ref="BR4" ca="1">_xll.YCP($B4,BR$2)</f>
-        <v>3.4044350000000001E-2</v>
+        <v>3.253528E-2</v>
       </c>
       <c r="BS4" s="4" cm="1">
         <f t="array" aca="1" ref="BS4" ca="1">_xll.YCP($B4,BS$2)</f>
-        <v>3.8751000000000001E-2</v>
+        <v>3.9732429999999999E-2</v>
       </c>
       <c r="BT4" s="4" cm="1">
         <f t="array" aca="1" ref="BT4" ca="1">_xll.YCP($B4,BT$2)</f>
-        <v>7.1555670000000002E-2</v>
+        <v>7.0823949999999997E-2</v>
       </c>
       <c r="BU4" s="4" cm="1">
         <f t="array" aca="1" ref="BU4" ca="1">_xll.YCP($B4,BU$2)</f>
-        <v>7.8274579999999996E-2</v>
+        <v>7.8410099999999996E-2</v>
       </c>
       <c r="BV4" s="4" cm="1">
         <f t="array" aca="1" ref="BV4" ca="1">_xll.YCP($B4,BV$2)</f>
-        <v>3.8879129999999998E-2</v>
+        <v>3.9181180000000003E-2</v>
       </c>
       <c r="BW4" s="4" cm="1">
         <f t="array" aca="1" ref="BW4" ca="1">_xll.YCP($B4,BW$2)</f>
-        <v>3.9272439999999999E-2</v>
+        <v>3.920771E-2</v>
       </c>
       <c r="BX4" s="4" cm="1">
         <f t="array" aca="1" ref="BX4" ca="1">_xll.YCP($B4,BX$2)</f>
-        <v>0.15354709</v>
+        <v>0.15813426999999999</v>
       </c>
       <c r="BY4" s="4" cm="1">
         <f t="array" aca="1" ref="BY4" ca="1">_xll.YCP($B4,BY$2)</f>
-        <v>8.9790499999999995E-2</v>
+        <v>9.0958999999999998E-2</v>
       </c>
       <c r="BZ4" s="4" cm="1">
         <f t="array" aca="1" ref="BZ4" ca="1">_xll.YCP($B4,BZ$2)</f>
-        <v>0.13319342000000001</v>
+        <v>0.13332580999999999</v>
       </c>
       <c r="CA4" s="4" cm="1">
         <f t="array" aca="1" ref="CA4" ca="1">_xll.YCP($B4,CA$2)</f>
-        <v>2.155172E-2</v>
+        <v>2.176809E-2</v>
       </c>
       <c r="CB4" s="4" cm="1">
         <f t="array" aca="1" ref="CB4" ca="1">_xll.YCP($B4,CB$2)</f>
-        <v>0.3009134</v>
+        <v>0.29352767000000002</v>
       </c>
       <c r="CC4" s="4" cm="1">
         <f t="array" aca="1" ref="CC4" ca="1">_xll.YCP($B4,CC$2)</f>
-        <v>3.171831E-2</v>
+        <v>3.2416269999999997E-2</v>
       </c>
       <c r="CD4" s="4" cm="1">
         <f t="array" aca="1" ref="CD4" ca="1">_xll.YCP($B4,CD$2)</f>
-        <v>8.1082299999999993E-3</v>
+        <v>7.2457199999999998E-3</v>
       </c>
       <c r="CE4" s="4" cm="1">
         <f t="array" aca="1" ref="CE4" ca="1">_xll.YCP($B4,CE$2)</f>
-        <v>0.51796017999999999</v>
+        <v>0.51527255000000005</v>
       </c>
       <c r="CF4" s="4" cm="1">
         <f t="array" aca="1" ref="CF4" ca="1">_xll.YCP($B4,CF$2)</f>
-        <v>0.47323611999999998</v>
+        <v>0.47675685000000001</v>
       </c>
       <c r="CG4" s="4" cm="1">
         <f t="array" aca="1" ref="CG4" ca="1">_xll.YCP($B4,CG$2)</f>
-        <v>3.1510000000000002E-5</v>
+        <v>3.1420000000000001E-5</v>
       </c>
       <c r="CH4" s="4" cm="1">
         <f t="array" aca="1" ref="CH4" ca="1">_xll.YCP($B4,CH$2)</f>
-        <v>3.8371E-4</v>
+        <v>3.7980000000000002E-4</v>
       </c>
       <c r="CI4" s="4" cm="1">
         <f t="array" aca="1" ref="CI4" ca="1">_xll.YCP($B4,CI$2)</f>
-        <v>2.8018999999999999E-4</v>
+        <v>3.1359999999999998E-4</v>
       </c>
       <c r="CJ4" s="4" cm="1">
         <f t="array" aca="1" ref="CJ4" ca="1">_xll.YCP($B4,CJ$2)</f>
-        <v>5.7085080000000003E-2</v>
+        <v>5.6872800000000001E-2</v>
       </c>
       <c r="CK4" s="4" cm="1">
         <f t="array" aca="1" ref="CK4" ca="1">_xll.YCP($B4,CK$2)</f>
-        <v>0.41553125000000002</v>
+        <v>0.41854587999999998</v>
       </c>
       <c r="CL4" s="4" cm="1">
         <f t="array" aca="1" ref="CL4" ca="1">_xll.YCP($B4,CL$2)</f>
-        <v>0.15886464</v>
+        <v>0.15895533000000001</v>
       </c>
       <c r="CM4" s="4" cm="1">
         <f t="array" aca="1" ref="CM4" ca="1">_xll.YCP($B4,CM$2)</f>
-        <v>0.15835298</v>
+        <v>0.15848625999999999</v>
       </c>
       <c r="CN4" s="4" cm="1">
         <f t="array" aca="1" ref="CN4" ca="1">_xll.YCP($B4,CN$2)</f>
-        <v>7.4801380000000001E-2</v>
+        <v>7.5556949999999998E-2</v>
       </c>
       <c r="CO4" s="4" cm="1">
         <f t="array" aca="1" ref="CO4" ca="1">_xll.YCP($B4,CO$2)</f>
-        <v>4.0600450000000003E-2</v>
+        <v>4.2057709999999998E-2</v>
       </c>
       <c r="CP4" s="4" cm="1">
         <f t="array" aca="1" ref="CP4" ca="1">_xll.YCP($B4,CP$2)</f>
-        <v>6.77599E-3</v>
+        <v>6.3080100000000002E-3</v>
       </c>
       <c r="CQ4" s="4" cm="1">
         <f t="array" aca="1" ref="CQ4" ca="1">_xll.YCP($B4,CQ$2)</f>
-        <v>3.9036979999999999E-2</v>
+        <v>3.9056380000000002E-2</v>
       </c>
       <c r="CR4" s="4" cm="1">
         <f t="array" aca="1" ref="CR4" ca="1">_xll.YCP($B4,CR$2)</f>
-        <v>8.5813589999999995E-2</v>
+        <v>8.4968139999999998E-2</v>
       </c>
       <c r="CS4" s="4" cm="1">
         <f t="array" aca="1" ref="CS4" ca="1">_xll.YCP($B4,CS$2)</f>
-        <v>0.15784371999999999</v>
+        <v>0.15646388</v>
       </c>
       <c r="CT4" s="4" cm="1">
         <f t="array" aca="1" ref="CT4" ca="1">_xll.YCP($B4,CT$2)</f>
-        <v>0.48289737999999999</v>
+        <v>0.48311553000000002</v>
       </c>
       <c r="CU4" s="4" cm="1">
         <f t="array" aca="1" ref="CU4" ca="1">_xll.YCP($B4,CU$2)</f>
-        <v>0.11791798000000001</v>
+        <v>0.11883418</v>
       </c>
       <c r="CV4" s="4" cm="1">
         <f t="array" aca="1" ref="CV4" ca="1">_xll.YCP($B4,CV$2)</f>
-        <v>0.10671873</v>
+        <v>0.10616201</v>
       </c>
       <c r="CW4" s="4" cm="1">
         <f t="array" aca="1" ref="CW4" ca="1">_xll.YCP($B4,CW$2)</f>
-        <v>1.844314E-2</v>
+        <v>1.8212180000000001E-2</v>
       </c>
       <c r="CX4" s="3" cm="1">
         <f t="array" aca="1" ref="CX4" ca="1">_xll.YCP($B4,CX$2)</f>
-        <v>5.6206149999999999</v>
+        <v>5.6067169999999997</v>
       </c>
       <c r="CY4" s="20" cm="1">
         <f t="array" aca="1" ref="CY4" ca="1">_xll.YCP($B4,CY$2)</f>
-        <v>7.4394539999999996</v>
+        <v>7.460197</v>
       </c>
       <c r="CZ4" s="4" cm="1">
         <f t="array" aca="1" ref="CZ4" ca="1">_xll.YCP($B4,CZ$2)</f>
-        <v>4.931953E-2</v>
+        <v>4.9910469999999998E-2</v>
       </c>
       <c r="DA4" s="4" cm="1">
         <f t="array" aca="1" ref="DA4" ca="1">_xll.YCP($B4,DA$2)</f>
-        <v>4.594782E-2</v>
+        <v>4.6038089999999997E-2</v>
       </c>
       <c r="DB4" s="4" cm="1">
         <f t="array" aca="1" ref="DB4" ca="1">_xll.YCP($B4,DB$2)</f>
-        <v>4.6281240000000001E-2</v>
+        <v>4.6412309999999998E-2</v>
       </c>
       <c r="DC4" s="4" cm="1">
         <f t="array" aca="1" ref="DC4" ca="1">_xll.YCP($B4,DC$2)</f>
-        <v>0.41008451000000001</v>
+        <v>0.40961746999999998</v>
       </c>
       <c r="DD4" s="4" cm="1">
         <f t="array" aca="1" ref="DD4" ca="1">_xll.YCP($B4,DD$2)</f>
-        <v>0.47380720999999998</v>
+        <v>0.47391624999999998</v>
       </c>
       <c r="DE4" s="4" cm="1">
         <f t="array" aca="1" ref="DE4" ca="1">_xll.YCP($B4,DE$2)</f>
-        <v>0.10118255</v>
+        <v>0.10114326999999999</v>
       </c>
       <c r="DF4" s="4" cm="1">
         <f t="array" aca="1" ref="DF4" ca="1">_xll.YCP($B4,DF$2)</f>
-        <v>7.4729899999999997E-3</v>
+        <v>7.5024799999999997E-3</v>
       </c>
       <c r="DG4" s="4" cm="1">
         <f t="array" aca="1" ref="DG4" ca="1">_xll.YCP($B4,DG$2)</f>
-        <v>7.4527500000000002E-3</v>
+        <v>7.8205299999999991E-3</v>
       </c>
       <c r="DH4" s="4" cm="1">
         <f t="array" aca="1" ref="DH4" ca="1">_xll.YCP($B4,DH$2)</f>
-        <v>0.51796017999999999</v>
+        <v>0.51527811999999995</v>
       </c>
       <c r="DI4" s="4" cm="1">
         <f t="array" aca="1" ref="DI4" ca="1">_xll.YCP($B4,DI$2)</f>
-        <v>0.47495289000000002</v>
+        <v>0.4784542</v>
       </c>
       <c r="DJ4" s="4" cm="1">
         <f t="array" aca="1" ref="DJ4" ca="1">_xll.YCP($B4,DJ$2)</f>
-        <v>8.1082299999999993E-3</v>
+        <v>7.2457199999999998E-3</v>
       </c>
       <c r="DK4" s="4" cm="1">
         <f t="array" aca="1" ref="DK4" ca="1">_xll.YCP($B4,DK$2)</f>
-        <v>2.136412E-2</v>
+        <v>2.373188E-2</v>
       </c>
       <c r="DL4" s="4" cm="1">
         <f t="array" aca="1" ref="DL4" ca="1">_xll.YCP($B4,DL$2)</f>
-        <v>0.32466557000000001</v>
+        <v>0.32259431</v>
       </c>
       <c r="DM4" s="4" cm="1">
         <f t="array" aca="1" ref="DM4" ca="1">_xll.YCP($B4,DM$2)</f>
-        <v>0.10261125</v>
+        <v>0.10318157</v>
       </c>
       <c r="DN4" s="4" cm="1">
         <f t="array" aca="1" ref="DN4" ca="1">_xll.YCP($B4,DN$2)</f>
-        <v>9.0214219999999998E-2</v>
+        <v>8.8980320000000002E-2</v>
       </c>
       <c r="DO4" s="4" cm="1">
         <f t="array" aca="1" ref="DO4" ca="1">_xll.YCP($B4,DO$2)</f>
-        <v>0.36820071999999998</v>
+        <v>0.37111781999999999</v>
       </c>
       <c r="DP4" s="4" cm="1">
         <f t="array" aca="1" ref="DP4" ca="1">_xll.YCP($B4,DP$2)</f>
-        <v>5.6956229999999997E-2</v>
+        <v>5.8005059999999997E-2</v>
       </c>
       <c r="DQ4" s="4" cm="1">
         <f t="array" aca="1" ref="DQ4" ca="1">_xll.YCP($B4,DQ$2)</f>
-        <v>7.7648300000000003E-3</v>
+        <v>8.1478799999999997E-3</v>
       </c>
       <c r="DR4" s="4" cm="1">
         <f t="array" aca="1" ref="DR4" ca="1">_xll.YCP($B4,DR$2)</f>
-        <v>0.97863588000000001</v>
+        <v>0.97626811999999996</v>
       </c>
     </row>
     <row r="5" spans="2:122" x14ac:dyDescent="0.45">
@@ -2400,11 +2400,11 @@
       </c>
       <c r="H5" s="4" cm="1">
         <f t="array" aca="1" ref="H5" ca="1">_xll.YCP($B5,H$2)</f>
-        <v>2.4278300000000002E-3</v>
+        <v>2.3980899999999999E-3</v>
       </c>
       <c r="I5" s="4" cm="1">
         <f t="array" aca="1" ref="I5" ca="1">_xll.YCP($B5,I$2)</f>
-        <v>2.1846000000000001E-2</v>
+        <v>2.2185E-2</v>
       </c>
       <c r="J5" s="5" cm="1">
         <f t="array" aca="1" ref="J5" ca="1">_xll.YCP($B5,J$2)</f>
@@ -2412,23 +2412,23 @@
       </c>
       <c r="K5" s="4" cm="1">
         <f t="array" aca="1" ref="K5" ca="1">_xll.YCP($B5,K$2)</f>
-        <v>0.65974681000000002</v>
+        <v>0.66423098000000003</v>
       </c>
       <c r="L5" s="4" cm="1">
         <f t="array" aca="1" ref="L5" ca="1">_xll.YCP($B5,L$2)</f>
-        <v>1.7077999999999999E-2</v>
+        <v>-2.2796E-2</v>
       </c>
       <c r="M5" s="4" cm="1">
         <f t="array" aca="1" ref="M5" ca="1">_xll.YCP($B5,M$2)</f>
-        <v>6.6511000000000001E-2</v>
+        <v>1.9896E-2</v>
       </c>
       <c r="N5" s="4" cm="1">
         <f t="array" aca="1" ref="N5" ca="1">_xll.YCP($B5,N$2)</f>
-        <v>9.1064000000000006E-2</v>
+        <v>7.4803999999999995E-2</v>
       </c>
       <c r="O5" s="4" cm="1">
         <f t="array" aca="1" ref="O5" ca="1">_xll.YCP($B5,O$2)</f>
-        <v>0.15953500000000001</v>
+        <v>0.13297500000000001</v>
       </c>
       <c r="P5" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P5" ca="1">_xll.YCP($B5,P$2)</f>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="R5" s="4" cm="1">
         <f t="array" aca="1" ref="R5" ca="1">_xll.YCP($B5,R$2)</f>
-        <v>0.125638</v>
+        <v>0.113992</v>
       </c>
       <c r="S5" s="3" cm="1">
         <f t="array" aca="1" ref="S5" ca="1">_xll.YCP($B5,S$2)</f>
@@ -2584,279 +2584,279 @@
       </c>
       <c r="BB5" s="4" cm="1">
         <f t="array" aca="1" ref="BB5" ca="1">_xll.YCP($B5,BB$2)</f>
-        <v>0.84737306999999995</v>
+        <v>0.84690158999999998</v>
       </c>
       <c r="BC5" s="4" cm="1">
         <f t="array" aca="1" ref="BC5" ca="1">_xll.YCP($B5,BC$2)</f>
-        <v>1.040309E-2</v>
+        <v>1.0265349999999999E-2</v>
       </c>
       <c r="BD5" s="4" cm="1">
         <f t="array" aca="1" ref="BD5" ca="1">_xll.YCP($B5,BD$2)</f>
-        <v>1.5547679999999999E-2</v>
+        <v>1.5758680000000001E-2</v>
       </c>
       <c r="BE5" s="4" cm="1">
         <f t="array" aca="1" ref="BE5" ca="1">_xll.YCP($B5,BE$2)</f>
-        <v>4.8091549999999997E-2</v>
+        <v>4.9469039999999999E-2</v>
       </c>
       <c r="BF5" s="4" cm="1">
         <f t="array" aca="1" ref="BF5" ca="1">_xll.YCP($B5,BF$2)</f>
-        <v>3.17651E-3</v>
+        <v>3.3881200000000001E-3</v>
       </c>
       <c r="BG5" s="4" cm="1">
         <f t="array" aca="1" ref="BG5" ca="1">_xll.YCP($B5,BG$2)</f>
-        <v>5.9347000000000002E-3</v>
+        <v>6.0880099999999996E-3</v>
       </c>
       <c r="BH5" s="4" cm="1">
         <f t="array" aca="1" ref="BH5" ca="1">_xll.YCP($B5,BH$2)</f>
-        <v>3.3958660000000002E-2</v>
+        <v>3.2005989999999998E-2</v>
       </c>
       <c r="BI5" s="4" cm="1">
         <f t="array" aca="1" ref="BI5" ca="1">_xll.YCP($B5,BI$2)</f>
-        <v>2.0106809999999999E-2</v>
+        <v>2.2405629999999999E-2</v>
       </c>
       <c r="BJ5" s="4" cm="1">
         <f t="array" aca="1" ref="BJ5" ca="1">_xll.YCP($B5,BJ$2)</f>
-        <v>0.18405730000000001</v>
+        <v>0.20215195</v>
       </c>
       <c r="BK5" s="4" cm="1">
         <f t="array" aca="1" ref="BK5" ca="1">_xll.YCP($B5,BK$2)</f>
-        <v>0.24454017</v>
+        <v>0.22607944999999999</v>
       </c>
       <c r="BL5" s="4" cm="1">
         <f t="array" aca="1" ref="BL5" ca="1">_xll.YCP($B5,BL$2)</f>
-        <v>0.17552704999999999</v>
+        <v>0.16719458000000001</v>
       </c>
       <c r="BM5" s="4" cm="1">
         <f t="array" aca="1" ref="BM5" ca="1">_xll.YCP($B5,BM$2)</f>
-        <v>0.10720393</v>
+        <v>0.11275256</v>
       </c>
       <c r="BN5" s="4" cm="1">
         <f t="array" aca="1" ref="BN5" ca="1">_xll.YCP($B5,BN$2)</f>
-        <v>0.10244505</v>
+        <v>0.10784440000000001</v>
       </c>
       <c r="BO5" s="4" cm="1">
         <f t="array" aca="1" ref="BO5" ca="1">_xll.YCP($B5,BO$2)</f>
-        <v>6.2892820000000002E-2</v>
+        <v>6.0463500000000003E-2</v>
       </c>
       <c r="BP5" s="4" cm="1">
         <f t="array" aca="1" ref="BP5" ca="1">_xll.YCP($B5,BP$2)</f>
-        <v>3.928653E-2</v>
+        <v>4.1028889999999998E-2</v>
       </c>
       <c r="BQ5" s="4" cm="1">
         <f t="array" aca="1" ref="BQ5" ca="1">_xll.YCP($B5,BQ$2)</f>
-        <v>4.55063E-2</v>
+        <v>4.5926549999999997E-2</v>
       </c>
       <c r="BR5" s="4" cm="1">
         <f t="array" aca="1" ref="BR5" ca="1">_xll.YCP($B5,BR$2)</f>
-        <v>3.854084E-2</v>
+        <v>3.6558130000000001E-2</v>
       </c>
       <c r="BS5" s="4" cm="1">
         <f t="array" aca="1" ref="BS5" ca="1">_xll.YCP($B5,BS$2)</f>
-        <v>3.338969E-2</v>
+        <v>3.5821489999999997E-2</v>
       </c>
       <c r="BT5" s="4" cm="1">
         <f t="array" aca="1" ref="BT5" ca="1">_xll.YCP($B5,BT$2)</f>
-        <v>7.3144529999999999E-2</v>
+        <v>7.1645959999999995E-2</v>
       </c>
       <c r="BU5" s="4" cm="1">
         <f t="array" aca="1" ref="BU5" ca="1">_xll.YCP($B5,BU$2)</f>
-        <v>8.0366690000000005E-2</v>
+        <v>7.9141089999999997E-2</v>
       </c>
       <c r="BV5" s="4" cm="1">
         <f t="array" aca="1" ref="BV5" ca="1">_xll.YCP($B5,BV$2)</f>
-        <v>3.8369729999999998E-2</v>
+        <v>3.7350559999999998E-2</v>
       </c>
       <c r="BW5" s="4" cm="1">
         <f t="array" aca="1" ref="BW5" ca="1">_xll.YCP($B5,BW$2)</f>
-        <v>3.968058E-2</v>
+        <v>3.9036809999999998E-2</v>
       </c>
       <c r="BX5" s="4" cm="1">
         <f t="array" aca="1" ref="BX5" ca="1">_xll.YCP($B5,BX$2)</f>
-        <v>0.14845576999999999</v>
+        <v>0.15105473999999999</v>
       </c>
       <c r="BY5" s="4" cm="1">
         <f t="array" aca="1" ref="BY5" ca="1">_xll.YCP($B5,BY$2)</f>
-        <v>8.8919129999999999E-2</v>
+        <v>9.1134279999999998E-2</v>
       </c>
       <c r="BZ5" s="4" cm="1">
         <f t="array" aca="1" ref="BZ5" ca="1">_xll.YCP($B5,BZ$2)</f>
-        <v>0.13058114000000001</v>
+        <v>0.13231872</v>
       </c>
       <c r="CA5" s="4" cm="1">
         <f t="array" aca="1" ref="CA5" ca="1">_xll.YCP($B5,CA$2)</f>
-        <v>2.2018360000000001E-2</v>
+        <v>2.2640480000000001E-2</v>
       </c>
       <c r="CB5" s="4" cm="1">
         <f t="array" aca="1" ref="CB5" ca="1">_xll.YCP($B5,CB$2)</f>
-        <v>0.31016916999999999</v>
+        <v>0.30445095999999999</v>
       </c>
       <c r="CC5" s="4" cm="1">
         <f t="array" aca="1" ref="CC5" ca="1">_xll.YCP($B5,CC$2)</f>
-        <v>3.2235760000000002E-2</v>
+        <v>3.2776340000000001E-2</v>
       </c>
       <c r="CD5" s="4" cm="1">
         <f t="array" aca="1" ref="CD5" ca="1">_xll.YCP($B5,CD$2)</f>
-        <v>9.2295499999999996E-3</v>
+        <v>8.5093100000000008E-3</v>
       </c>
       <c r="CE5" s="4" cm="1">
         <f t="array" aca="1" ref="CE5" ca="1">_xll.YCP($B5,CE$2)</f>
-        <v>0.68503455999999996</v>
+        <v>0.68216246999999997</v>
       </c>
       <c r="CF5" s="4" cm="1">
         <f t="array" aca="1" ref="CF5" ca="1">_xll.YCP($B5,CF$2)</f>
-        <v>0.30497222000000002</v>
+        <v>0.30862130999999998</v>
       </c>
       <c r="CG5" s="4" cm="1">
         <f t="array" aca="1" ref="CG5" ca="1">_xll.YCP($B5,CG$2)</f>
-        <v>1.9579999999999999E-5</v>
+        <v>1.9640000000000002E-5</v>
       </c>
       <c r="CH5" s="4" cm="1">
         <f t="array" aca="1" ref="CH5" ca="1">_xll.YCP($B5,CH$2)</f>
-        <v>2.7043999999999999E-4</v>
+        <v>2.6924000000000002E-4</v>
       </c>
       <c r="CI5" s="4" cm="1">
         <f t="array" aca="1" ref="CI5" ca="1">_xll.YCP($B5,CI$2)</f>
-        <v>4.7356999999999998E-4</v>
+        <v>4.1796999999999998E-4</v>
       </c>
       <c r="CJ5" s="4" cm="1">
         <f t="array" aca="1" ref="CJ5" ca="1">_xll.YCP($B5,CJ$2)</f>
-        <v>5.2204649999999998E-2</v>
+        <v>5.2177660000000001E-2</v>
       </c>
       <c r="CK5" s="4" cm="1">
         <f t="array" aca="1" ref="CK5" ca="1">_xll.YCP($B5,CK$2)</f>
-        <v>0.43332970999999998</v>
+        <v>0.43599315999999999</v>
       </c>
       <c r="CL5" s="4" cm="1">
         <f t="array" aca="1" ref="CL5" ca="1">_xll.YCP($B5,CL$2)</f>
-        <v>0.14910648000000001</v>
+        <v>0.14935451999999999</v>
       </c>
       <c r="CM5" s="4" cm="1">
         <f t="array" aca="1" ref="CM5" ca="1">_xll.YCP($B5,CM$2)</f>
-        <v>0.16230073</v>
+        <v>0.16248446999999999</v>
       </c>
       <c r="CN5" s="4" cm="1">
         <f t="array" aca="1" ref="CN5" ca="1">_xll.YCP($B5,CN$2)</f>
-        <v>7.5951850000000001E-2</v>
+        <v>7.6662960000000002E-2</v>
       </c>
       <c r="CO5" s="4" cm="1">
         <f t="array" aca="1" ref="CO5" ca="1">_xll.YCP($B5,CO$2)</f>
-        <v>4.1056509999999997E-2</v>
+        <v>4.2501709999999998E-2</v>
       </c>
       <c r="CP5" s="4" cm="1">
         <f t="array" aca="1" ref="CP5" ca="1">_xll.YCP($B5,CP$2)</f>
-        <v>6.8520999999999999E-3</v>
+        <v>6.3746000000000002E-3</v>
       </c>
       <c r="CQ5" s="4" cm="1">
         <f t="array" aca="1" ref="CQ5" ca="1">_xll.YCP($B5,CQ$2)</f>
-        <v>3.9087129999999998E-2</v>
+        <v>3.9317320000000003E-2</v>
       </c>
       <c r="CR5" s="4" cm="1">
         <f t="array" aca="1" ref="CR5" ca="1">_xll.YCP($B5,CR$2)</f>
-        <v>7.4795650000000005E-2</v>
+        <v>7.268281E-2</v>
       </c>
       <c r="CS5" s="4" cm="1">
         <f t="array" aca="1" ref="CS5" ca="1">_xll.YCP($B5,CS$2)</f>
-        <v>0.15344651000000001</v>
+        <v>0.15261521</v>
       </c>
       <c r="CT5" s="4" cm="1">
         <f t="array" aca="1" ref="CT5" ca="1">_xll.YCP($B5,CT$2)</f>
-        <v>0.49122417000000002</v>
+        <v>0.49163951</v>
       </c>
       <c r="CU5" s="4" cm="1">
         <f t="array" aca="1" ref="CU5" ca="1">_xll.YCP($B5,CU$2)</f>
-        <v>0.1199614</v>
+        <v>0.12066934</v>
       </c>
       <c r="CV5" s="4" cm="1">
         <f t="array" aca="1" ref="CV5" ca="1">_xll.YCP($B5,CV$2)</f>
-        <v>0.11173282</v>
+        <v>0.11123731000000001</v>
       </c>
       <c r="CW5" s="4" cm="1">
         <f t="array" aca="1" ref="CW5" ca="1">_xll.YCP($B5,CW$2)</f>
-        <v>1.7115729999999999E-2</v>
+        <v>1.6873260000000001E-2</v>
       </c>
       <c r="CX5" s="3" cm="1">
         <f t="array" aca="1" ref="CX5" ca="1">_xll.YCP($B5,CX$2)</f>
-        <v>5.5818250000000003</v>
+        <v>5.5660689999999997</v>
       </c>
       <c r="CY5" s="20" cm="1">
         <f t="array" aca="1" ref="CY5" ca="1">_xll.YCP($B5,CY$2)</f>
-        <v>7.404388</v>
+        <v>7.4289259999999997</v>
       </c>
       <c r="CZ5" s="4" cm="1">
         <f t="array" aca="1" ref="CZ5" ca="1">_xll.YCP($B5,CZ$2)</f>
-        <v>5.0340080000000002E-2</v>
+        <v>5.1052050000000002E-2</v>
       </c>
       <c r="DA5" s="4" cm="1">
         <f t="array" aca="1" ref="DA5" ca="1">_xll.YCP($B5,DA$2)</f>
-        <v>4.7002910000000002E-2</v>
+        <v>4.7117149999999997E-2</v>
       </c>
       <c r="DB5" s="4" cm="1">
         <f t="array" aca="1" ref="DB5" ca="1">_xll.YCP($B5,DB$2)</f>
-        <v>4.758308E-2</v>
+        <v>4.7740629999999999E-2</v>
       </c>
       <c r="DC5" s="4" cm="1">
         <f t="array" aca="1" ref="DC5" ca="1">_xll.YCP($B5,DC$2)</f>
-        <v>0.38822770000000001</v>
+        <v>0.38799422</v>
       </c>
       <c r="DD5" s="4" cm="1">
         <f t="array" aca="1" ref="DD5" ca="1">_xll.YCP($B5,DD$2)</f>
-        <v>0.47928056000000002</v>
+        <v>0.47920748000000002</v>
       </c>
       <c r="DE5" s="4" cm="1">
         <f t="array" aca="1" ref="DE5" ca="1">_xll.YCP($B5,DE$2)</f>
-        <v>0.11838553</v>
+        <v>0.11826136</v>
       </c>
       <c r="DF5" s="4" cm="1">
         <f t="array" aca="1" ref="DF5" ca="1">_xll.YCP($B5,DF$2)</f>
-        <v>6.5375199999999998E-3</v>
+        <v>6.6108599999999997E-3</v>
       </c>
       <c r="DG5" s="4" cm="1">
         <f t="array" aca="1" ref="DG5" ca="1">_xll.YCP($B5,DG$2)</f>
-        <v>7.5686800000000004E-3</v>
+        <v>7.9260800000000003E-3</v>
       </c>
       <c r="DH5" s="4" cm="1">
         <f t="array" aca="1" ref="DH5" ca="1">_xll.YCP($B5,DH$2)</f>
-        <v>0.68503455999999996</v>
+        <v>0.68216982999999998</v>
       </c>
       <c r="DI5" s="4" cm="1">
         <f t="array" aca="1" ref="DI5" ca="1">_xll.YCP($B5,DI$2)</f>
-        <v>0.30611699999999997</v>
+        <v>0.30975793000000001</v>
       </c>
       <c r="DJ5" s="4" cm="1">
         <f t="array" aca="1" ref="DJ5" ca="1">_xll.YCP($B5,DJ$2)</f>
-        <v>9.2295499999999996E-3</v>
+        <v>8.5093100000000008E-3</v>
       </c>
       <c r="DK5" s="4" cm="1">
         <f t="array" aca="1" ref="DK5" ca="1">_xll.YCP($B5,DK$2)</f>
-        <v>4.6821969999999997E-2</v>
+        <v>5.0522070000000002E-2</v>
       </c>
       <c r="DL5" s="4" cm="1">
         <f t="array" aca="1" ref="DL5" ca="1">_xll.YCP($B5,DL$2)</f>
-        <v>0.41766640999999999</v>
+        <v>0.41521741000000001</v>
       </c>
       <c r="DM5" s="4" cm="1">
         <f t="array" aca="1" ref="DM5" ca="1">_xll.YCP($B5,DM$2)</f>
-        <v>0.13456137000000001</v>
+        <v>0.13498252999999999</v>
       </c>
       <c r="DN5" s="4" cm="1">
         <f t="array" aca="1" ref="DN5" ca="1">_xll.YCP($B5,DN$2)</f>
-        <v>0.13167308999999999</v>
+        <v>0.13049267000000001</v>
       </c>
       <c r="DO5" s="4" cm="1">
         <f t="array" aca="1" ref="DO5" ca="1">_xll.YCP($B5,DO$2)</f>
-        <v>0.23916176</v>
+        <v>0.24208922999999999</v>
       </c>
       <c r="DP5" s="4" cm="1">
         <f t="array" aca="1" ref="DP5" ca="1">_xll.YCP($B5,DP$2)</f>
-        <v>3.7170460000000002E-2</v>
+        <v>3.7989170000000003E-2</v>
       </c>
       <c r="DQ5" s="4" cm="1">
         <f t="array" aca="1" ref="DQ5" ca="1">_xll.YCP($B5,DQ$2)</f>
-        <v>7.9420600000000008E-3</v>
+        <v>8.31666E-3</v>
       </c>
       <c r="DR5" s="4" cm="1">
         <f t="array" aca="1" ref="DR5" ca="1">_xll.YCP($B5,DR$2)</f>
-        <v>0.95317803000000001</v>
+        <v>0.94947793000000003</v>
       </c>
     </row>
     <row r="6" spans="2:122" x14ac:dyDescent="0.45">
@@ -2885,11 +2885,11 @@
       </c>
       <c r="H6" s="4" cm="1">
         <f t="array" aca="1" ref="H6" ca="1">_xll.YCP($B6,H$2)</f>
-        <v>2.4793900000000002E-3</v>
+        <v>2.4446899999999998E-3</v>
       </c>
       <c r="I6" s="4" cm="1">
         <f t="array" aca="1" ref="I6" ca="1">_xll.YCP($B6,I$2)</f>
-        <v>1.6036999999999999E-2</v>
+        <v>1.6317999999999999E-2</v>
       </c>
       <c r="J6" s="5" cm="1">
         <f t="array" aca="1" ref="J6" ca="1">_xll.YCP($B6,J$2)</f>
@@ -2897,23 +2897,23 @@
       </c>
       <c r="K6" s="4" cm="1">
         <f t="array" aca="1" ref="K6" ca="1">_xll.YCP($B6,K$2)</f>
-        <v>0.60754735999999998</v>
+        <v>0.61224232999999995</v>
       </c>
       <c r="L6" s="4" cm="1">
         <f t="array" aca="1" ref="L6" ca="1">_xll.YCP($B6,L$2)</f>
-        <v>2.0926E-2</v>
+        <v>-2.6200000000000001E-2</v>
       </c>
       <c r="M6" s="4" cm="1">
         <f t="array" aca="1" ref="M6" ca="1">_xll.YCP($B6,M$2)</f>
-        <v>8.3173999999999998E-2</v>
+        <v>2.5780999999999998E-2</v>
       </c>
       <c r="N6" s="4" cm="1">
         <f t="array" aca="1" ref="N6" ca="1">_xll.YCP($B6,N$2)</f>
-        <v>0.110693</v>
+        <v>9.1591000000000006E-2</v>
       </c>
       <c r="O6" s="4" cm="1">
         <f t="array" aca="1" ref="O6" ca="1">_xll.YCP($B6,O$2)</f>
-        <v>0.18790599999999999</v>
+        <v>0.15717300000000001</v>
       </c>
       <c r="P6" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P6" ca="1">_xll.YCP($B6,P$2)</f>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="R6" s="4" cm="1">
         <f t="array" aca="1" ref="R6" ca="1">_xll.YCP($B6,R$2)</f>
-        <v>0.14536199999999999</v>
+        <v>0.131714</v>
       </c>
       <c r="S6" s="3" cm="1">
         <f t="array" aca="1" ref="S6" ca="1">_xll.YCP($B6,S$2)</f>
@@ -3069,159 +3069,159 @@
       </c>
       <c r="BB6" s="4" cm="1">
         <f t="array" aca="1" ref="BB6" ca="1">_xll.YCP($B6,BB$2)</f>
-        <v>0.83877955000000004</v>
+        <v>0.83732019000000002</v>
       </c>
       <c r="BC6" s="4" cm="1">
         <f t="array" aca="1" ref="BC6" ca="1">_xll.YCP($B6,BC$2)</f>
-        <v>1.074286E-2</v>
+        <v>1.0619760000000001E-2</v>
       </c>
       <c r="BD6" s="4" cm="1">
         <f t="array" aca="1" ref="BD6" ca="1">_xll.YCP($B6,BD$2)</f>
-        <v>1.455798E-2</v>
+        <v>1.478169E-2</v>
       </c>
       <c r="BE6" s="4" cm="1">
         <f t="array" aca="1" ref="BE6" ca="1">_xll.YCP($B6,BE$2)</f>
-        <v>4.9561639999999997E-2</v>
+        <v>5.1099260000000001E-2</v>
       </c>
       <c r="BF6" s="4" cm="1">
         <f t="array" aca="1" ref="BF6" ca="1">_xll.YCP($B6,BF$2)</f>
-        <v>2.7552700000000002E-3</v>
+        <v>2.96977E-3</v>
       </c>
       <c r="BG6" s="4" cm="1">
         <f t="array" aca="1" ref="BG6" ca="1">_xll.YCP($B6,BG$2)</f>
-        <v>5.1968500000000003E-3</v>
+        <v>5.3378899999999996E-3</v>
       </c>
       <c r="BH6" s="4" cm="1">
         <f t="array" aca="1" ref="BH6" ca="1">_xll.YCP($B6,BH$2)</f>
-        <v>3.5396549999999999E-2</v>
+        <v>3.3396879999999997E-2</v>
       </c>
       <c r="BI6" s="4" cm="1">
         <f t="array" aca="1" ref="BI6" ca="1">_xll.YCP($B6,BI$2)</f>
-        <v>2.0247399999999999E-2</v>
+        <v>2.2652039999999998E-2</v>
       </c>
       <c r="BJ6" s="4" cm="1">
         <f t="array" aca="1" ref="BJ6" ca="1">_xll.YCP($B6,BJ$2)</f>
-        <v>0.18168587</v>
+        <v>0.19960732</v>
       </c>
       <c r="BK6" s="4" cm="1">
         <f t="array" aca="1" ref="BK6" ca="1">_xll.YCP($B6,BK$2)</f>
-        <v>0.24426808</v>
+        <v>0.22563259999999999</v>
       </c>
       <c r="BL6" s="4" cm="1">
         <f t="array" aca="1" ref="BL6" ca="1">_xll.YCP($B6,BL$2)</f>
-        <v>0.17580459000000001</v>
+        <v>0.16744332000000001</v>
       </c>
       <c r="BM6" s="4" cm="1">
         <f t="array" aca="1" ref="BM6" ca="1">_xll.YCP($B6,BM$2)</f>
-        <v>0.10747063</v>
+        <v>0.1131933</v>
       </c>
       <c r="BN6" s="4" cm="1">
         <f t="array" aca="1" ref="BN6" ca="1">_xll.YCP($B6,BN$2)</f>
-        <v>0.10362194</v>
+        <v>0.10915585</v>
       </c>
       <c r="BO6" s="4" cm="1">
         <f t="array" aca="1" ref="BO6" ca="1">_xll.YCP($B6,BO$2)</f>
-        <v>6.3523789999999997E-2</v>
+        <v>6.1055619999999998E-2</v>
       </c>
       <c r="BP6" s="4" cm="1">
         <f t="array" aca="1" ref="BP6" ca="1">_xll.YCP($B6,BP$2)</f>
-        <v>3.918804E-2</v>
+        <v>4.0980919999999997E-2</v>
       </c>
       <c r="BQ6" s="4" cm="1">
         <f t="array" aca="1" ref="BQ6" ca="1">_xll.YCP($B6,BQ$2)</f>
-        <v>4.551169E-2</v>
+        <v>4.6011080000000003E-2</v>
       </c>
       <c r="BR6" s="4" cm="1">
         <f t="array" aca="1" ref="BR6" ca="1">_xll.YCP($B6,BR$2)</f>
-        <v>3.8925370000000001E-2</v>
+        <v>3.6919979999999998E-2</v>
       </c>
       <c r="BS6" s="4" cm="1">
         <f t="array" aca="1" ref="BS6" ca="1">_xll.YCP($B6,BS$2)</f>
-        <v>3.2690070000000002E-2</v>
+        <v>3.4732249999999999E-2</v>
       </c>
       <c r="BT6" s="4" cm="1">
         <f t="array" aca="1" ref="BT6" ca="1">_xll.YCP($B6,BT$2)</f>
-        <v>7.3626629999999998E-2</v>
+        <v>7.2132160000000001E-2</v>
       </c>
       <c r="BU6" s="4" cm="1">
         <f t="array" aca="1" ref="BU6" ca="1">_xll.YCP($B6,BU$2)</f>
-        <v>7.980487E-2</v>
+        <v>7.8775319999999996E-2</v>
       </c>
       <c r="BV6" s="4" cm="1">
         <f t="array" aca="1" ref="BV6" ca="1">_xll.YCP($B6,BV$2)</f>
-        <v>3.8163639999999999E-2</v>
+        <v>3.7371050000000003E-2</v>
       </c>
       <c r="BW6" s="4" cm="1">
         <f t="array" aca="1" ref="BW6" ca="1">_xll.YCP($B6,BW$2)</f>
-        <v>3.8851320000000002E-2</v>
+        <v>3.8259399999999999E-2</v>
       </c>
       <c r="BX6" s="4" cm="1">
         <f t="array" aca="1" ref="BX6" ca="1">_xll.YCP($B6,BX$2)</f>
-        <v>0.14649052000000001</v>
+        <v>0.14925490999999999</v>
       </c>
       <c r="BY6" s="4" cm="1">
         <f t="array" aca="1" ref="BY6" ca="1">_xll.YCP($B6,BY$2)</f>
-        <v>8.9953959999999999E-2</v>
+        <v>9.2071910000000007E-2</v>
       </c>
       <c r="BZ6" s="4" cm="1">
         <f t="array" aca="1" ref="BZ6" ca="1">_xll.YCP($B6,BZ$2)</f>
-        <v>0.13047474000000001</v>
+        <v>0.13188401</v>
       </c>
       <c r="CA6" s="4" cm="1">
         <f t="array" aca="1" ref="CA6" ca="1">_xll.YCP($B6,CA$2)</f>
-        <v>2.2426129999999999E-2</v>
+        <v>2.3029870000000001E-2</v>
       </c>
       <c r="CB6" s="4" cm="1">
         <f t="array" aca="1" ref="CB6" ca="1">_xll.YCP($B6,CB$2)</f>
-        <v>0.31276755000000001</v>
+        <v>0.30715896999999998</v>
       </c>
       <c r="CC6" s="4" cm="1">
         <f t="array" aca="1" ref="CC6" ca="1">_xll.YCP($B6,CC$2)</f>
-        <v>3.2144109999999997E-2</v>
+        <v>3.2764290000000001E-2</v>
       </c>
       <c r="CD6" s="4" cm="1">
         <f t="array" aca="1" ref="CD6" ca="1">_xll.YCP($B6,CD$2)</f>
-        <v>9.6586499999999995E-3</v>
+        <v>9.0599700000000005E-3</v>
       </c>
       <c r="CE6" s="4" cm="1">
         <f t="array" aca="1" ref="CE6" ca="1">_xll.YCP($B6,CE$2)</f>
-        <v>0.82600996999999998</v>
+        <v>0.82418893000000004</v>
       </c>
       <c r="CF6" s="4" cm="1">
         <f t="array" aca="1" ref="CF6" ca="1">_xll.YCP($B6,CF$2)</f>
-        <v>0.16367114999999999</v>
+        <v>0.16613375999999999</v>
       </c>
       <c r="CG6" s="4" cm="1">
         <f t="array" aca="1" ref="CG6" ca="1">_xll.YCP($B6,CG$2)</f>
-        <v>1.3720000000000001E-5</v>
+        <v>1.38E-5</v>
       </c>
       <c r="CH6" s="4" cm="1">
         <f t="array" aca="1" ref="CH6" ca="1">_xll.YCP($B6,CH$2)</f>
-        <v>1.0817E-4</v>
+        <v>1.0993E-4</v>
       </c>
       <c r="CI6" s="4" cm="1">
         <f t="array" aca="1" ref="CI6" ca="1">_xll.YCP($B6,CI$2)</f>
-        <v>5.3826000000000004E-4</v>
+        <v>4.9353999999999999E-4</v>
       </c>
       <c r="CJ6" s="4" cm="1">
         <f t="array" aca="1" ref="CJ6" ca="1">_xll.YCP($B6,CJ$2)</f>
-        <v>6.7337540000000001E-2</v>
+        <v>6.7301620000000006E-2</v>
       </c>
       <c r="CK6" s="4" cm="1">
         <f t="array" aca="1" ref="CK6" ca="1">_xll.YCP($B6,CK$2)</f>
-        <v>0.47123821999999999</v>
+        <v>0.47466153999999999</v>
       </c>
       <c r="CL6" s="4" cm="1">
         <f t="array" aca="1" ref="CL6" ca="1">_xll.YCP($B6,CL$2)</f>
-        <v>0.16884225999999999</v>
+        <v>0.16918463</v>
       </c>
       <c r="CM6" s="4" cm="1">
         <f t="array" aca="1" ref="CM6" ca="1">_xll.YCP($B6,CM$2)</f>
-        <v>0.18634651999999999</v>
+        <v>0.18659723</v>
       </c>
       <c r="CN6" s="4" cm="1">
         <f t="array" aca="1" ref="CN6" ca="1">_xll.YCP($B6,CN$2)</f>
-        <v>3.4545299999999999E-3</v>
+        <v>3.4505400000000002E-3</v>
       </c>
       <c r="CO6" s="4" cm="1">
         <f t="array" aca="1" ref="CO6" ca="1">_xll.YCP($B6,CO$2)</f>
@@ -3233,115 +3233,115 @@
       </c>
       <c r="CQ6" s="4" cm="1">
         <f t="array" aca="1" ref="CQ6" ca="1">_xll.YCP($B6,CQ$2)</f>
-        <v>3.6530449999999999E-2</v>
+        <v>3.6516029999999998E-2</v>
       </c>
       <c r="CR6" s="4" cm="1">
         <f t="array" aca="1" ref="CR6" ca="1">_xll.YCP($B6,CR$2)</f>
-        <v>5.053966E-2</v>
+        <v>4.7412160000000002E-2</v>
       </c>
       <c r="CS6" s="4" cm="1">
         <f t="array" aca="1" ref="CS6" ca="1">_xll.YCP($B6,CS$2)</f>
-        <v>0.11758502999999999</v>
+        <v>0.11652286000000001</v>
       </c>
       <c r="CT6" s="4" cm="1">
         <f t="array" aca="1" ref="CT6" ca="1">_xll.YCP($B6,CT$2)</f>
-        <v>0.54200194000000002</v>
+        <v>0.54222619000000005</v>
       </c>
       <c r="CU6" s="4" cm="1">
         <f t="array" aca="1" ref="CU6" ca="1">_xll.YCP($B6,CU$2)</f>
-        <v>0.12611939999999999</v>
+        <v>0.12620053000000001</v>
       </c>
       <c r="CV6" s="4" cm="1">
         <f t="array" aca="1" ref="CV6" ca="1">_xll.YCP($B6,CV$2)</f>
-        <v>0.11474961</v>
+        <v>0.11463819</v>
       </c>
       <c r="CW6" s="4" cm="1">
         <f t="array" aca="1" ref="CW6" ca="1">_xll.YCP($B6,CW$2)</f>
-        <v>3.3843200000000001E-3</v>
+        <v>3.2824400000000002E-3</v>
       </c>
       <c r="CX6" s="3" cm="1">
         <f t="array" aca="1" ref="CX6" ca="1">_xll.YCP($B6,CX$2)</f>
-        <v>5.894755</v>
+        <v>5.8781929999999996</v>
       </c>
       <c r="CY6" s="20" cm="1">
         <f t="array" aca="1" ref="CY6" ca="1">_xll.YCP($B6,CY$2)</f>
-        <v>7.6588950000000002</v>
+        <v>7.69834</v>
       </c>
       <c r="CZ6" s="4" cm="1">
         <f t="array" aca="1" ref="CZ6" ca="1">_xll.YCP($B6,CZ$2)</f>
-        <v>4.7343900000000001E-2</v>
+        <v>4.8319180000000003E-2</v>
       </c>
       <c r="DA6" s="4" cm="1">
         <f t="array" aca="1" ref="DA6" ca="1">_xll.YCP($B6,DA$2)</f>
-        <v>4.382254E-2</v>
+        <v>4.3940479999999997E-2</v>
       </c>
       <c r="DB6" s="4" cm="1">
         <f t="array" aca="1" ref="DB6" ca="1">_xll.YCP($B6,DB$2)</f>
-        <v>4.3656269999999997E-2</v>
+        <v>4.3820909999999998E-2</v>
       </c>
       <c r="DC6" s="4" cm="1">
         <f t="array" aca="1" ref="DC6" ca="1">_xll.YCP($B6,DC$2)</f>
-        <v>0.43342440999999998</v>
+        <v>0.43279117</v>
       </c>
       <c r="DD6" s="4" cm="1">
         <f t="array" aca="1" ref="DD6" ca="1">_xll.YCP($B6,DD$2)</f>
-        <v>0.39298853</v>
+        <v>0.39354639000000002</v>
       </c>
       <c r="DE6" s="4" cm="1">
         <f t="array" aca="1" ref="DE6" ca="1">_xll.YCP($B6,DE$2)</f>
-        <v>0.1583823</v>
+        <v>0.15821798000000001</v>
       </c>
       <c r="DF6" s="4" cm="1">
         <f t="array" aca="1" ref="DF6" ca="1">_xll.YCP($B6,DF$2)</f>
-        <v>8.7049599999999994E-3</v>
+        <v>8.8013299999999996E-3</v>
       </c>
       <c r="DG6" s="4" cm="1">
         <f t="array" aca="1" ref="DG6" ca="1">_xll.YCP($B6,DG$2)</f>
-        <v>6.4998E-3</v>
+        <v>6.6431299999999997E-3</v>
       </c>
       <c r="DH6" s="4" cm="1">
         <f t="array" aca="1" ref="DH6" ca="1">_xll.YCP($B6,DH$2)</f>
-        <v>0.82600996999999998</v>
+        <v>0.82419805000000002</v>
       </c>
       <c r="DI6" s="4" cm="1">
         <f t="array" aca="1" ref="DI6" ca="1">_xll.YCP($B6,DI$2)</f>
-        <v>0.16447342000000001</v>
+        <v>0.16693218000000001</v>
       </c>
       <c r="DJ6" s="4" cm="1">
         <f t="array" aca="1" ref="DJ6" ca="1">_xll.YCP($B6,DJ$2)</f>
-        <v>9.6586499999999995E-3</v>
+        <v>9.0599700000000005E-3</v>
       </c>
       <c r="DK6" s="4" cm="1">
         <f t="array" aca="1" ref="DK6" ca="1">_xll.YCP($B6,DK$2)</f>
-        <v>3.9881279999999998E-2</v>
+        <v>4.3064669999999999E-2</v>
       </c>
       <c r="DL6" s="4" cm="1">
         <f t="array" aca="1" ref="DL6" ca="1">_xll.YCP($B6,DL$2)</f>
-        <v>0.50198103999999999</v>
+        <v>0.50001198000000002</v>
       </c>
       <c r="DM6" s="4" cm="1">
         <f t="array" aca="1" ref="DM6" ca="1">_xll.YCP($B6,DM$2)</f>
-        <v>0.16298828000000001</v>
+        <v>0.16387804</v>
       </c>
       <c r="DN6" s="4" cm="1">
         <f t="array" aca="1" ref="DN6" ca="1">_xll.YCP($B6,DN$2)</f>
-        <v>0.1598339</v>
+        <v>0.15874634000000001</v>
       </c>
       <c r="DO6" s="4" cm="1">
         <f t="array" aca="1" ref="DO6" ca="1">_xll.YCP($B6,DO$2)</f>
-        <v>0.14298331</v>
+        <v>0.14543918</v>
       </c>
       <c r="DP6" s="4" cm="1">
         <f t="array" aca="1" ref="DP6" ca="1">_xll.YCP($B6,DP$2)</f>
-        <v>5.5265000000000002E-4</v>
+        <v>5.5900000000000004E-4</v>
       </c>
       <c r="DQ6" s="4" cm="1">
         <f t="array" aca="1" ref="DQ6" ca="1">_xll.YCP($B6,DQ$2)</f>
-        <v>6.93605E-3</v>
+        <v>7.0885100000000001E-3</v>
       </c>
       <c r="DR6" s="4" cm="1">
         <f t="array" aca="1" ref="DR6" ca="1">_xll.YCP($B6,DR$2)</f>
-        <v>0.96011871999999998</v>
+        <v>0.95693532999999997</v>
       </c>
     </row>
     <row r="7" spans="2:122" x14ac:dyDescent="0.45">
@@ -3370,11 +3370,11 @@
       </c>
       <c r="H7" s="4" cm="1">
         <f t="array" aca="1" ref="H7" ca="1">_xll.YCP($B7,H$2)</f>
-        <v>2.64722E-3</v>
+        <v>2.6082900000000001E-3</v>
       </c>
       <c r="I7" s="4" cm="1">
         <f t="array" aca="1" ref="I7" ca="1">_xll.YCP($B7,I$2)</f>
-        <v>1.0932000000000001E-2</v>
+        <v>1.1148999999999999E-2</v>
       </c>
       <c r="J7" s="5" cm="1">
         <f t="array" aca="1" ref="J7" ca="1">_xll.YCP($B7,J$2)</f>
@@ -3382,23 +3382,23 @@
       </c>
       <c r="K7" s="4" cm="1">
         <f t="array" aca="1" ref="K7" ca="1">_xll.YCP($B7,K$2)</f>
-        <v>0.49730806999999999</v>
+        <v>0.50131218</v>
       </c>
       <c r="L7" s="4" cm="1">
         <f t="array" aca="1" ref="L7" ca="1">_xll.YCP($B7,L$2)</f>
-        <v>2.5121000000000001E-2</v>
+        <v>-2.9163999999999999E-2</v>
       </c>
       <c r="M7" s="4" cm="1">
         <f t="array" aca="1" ref="M7" ca="1">_xll.YCP($B7,M$2)</f>
-        <v>0.10247199999999999</v>
+        <v>3.2698999999999999E-2</v>
       </c>
       <c r="N7" s="4" cm="1">
         <f t="array" aca="1" ref="N7" ca="1">_xll.YCP($B7,N$2)</f>
-        <v>0.13586899999999999</v>
+        <v>0.11375</v>
       </c>
       <c r="O7" s="4" cm="1">
         <f t="array" aca="1" ref="O7" ca="1">_xll.YCP($B7,O$2)</f>
-        <v>0.22533300000000001</v>
+        <v>0.18736800000000001</v>
       </c>
       <c r="P7" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P7" ca="1">_xll.YCP($B7,P$2)</f>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="R7" s="4" cm="1">
         <f t="array" aca="1" ref="R7" ca="1">_xll.YCP($B7,R$2)</f>
-        <v>0.17122699999999999</v>
+        <v>0.15528700000000001</v>
       </c>
       <c r="S7" s="3" cm="1">
         <f t="array" aca="1" ref="S7" ca="1">_xll.YCP($B7,S$2)</f>
@@ -3554,123 +3554,123 @@
       </c>
       <c r="BB7" s="4" cm="1">
         <f t="array" aca="1" ref="BB7" ca="1">_xll.YCP($B7,BB$2)</f>
-        <v>0.81633389000000001</v>
+        <v>0.81425398999999998</v>
       </c>
       <c r="BC7" s="4" cm="1">
         <f t="array" aca="1" ref="BC7" ca="1">_xll.YCP($B7,BC$2)</f>
-        <v>1.1668039999999999E-2</v>
+        <v>1.150313E-2</v>
       </c>
       <c r="BD7" s="4" cm="1">
         <f t="array" aca="1" ref="BD7" ca="1">_xll.YCP($B7,BD$2)</f>
-        <v>1.5369219999999999E-2</v>
+        <v>1.5636130000000002E-2</v>
       </c>
       <c r="BE7" s="4" cm="1">
         <f t="array" aca="1" ref="BE7" ca="1">_xll.YCP($B7,BE$2)</f>
-        <v>5.5226549999999999E-2</v>
+        <v>5.7076429999999997E-2</v>
       </c>
       <c r="BF7" s="4" cm="1">
         <f t="array" aca="1" ref="BF7" ca="1">_xll.YCP($B7,BF$2)</f>
-        <v>3.2272500000000001E-3</v>
+        <v>3.4955799999999999E-3</v>
       </c>
       <c r="BG7" s="4" cm="1">
         <f t="array" aca="1" ref="BG7" ca="1">_xll.YCP($B7,BG$2)</f>
-        <v>6.10314E-3</v>
+        <v>6.2830200000000003E-3</v>
       </c>
       <c r="BH7" s="4" cm="1">
         <f t="array" aca="1" ref="BH7" ca="1">_xll.YCP($B7,BH$2)</f>
-        <v>4.2163449999999998E-2</v>
+        <v>3.9876759999999997E-2</v>
       </c>
       <c r="BI7" s="4" cm="1">
         <f t="array" aca="1" ref="BI7" ca="1">_xll.YCP($B7,BI$2)</f>
-        <v>2.4082800000000001E-2</v>
+        <v>2.7030990000000001E-2</v>
       </c>
       <c r="BJ7" s="4" cm="1">
         <f t="array" aca="1" ref="BJ7" ca="1">_xll.YCP($B7,BJ$2)</f>
-        <v>0.18219572000000001</v>
+        <v>0.20029526</v>
       </c>
       <c r="BK7" s="4" cm="1">
         <f t="array" aca="1" ref="BK7" ca="1">_xll.YCP($B7,BK$2)</f>
-        <v>0.24505974999999999</v>
+        <v>0.22620631999999999</v>
       </c>
       <c r="BL7" s="4" cm="1">
         <f t="array" aca="1" ref="BL7" ca="1">_xll.YCP($B7,BL$2)</f>
-        <v>0.17620754999999999</v>
+        <v>0.16785710000000001</v>
       </c>
       <c r="BM7" s="4" cm="1">
         <f t="array" aca="1" ref="BM7" ca="1">_xll.YCP($B7,BM$2)</f>
-        <v>0.10775789</v>
+        <v>0.11348489</v>
       </c>
       <c r="BN7" s="4" cm="1">
         <f t="array" aca="1" ref="BN7" ca="1">_xll.YCP($B7,BN$2)</f>
-        <v>0.10375884</v>
+        <v>0.10930775</v>
       </c>
       <c r="BO7" s="4" cm="1">
         <f t="array" aca="1" ref="BO7" ca="1">_xll.YCP($B7,BO$2)</f>
-        <v>6.3147380000000003E-2</v>
+        <v>6.0690580000000001E-2</v>
       </c>
       <c r="BP7" s="4" cm="1">
         <f t="array" aca="1" ref="BP7" ca="1">_xll.YCP($B7,BP$2)</f>
-        <v>3.8747770000000001E-2</v>
+        <v>4.0523290000000003E-2</v>
       </c>
       <c r="BQ7" s="4" cm="1">
         <f t="array" aca="1" ref="BQ7" ca="1">_xll.YCP($B7,BQ$2)</f>
-        <v>4.4886009999999997E-2</v>
+        <v>4.5368400000000003E-2</v>
       </c>
       <c r="BR7" s="4" cm="1">
         <f t="array" aca="1" ref="BR7" ca="1">_xll.YCP($B7,BR$2)</f>
-        <v>3.8239099999999998E-2</v>
+        <v>3.6266409999999999E-2</v>
       </c>
       <c r="BS7" s="4" cm="1">
         <f t="array" aca="1" ref="BS7" ca="1">_xll.YCP($B7,BS$2)</f>
-        <v>3.2450769999999997E-2</v>
+        <v>3.4516890000000001E-2</v>
       </c>
       <c r="BT7" s="4" cm="1">
         <f t="array" aca="1" ref="BT7" ca="1">_xll.YCP($B7,BT$2)</f>
-        <v>7.3915369999999994E-2</v>
+        <v>7.239218E-2</v>
       </c>
       <c r="BU7" s="4" cm="1">
         <f t="array" aca="1" ref="BU7" ca="1">_xll.YCP($B7,BU$2)</f>
-        <v>7.9940120000000003E-2</v>
+        <v>7.8869930000000005E-2</v>
       </c>
       <c r="BV7" s="4" cm="1">
         <f t="array" aca="1" ref="BV7" ca="1">_xll.YCP($B7,BV$2)</f>
-        <v>3.8179079999999997E-2</v>
+        <v>3.7359080000000003E-2</v>
       </c>
       <c r="BW7" s="4" cm="1">
         <f t="array" aca="1" ref="BW7" ca="1">_xll.YCP($B7,BW$2)</f>
-        <v>3.8699289999999997E-2</v>
+        <v>3.8097590000000001E-2</v>
       </c>
       <c r="BX7" s="4" cm="1">
         <f t="array" aca="1" ref="BX7" ca="1">_xll.YCP($B7,BX$2)</f>
-        <v>0.14645093000000001</v>
+        <v>0.14916962</v>
       </c>
       <c r="BY7" s="4" cm="1">
         <f t="array" aca="1" ref="BY7" ca="1">_xll.YCP($B7,BY$2)</f>
-        <v>8.9701009999999998E-2</v>
+        <v>9.1852260000000005E-2</v>
       </c>
       <c r="BZ7" s="4" cm="1">
         <f t="array" aca="1" ref="BZ7" ca="1">_xll.YCP($B7,BZ$2)</f>
-        <v>0.12986721000000001</v>
+        <v>0.13132632999999999</v>
       </c>
       <c r="CA7" s="4" cm="1">
         <f t="array" aca="1" ref="CA7" ca="1">_xll.YCP($B7,CA$2)</f>
-        <v>2.2419100000000001E-2</v>
+        <v>2.302715E-2</v>
       </c>
       <c r="CB7" s="4" cm="1">
         <f t="array" aca="1" ref="CB7" ca="1">_xll.YCP($B7,CB$2)</f>
-        <v>0.31359791999999997</v>
+        <v>0.30803782000000002</v>
       </c>
       <c r="CC7" s="4" cm="1">
         <f t="array" aca="1" ref="CC7" ca="1">_xll.YCP($B7,CC$2)</f>
-        <v>3.2187680000000003E-2</v>
+        <v>3.2802730000000002E-2</v>
       </c>
       <c r="CD7" s="4" cm="1">
         <f t="array" aca="1" ref="CD7" ca="1">_xll.YCP($B7,CD$2)</f>
-        <v>1.209285E-2</v>
+        <v>1.1959020000000001E-2</v>
       </c>
       <c r="CE7" s="4" cm="1">
         <f t="array" aca="1" ref="CE7" ca="1">_xll.YCP($B7,CE$2)</f>
-        <v>0.98725770999999996</v>
+        <v>0.98744578000000005</v>
       </c>
       <c r="CF7" s="4" cm="1">
         <f t="array" aca="1" ref="CF7" ca="1">_xll.YCP($B7,CF$2)</f>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="CI7" s="4" cm="1">
         <f t="array" aca="1" ref="CI7" ca="1">_xll.YCP($B7,CI$2)</f>
-        <v>6.4935999999999998E-4</v>
+        <v>5.9513999999999997E-4</v>
       </c>
       <c r="CJ7" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="CJ7" ca="1">_xll.YCP($B7,CJ$2)</f>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="DH7" s="4" cm="1">
         <f t="array" aca="1" ref="DH7" ca="1">_xll.YCP($B7,DH$2)</f>
-        <v>0.98725770999999996</v>
+        <v>0.98745682000000001</v>
       </c>
       <c r="DI7" s="4" cm="1">
         <f t="array" aca="1" ref="DI7" ca="1">_xll.YCP($B7,DI$2)</f>
@@ -3794,23 +3794,23 @@
       </c>
       <c r="DJ7" s="4" cm="1">
         <f t="array" aca="1" ref="DJ7" ca="1">_xll.YCP($B7,DJ$2)</f>
-        <v>1.209285E-2</v>
+        <v>1.1959020000000001E-2</v>
       </c>
       <c r="DK7" s="4" cm="1">
         <f t="array" aca="1" ref="DK7" ca="1">_xll.YCP($B7,DK$2)</f>
-        <v>4.0293519999999999E-2</v>
+        <v>4.3495109999999997E-2</v>
       </c>
       <c r="DL7" s="4" cm="1">
         <f t="array" aca="1" ref="DL7" ca="1">_xll.YCP($B7,DL$2)</f>
-        <v>0.60178540999999997</v>
+        <v>0.60083226999999995</v>
       </c>
       <c r="DM7" s="4" cm="1">
         <f t="array" aca="1" ref="DM7" ca="1">_xll.YCP($B7,DM$2)</f>
-        <v>0.19483579000000001</v>
+        <v>0.19636745</v>
       </c>
       <c r="DN7" s="4" cm="1">
         <f t="array" aca="1" ref="DN7" ca="1">_xll.YCP($B7,DN$2)</f>
-        <v>0.18916508000000001</v>
+        <v>0.18835283</v>
       </c>
       <c r="DO7" s="4" cm="1">
         <f t="array" aca="1" ref="DO7" ca="1">_xll.YCP($B7,DO$2)</f>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="DR7" s="4" cm="1">
         <f t="array" aca="1" ref="DR7" ca="1">_xll.YCP($B7,DR$2)</f>
-        <v>0.95970648000000003</v>
+        <v>0.95650489000000005</v>
       </c>
     </row>
     <row r="8" spans="2:122" x14ac:dyDescent="0.45">
@@ -4314,11 +4314,11 @@
       </c>
       <c r="H9" s="4" cm="1">
         <f t="array" aca="1" ref="H9" ca="1">_xll.YCP($B9,H$2)</f>
-        <v>4.3265899999999999E-3</v>
+        <v>4.3284700000000001E-3</v>
       </c>
       <c r="I9" s="4" cm="1">
         <f t="array" aca="1" ref="I9" ca="1">_xll.YCP($B9,I$2)</f>
-        <v>3.2148999999999997E-2</v>
+        <v>3.2361000000000001E-2</v>
       </c>
       <c r="J9" s="5" cm="1">
         <f t="array" aca="1" ref="J9" ca="1">_xll.YCP($B9,J$2)</f>
@@ -4326,23 +4326,23 @@
       </c>
       <c r="K9" s="4" cm="1">
         <f t="array" aca="1" ref="K9" ca="1">_xll.YCP($B9,K$2)</f>
-        <v>1.00381886</v>
+        <v>0.98537768000000003</v>
       </c>
       <c r="L9" s="4" cm="1">
         <f t="array" aca="1" ref="L9" ca="1">_xll.YCP($B9,L$2)</f>
-        <v>6.783E-3</v>
+        <v>-6.7260000000000002E-3</v>
       </c>
       <c r="M9" s="4" cm="1">
         <f t="array" aca="1" ref="M9" ca="1">_xll.YCP($B9,M$2)</f>
-        <v>2.5949E-2</v>
+        <v>8.4019999999999997E-3</v>
       </c>
       <c r="N9" s="4" cm="1">
         <f t="array" aca="1" ref="N9" ca="1">_xll.YCP($B9,N$2)</f>
-        <v>3.7701999999999999E-2</v>
+        <v>3.3563000000000003E-2</v>
       </c>
       <c r="O9" s="4" cm="1">
         <f t="array" aca="1" ref="O9" ca="1">_xll.YCP($B9,O$2)</f>
-        <v>8.1069000000000002E-2</v>
+        <v>7.2460999999999998E-2</v>
       </c>
       <c r="P9" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P9" ca="1">_xll.YCP($B9,P$2)</f>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="R9" s="4" cm="1">
         <f t="array" aca="1" ref="R9" ca="1">_xll.YCP($B9,R$2)</f>
-        <v>6.9648000000000002E-2</v>
+        <v>6.5818000000000002E-2</v>
       </c>
       <c r="S9" s="3" cm="1">
         <f t="array" aca="1" ref="S9" ca="1">_xll.YCP($B9,S$2)</f>
@@ -4498,279 +4498,279 @@
       </c>
       <c r="BB9" s="4" cm="1">
         <f t="array" aca="1" ref="BB9" ca="1">_xll.YCP($B9,BB$2)</f>
-        <v>0.86730439000000004</v>
+        <v>0.86664377000000004</v>
       </c>
       <c r="BC9" s="4" cm="1">
         <f t="array" aca="1" ref="BC9" ca="1">_xll.YCP($B9,BC$2)</f>
-        <v>7.3674099999999996E-3</v>
+        <v>7.4351599999999997E-3</v>
       </c>
       <c r="BD9" s="4" cm="1">
         <f t="array" aca="1" ref="BD9" ca="1">_xll.YCP($B9,BD$2)</f>
-        <v>2.3881119999999999E-2</v>
+        <v>2.3914999999999999E-2</v>
       </c>
       <c r="BE9" s="4" cm="1">
         <f t="array" aca="1" ref="BE9" ca="1">_xll.YCP($B9,BE$2)</f>
-        <v>4.6615049999999998E-2</v>
+        <v>4.6542500000000001E-2</v>
       </c>
       <c r="BF9" s="4" cm="1">
         <f t="array" aca="1" ref="BF9" ca="1">_xll.YCP($B9,BF$2)</f>
-        <v>3.6413E-4</v>
+        <v>3.6036E-4</v>
       </c>
       <c r="BG9" s="4" cm="1">
         <f t="array" aca="1" ref="BG9" ca="1">_xll.YCP($B9,BG$2)</f>
-        <v>1.83059E-3</v>
+        <v>1.89737E-3</v>
       </c>
       <c r="BH9" s="4" cm="1">
         <f t="array" aca="1" ref="BH9" ca="1">_xll.YCP($B9,BH$2)</f>
-        <v>1.4514229999999999E-2</v>
+        <v>1.389554E-2</v>
       </c>
       <c r="BI9" s="4" cm="1">
         <f t="array" aca="1" ref="BI9" ca="1">_xll.YCP($B9,BI$2)</f>
-        <v>6.3973700000000003E-3</v>
+        <v>6.2776000000000004E-3</v>
       </c>
       <c r="BJ9" s="4" cm="1">
         <f t="array" aca="1" ref="BJ9" ca="1">_xll.YCP($B9,BJ$2)</f>
-        <v>0.20585540999999999</v>
+        <v>0.23141254</v>
       </c>
       <c r="BK9" s="4" cm="1">
         <f t="array" aca="1" ref="BK9" ca="1">_xll.YCP($B9,BK$2)</f>
-        <v>0.30773584999999998</v>
+        <v>0.27908843999999999</v>
       </c>
       <c r="BL9" s="4" cm="1">
         <f t="array" aca="1" ref="BL9" ca="1">_xll.YCP($B9,BL$2)</f>
-        <v>0.22018989999999999</v>
+        <v>0.21920582</v>
       </c>
       <c r="BM9" s="4" cm="1">
         <f t="array" aca="1" ref="BM9" ca="1">_xll.YCP($B9,BM$2)</f>
-        <v>5.9379550000000003E-2</v>
+        <v>5.9372660000000001E-2</v>
       </c>
       <c r="BN9" s="4" cm="1">
         <f t="array" aca="1" ref="BN9" ca="1">_xll.YCP($B9,BN$2)</f>
-        <v>7.8438900000000006E-2</v>
+        <v>8.3919229999999997E-2</v>
       </c>
       <c r="BO9" s="4" cm="1">
         <f t="array" aca="1" ref="BO9" ca="1">_xll.YCP($B9,BO$2)</f>
-        <v>6.0426840000000002E-2</v>
+        <v>5.5320929999999997E-2</v>
       </c>
       <c r="BP9" s="4" cm="1">
         <f t="array" aca="1" ref="BP9" ca="1">_xll.YCP($B9,BP$2)</f>
-        <v>1.531684E-2</v>
+        <v>1.235845E-2</v>
       </c>
       <c r="BQ9" s="4" cm="1">
         <f t="array" aca="1" ref="BQ9" ca="1">_xll.YCP($B9,BQ$2)</f>
-        <v>3.0898749999999999E-2</v>
+        <v>3.6853230000000001E-2</v>
       </c>
       <c r="BR9" s="4" cm="1">
         <f t="array" aca="1" ref="BR9" ca="1">_xll.YCP($B9,BR$2)</f>
-        <v>2.1757970000000001E-2</v>
+        <v>2.2468700000000001E-2</v>
       </c>
       <c r="BS9" s="4" cm="1">
         <f t="array" aca="1" ref="BS9" ca="1">_xll.YCP($B9,BS$2)</f>
-        <v>2.807898E-2</v>
+        <v>2.8932490000000002E-2</v>
       </c>
       <c r="BT9" s="4" cm="1">
         <f t="array" aca="1" ref="BT9" ca="1">_xll.YCP($B9,BT$2)</f>
-        <v>8.400138E-2</v>
+        <v>8.2086599999999996E-2</v>
       </c>
       <c r="BU9" s="4" cm="1">
         <f t="array" aca="1" ref="BU9" ca="1">_xll.YCP($B9,BU$2)</f>
-        <v>9.4478699999999999E-2</v>
+        <v>9.3682169999999995E-2</v>
       </c>
       <c r="BV9" s="4" cm="1">
         <f t="array" aca="1" ref="BV9" ca="1">_xll.YCP($B9,BV$2)</f>
-        <v>4.3907429999999997E-2</v>
+        <v>4.3856359999999997E-2</v>
       </c>
       <c r="BW9" s="4" cm="1">
         <f t="array" aca="1" ref="BW9" ca="1">_xll.YCP($B9,BW$2)</f>
-        <v>6.9088060000000007E-2</v>
+        <v>6.9293869999999994E-2</v>
       </c>
       <c r="BX9" s="4" cm="1">
         <f t="array" aca="1" ref="BX9" ca="1">_xll.YCP($B9,BX$2)</f>
-        <v>0.13125212999999999</v>
+        <v>0.13407357</v>
       </c>
       <c r="BY9" s="4" cm="1">
         <f t="array" aca="1" ref="BY9" ca="1">_xll.YCP($B9,BY$2)</f>
-        <v>8.1421170000000001E-2</v>
+        <v>8.4049170000000006E-2</v>
       </c>
       <c r="BZ9" s="4" cm="1">
         <f t="array" aca="1" ref="BZ9" ca="1">_xll.YCP($B9,BZ$2)</f>
-        <v>0.12761330000000001</v>
+        <v>0.13002037999999999</v>
       </c>
       <c r="CA9" s="4" cm="1">
         <f t="array" aca="1" ref="CA9" ca="1">_xll.YCP($B9,CA$2)</f>
-        <v>1.744387E-2</v>
+        <v>1.7519340000000001E-2</v>
       </c>
       <c r="CB9" s="4" cm="1">
         <f t="array" aca="1" ref="CB9" ca="1">_xll.YCP($B9,CB$2)</f>
-        <v>0.28952149999999999</v>
+        <v>0.28330071000000001</v>
       </c>
       <c r="CC9" s="4" cm="1">
         <f t="array" aca="1" ref="CC9" ca="1">_xll.YCP($B9,CC$2)</f>
-        <v>1.5191680000000001E-2</v>
+        <v>1.5321069999999999E-2</v>
       </c>
       <c r="CD9" s="4" cm="1">
         <f t="array" aca="1" ref="CD9" ca="1">_xll.YCP($B9,CD$2)</f>
-        <v>-1.2639030000000001E-2</v>
+        <v>-1.6922429999999999E-2</v>
       </c>
       <c r="CE9" s="4" cm="1">
         <f t="array" aca="1" ref="CE9" ca="1">_xll.YCP($B9,CE$2)</f>
-        <v>0.33891921000000003</v>
+        <v>0.33968271999999999</v>
       </c>
       <c r="CF9" s="4" cm="1">
         <f t="array" aca="1" ref="CF9" ca="1">_xll.YCP($B9,CF$2)</f>
-        <v>0.66864142000000004</v>
+        <v>0.66808780999999995</v>
       </c>
       <c r="CG9" s="4" cm="1">
         <f t="array" aca="1" ref="CG9" ca="1">_xll.YCP($B9,CG$2)</f>
-        <v>1.0428E-3</v>
+        <v>1.03122E-3</v>
       </c>
       <c r="CH9" s="4" cm="1">
         <f t="array" aca="1" ref="CH9" ca="1">_xll.YCP($B9,CH$2)</f>
-        <v>3.6059400000000002E-3</v>
+        <v>3.56844E-3</v>
       </c>
       <c r="CI9" s="4" cm="1">
         <f t="array" aca="1" ref="CI9" ca="1">_xll.YCP($B9,CI$2)</f>
-        <v>4.2959999999999998E-4</v>
+        <v>4.5521499999999996E-3</v>
       </c>
       <c r="CJ9" s="4" cm="1">
         <f t="array" aca="1" ref="CJ9" ca="1">_xll.YCP($B9,CJ$2)</f>
-        <v>7.2264819999999994E-2</v>
+        <v>7.2215150000000006E-2</v>
       </c>
       <c r="CK9" s="4" cm="1">
         <f t="array" aca="1" ref="CK9" ca="1">_xll.YCP($B9,CK$2)</f>
-        <v>0.40056422000000003</v>
+        <v>0.39726877999999999</v>
       </c>
       <c r="CL9" s="4" cm="1">
         <f t="array" aca="1" ref="CL9" ca="1">_xll.YCP($B9,CL$2)</f>
-        <v>0.10300642</v>
+        <v>0.10480984</v>
       </c>
       <c r="CM9" s="4" cm="1">
         <f t="array" aca="1" ref="CM9" ca="1">_xll.YCP($B9,CM$2)</f>
-        <v>0.18625048999999999</v>
+        <v>0.18710861000000001</v>
       </c>
       <c r="CN9" s="4" cm="1">
         <f t="array" aca="1" ref="CN9" ca="1">_xll.YCP($B9,CN$2)</f>
-        <v>3.3205800000000001E-2</v>
+        <v>3.2827429999999998E-2</v>
       </c>
       <c r="CO9" s="4" cm="1">
         <f t="array" aca="1" ref="CO9" ca="1">_xll.YCP($B9,CO$2)</f>
-        <v>2.6872610000000002E-2</v>
+        <v>2.652676E-2</v>
       </c>
       <c r="CP9" s="4" cm="1">
         <f t="array" aca="1" ref="CP9" ca="1">_xll.YCP($B9,CP$2)</f>
-        <v>6.2618200000000004E-3</v>
+        <v>6.1892300000000004E-3</v>
       </c>
       <c r="CQ9" s="4" cm="1">
         <f t="array" aca="1" ref="CQ9" ca="1">_xll.YCP($B9,CQ$2)</f>
-        <v>4.6364420000000003E-2</v>
+        <v>4.6858980000000001E-2</v>
       </c>
       <c r="CR9" s="4" cm="1">
         <f t="array" aca="1" ref="CR9" ca="1">_xll.YCP($B9,CR$2)</f>
-        <v>0.17794094999999999</v>
+        <v>0.17520458</v>
       </c>
       <c r="CS9" s="4" cm="1">
         <f t="array" aca="1" ref="CS9" ca="1">_xll.YCP($B9,CS$2)</f>
-        <v>0.19740152</v>
+        <v>0.18719673000000001</v>
       </c>
       <c r="CT9" s="4" cm="1">
         <f t="array" aca="1" ref="CT9" ca="1">_xll.YCP($B9,CT$2)</f>
-        <v>0.24689407999999999</v>
+        <v>0.24787815999999999</v>
       </c>
       <c r="CU9" s="4" cm="1">
         <f t="array" aca="1" ref="CU9" ca="1">_xll.YCP($B9,CU$2)</f>
-        <v>0.10979427999999999</v>
+        <v>0.10983803</v>
       </c>
       <c r="CV9" s="4" cm="1">
         <f t="array" aca="1" ref="CV9" ca="1">_xll.YCP($B9,CV$2)</f>
-        <v>0.18453027999999999</v>
+        <v>0.18441281000000001</v>
       </c>
       <c r="CW9" s="4" cm="1">
         <f t="array" aca="1" ref="CW9" ca="1">_xll.YCP($B9,CW$2)</f>
-        <v>5.8170060000000003E-2</v>
+        <v>7.4369790000000005E-2</v>
       </c>
       <c r="CX9" s="3" cm="1">
         <f t="array" aca="1" ref="CX9" ca="1">_xll.YCP($B9,CX$2)</f>
-        <v>4.9363590000000004</v>
+        <v>4.9383150000000002</v>
       </c>
       <c r="CY9" s="20" cm="1">
         <f t="array" aca="1" ref="CY9" ca="1">_xll.YCP($B9,CY$2)</f>
-        <v>6.0981139999999998</v>
+        <v>6.0366540000000004</v>
       </c>
       <c r="CZ9" s="4" cm="1">
         <f t="array" aca="1" ref="CZ9" ca="1">_xll.YCP($B9,CZ$2)</f>
-        <v>4.971478E-2</v>
+        <v>5.4293399999999999E-2</v>
       </c>
       <c r="DA9" s="4" cm="1">
         <f t="array" aca="1" ref="DA9" ca="1">_xll.YCP($B9,DA$2)</f>
-        <v>4.5562569999999997E-2</v>
+        <v>4.5802750000000003E-2</v>
       </c>
       <c r="DB9" s="4" cm="1">
         <f t="array" aca="1" ref="DB9" ca="1">_xll.YCP($B9,DB$2)</f>
-        <v>4.3923799999999999E-2</v>
+        <v>4.4072739999999999E-2</v>
       </c>
       <c r="DC9" s="4" cm="1">
         <f t="array" aca="1" ref="DC9" ca="1">_xll.YCP($B9,DC$2)</f>
-        <v>0.36734601</v>
+        <v>0.36442335999999997</v>
       </c>
       <c r="DD9" s="4" cm="1">
         <f t="array" aca="1" ref="DD9" ca="1">_xll.YCP($B9,DD$2)</f>
-        <v>0.37564846000000002</v>
+        <v>0.37772170999999999</v>
       </c>
       <c r="DE9" s="4" cm="1">
         <f t="array" aca="1" ref="DE9" ca="1">_xll.YCP($B9,DE$2)</f>
-        <v>0.24039314000000001</v>
+        <v>0.24142858</v>
       </c>
       <c r="DF9" s="4" cm="1">
         <f t="array" aca="1" ref="DF9" ca="1">_xll.YCP($B9,DF$2)</f>
-        <v>6.1951200000000001E-3</v>
+        <v>6.1008900000000003E-3</v>
       </c>
       <c r="DG9" s="4" cm="1">
         <f t="array" aca="1" ref="DG9" ca="1">_xll.YCP($B9,DG$2)</f>
-        <v>1.0417269999999999E-2</v>
+        <v>1.032546E-2</v>
       </c>
       <c r="DH9" s="4" cm="1">
         <f t="array" aca="1" ref="DH9" ca="1">_xll.YCP($B9,DH$2)</f>
-        <v>0.33908215000000003</v>
+        <v>0.33984593000000002</v>
       </c>
       <c r="DI9" s="4" cm="1">
         <f t="array" aca="1" ref="DI9" ca="1">_xll.YCP($B9,DI$2)</f>
-        <v>0.73383648000000001</v>
+        <v>0.73316970999999997</v>
       </c>
       <c r="DJ9" s="4" cm="1">
         <f t="array" aca="1" ref="DJ9" ca="1">_xll.YCP($B9,DJ$2)</f>
-        <v>-1.2639030000000001E-2</v>
+        <v>-1.6922429999999999E-2</v>
       </c>
       <c r="DK9" s="4" cm="1">
         <f t="array" aca="1" ref="DK9" ca="1">_xll.YCP($B9,DK$2)</f>
-        <v>1.9999380000000001E-2</v>
+        <v>2.0287779999999998E-2</v>
       </c>
       <c r="DL9" s="4" cm="1">
         <f t="array" aca="1" ref="DL9" ca="1">_xll.YCP($B9,DL$2)</f>
-        <v>0.25283503000000002</v>
+        <v>0.25204913000000001</v>
       </c>
       <c r="DM9" s="4" cm="1">
         <f t="array" aca="1" ref="DM9" ca="1">_xll.YCP($B9,DM$2)</f>
-        <v>4.9980749999999997E-2</v>
+        <v>5.0221290000000002E-2</v>
       </c>
       <c r="DN9" s="4" cm="1">
         <f t="array" aca="1" ref="DN9" ca="1">_xll.YCP($B9,DN$2)</f>
-        <v>3.4289649999999998E-2</v>
+        <v>3.5221830000000003E-2</v>
       </c>
       <c r="DO9" s="4" cm="1">
         <f t="array" aca="1" ref="DO9" ca="1">_xll.YCP($B9,DO$2)</f>
-        <v>0.47305691</v>
+        <v>0.47284471</v>
       </c>
       <c r="DP9" s="4" cm="1">
         <f t="array" aca="1" ref="DP9" ca="1">_xll.YCP($B9,DP$2)</f>
-        <v>4.1180010000000003E-2</v>
+        <v>4.0703650000000001E-2</v>
       </c>
       <c r="DQ9" s="4" cm="1">
         <f t="array" aca="1" ref="DQ9" ca="1">_xll.YCP($B9,DQ$2)</f>
-        <v>1.081534E-2</v>
+        <v>1.071919E-2</v>
       </c>
       <c r="DR9" s="4" cm="1">
         <f t="array" aca="1" ref="DR9" ca="1">_xll.YCP($B9,DR$2)</f>
-        <v>0.98000061999999999</v>
+        <v>0.97971222000000002</v>
       </c>
     </row>
     <row r="10" spans="2:122" x14ac:dyDescent="0.45">
@@ -4799,11 +4799,11 @@
       </c>
       <c r="H10" s="4" cm="1">
         <f t="array" aca="1" ref="H10" ca="1">_xll.YCP($B10,H$2)</f>
-        <v>4.8802100000000003E-3</v>
+        <v>4.8798399999999999E-3</v>
       </c>
       <c r="I10" s="4" cm="1">
         <f t="array" aca="1" ref="I10" ca="1">_xll.YCP($B10,I$2)</f>
-        <v>2.6106000000000001E-2</v>
+        <v>2.6373000000000001E-2</v>
       </c>
       <c r="J10" s="5" cm="1">
         <f t="array" aca="1" ref="J10" ca="1">_xll.YCP($B10,J$2)</f>
@@ -4811,23 +4811,23 @@
       </c>
       <c r="K10" s="4" cm="1">
         <f t="array" aca="1" ref="K10" ca="1">_xll.YCP($B10,K$2)</f>
-        <v>0.90577932000000005</v>
+        <v>0.89032597999999996</v>
       </c>
       <c r="L10" s="4" cm="1">
         <f t="array" aca="1" ref="L10" ca="1">_xll.YCP($B10,L$2)</f>
-        <v>1.1558000000000001E-2</v>
+        <v>-1.2519000000000001E-2</v>
       </c>
       <c r="M10" s="4" cm="1">
         <f t="array" aca="1" ref="M10" ca="1">_xll.YCP($B10,M$2)</f>
-        <v>4.5470999999999998E-2</v>
+        <v>1.7163999999999999E-2</v>
       </c>
       <c r="N10" s="4" cm="1">
         <f t="array" aca="1" ref="N10" ca="1">_xll.YCP($B10,N$2)</f>
-        <v>6.5490000000000007E-2</v>
+        <v>5.8384999999999999E-2</v>
       </c>
       <c r="O10" s="4" cm="1">
         <f t="array" aca="1" ref="O10" ca="1">_xll.YCP($B10,O$2)</f>
-        <v>0.118575</v>
+        <v>0.10587299999999999</v>
       </c>
       <c r="P10" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P10" ca="1">_xll.YCP($B10,P$2)</f>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="R10" s="4" cm="1">
         <f t="array" aca="1" ref="R10" ca="1">_xll.YCP($B10,R$2)</f>
-        <v>9.2211000000000001E-2</v>
+        <v>8.6371000000000003E-2</v>
       </c>
       <c r="S10" s="3" cm="1">
         <f t="array" aca="1" ref="S10" ca="1">_xll.YCP($B10,S$2)</f>
@@ -4983,279 +4983,279 @@
       </c>
       <c r="BB10" s="4" cm="1">
         <f t="array" aca="1" ref="BB10" ca="1">_xll.YCP($B10,BB$2)</f>
-        <v>0.81792332000000001</v>
+        <v>0.81774853000000003</v>
       </c>
       <c r="BC10" s="4" cm="1">
         <f t="array" aca="1" ref="BC10" ca="1">_xll.YCP($B10,BC$2)</f>
-        <v>9.5964499999999994E-3</v>
+        <v>9.5309599999999998E-3</v>
       </c>
       <c r="BD10" s="4" cm="1">
         <f t="array" aca="1" ref="BD10" ca="1">_xll.YCP($B10,BD$2)</f>
-        <v>2.8723220000000001E-2</v>
+        <v>2.863777E-2</v>
       </c>
       <c r="BE10" s="4" cm="1">
         <f t="array" aca="1" ref="BE10" ca="1">_xll.YCP($B10,BE$2)</f>
-        <v>6.0723699999999999E-2</v>
+        <v>6.1012619999999997E-2</v>
       </c>
       <c r="BF10" s="4" cm="1">
         <f t="array" aca="1" ref="BF10" ca="1">_xll.YCP($B10,BF$2)</f>
-        <v>5.6609E-4</v>
+        <v>5.5986000000000002E-4</v>
       </c>
       <c r="BG10" s="4" cm="1">
         <f t="array" aca="1" ref="BG10" ca="1">_xll.YCP($B10,BG$2)</f>
-        <v>2.73457E-3</v>
+        <v>2.89324E-3</v>
       </c>
       <c r="BH10" s="4" cm="1">
         <f t="array" aca="1" ref="BH10" ca="1">_xll.YCP($B10,BH$2)</f>
-        <v>2.6659240000000001E-2</v>
+        <v>2.5316910000000001E-2</v>
       </c>
       <c r="BI10" s="4" cm="1">
         <f t="array" aca="1" ref="BI10" ca="1">_xll.YCP($B10,BI$2)</f>
-        <v>1.4747959999999999E-2</v>
+        <v>1.4578870000000001E-2</v>
       </c>
       <c r="BJ10" s="4" cm="1">
         <f t="array" aca="1" ref="BJ10" ca="1">_xll.YCP($B10,BJ$2)</f>
-        <v>0.22075056000000001</v>
+        <v>0.23558064000000001</v>
       </c>
       <c r="BK10" s="4" cm="1">
         <f t="array" aca="1" ref="BK10" ca="1">_xll.YCP($B10,BK$2)</f>
-        <v>0.26967591000000002</v>
+        <v>0.25637374000000002</v>
       </c>
       <c r="BL10" s="4" cm="1">
         <f t="array" aca="1" ref="BL10" ca="1">_xll.YCP($B10,BL$2)</f>
-        <v>0.21165018999999999</v>
+        <v>0.20404884000000001</v>
       </c>
       <c r="BM10" s="4" cm="1">
         <f t="array" aca="1" ref="BM10" ca="1">_xll.YCP($B10,BM$2)</f>
-        <v>5.8448220000000002E-2</v>
+        <v>5.6935560000000003E-2</v>
       </c>
       <c r="BN10" s="4" cm="1">
         <f t="array" aca="1" ref="BN10" ca="1">_xll.YCP($B10,BN$2)</f>
-        <v>7.5685970000000005E-2</v>
+        <v>8.6156140000000006E-2</v>
       </c>
       <c r="BO10" s="4" cm="1">
         <f t="array" aca="1" ref="BO10" ca="1">_xll.YCP($B10,BO$2)</f>
-        <v>6.6757990000000003E-2</v>
+        <v>6.0851080000000002E-2</v>
       </c>
       <c r="BP10" s="4" cm="1">
         <f t="array" aca="1" ref="BP10" ca="1">_xll.YCP($B10,BP$2)</f>
-        <v>2.5633199999999998E-2</v>
+        <v>2.140421E-2</v>
       </c>
       <c r="BQ10" s="4" cm="1">
         <f t="array" aca="1" ref="BQ10" ca="1">_xll.YCP($B10,BQ$2)</f>
-        <v>3.9013760000000001E-2</v>
+        <v>4.6075489999999997E-2</v>
       </c>
       <c r="BR10" s="4" cm="1">
         <f t="array" aca="1" ref="BR10" ca="1">_xll.YCP($B10,BR$2)</f>
-        <v>3.238419E-2</v>
+        <v>3.2574289999999999E-2</v>
       </c>
       <c r="BS10" s="4" cm="1">
         <f t="array" aca="1" ref="BS10" ca="1">_xll.YCP($B10,BS$2)</f>
-        <v>3.1153819999999999E-2</v>
+        <v>3.1814250000000002E-2</v>
       </c>
       <c r="BT10" s="4" cm="1">
         <f t="array" aca="1" ref="BT10" ca="1">_xll.YCP($B10,BT$2)</f>
-        <v>6.5873429999999997E-2</v>
+        <v>6.4640349999999999E-2</v>
       </c>
       <c r="BU10" s="4" cm="1">
         <f t="array" aca="1" ref="BU10" ca="1">_xll.YCP($B10,BU$2)</f>
-        <v>8.8748300000000002E-2</v>
+        <v>8.8837899999999997E-2</v>
       </c>
       <c r="BV10" s="4" cm="1">
         <f t="array" aca="1" ref="BV10" ca="1">_xll.YCP($B10,BV$2)</f>
-        <v>5.1080880000000002E-2</v>
+        <v>5.1533210000000003E-2</v>
       </c>
       <c r="BW10" s="4" cm="1">
         <f t="array" aca="1" ref="BW10" ca="1">_xll.YCP($B10,BW$2)</f>
-        <v>7.1593390000000007E-2</v>
+        <v>7.2509270000000001E-2</v>
       </c>
       <c r="BX10" s="4" cm="1">
         <f t="array" aca="1" ref="BX10" ca="1">_xll.YCP($B10,BX$2)</f>
-        <v>0.13907428999999999</v>
+        <v>0.14326686999999999</v>
       </c>
       <c r="BY10" s="4" cm="1">
         <f t="array" aca="1" ref="BY10" ca="1">_xll.YCP($B10,BY$2)</f>
-        <v>7.5608170000000002E-2</v>
+        <v>7.8960610000000001E-2</v>
       </c>
       <c r="BZ10" s="4" cm="1">
         <f t="array" aca="1" ref="BZ10" ca="1">_xll.YCP($B10,BZ$2)</f>
-        <v>0.12902101999999999</v>
+        <v>0.1300656</v>
       </c>
       <c r="CA10" s="4" cm="1">
         <f t="array" aca="1" ref="CA10" ca="1">_xll.YCP($B10,CA$2)</f>
-        <v>1.5573119999999999E-2</v>
+        <v>1.5683929999999999E-2</v>
       </c>
       <c r="CB10" s="4" cm="1">
         <f t="array" aca="1" ref="CB10" ca="1">_xll.YCP($B10,CB$2)</f>
-        <v>0.29733933000000001</v>
+        <v>0.28832256000000001</v>
       </c>
       <c r="CC10" s="4" cm="1">
         <f t="array" aca="1" ref="CC10" ca="1">_xll.YCP($B10,CC$2)</f>
-        <v>2.291048E-2</v>
+        <v>2.2833010000000001E-2</v>
       </c>
       <c r="CD10" s="4" cm="1">
         <f t="array" aca="1" ref="CD10" ca="1">_xll.YCP($B10,CD$2)</f>
-        <v>-7.4111799999999999E-3</v>
+        <v>-1.090026E-2</v>
       </c>
       <c r="CE10" s="4" cm="1">
         <f t="array" aca="1" ref="CE10" ca="1">_xll.YCP($B10,CE$2)</f>
-        <v>0.51933801000000002</v>
+        <v>0.51927201000000001</v>
       </c>
       <c r="CF10" s="4" cm="1">
         <f t="array" aca="1" ref="CF10" ca="1">_xll.YCP($B10,CF$2)</f>
-        <v>0.48391108999999999</v>
+        <v>0.48470592000000001</v>
       </c>
       <c r="CG10" s="4" cm="1">
         <f t="array" aca="1" ref="CG10" ca="1">_xll.YCP($B10,CG$2)</f>
-        <v>8.3668000000000002E-4</v>
+        <v>8.2950000000000005E-4</v>
       </c>
       <c r="CH10" s="4" cm="1">
         <f t="array" aca="1" ref="CH10" ca="1">_xll.YCP($B10,CH$2)</f>
-        <v>2.9462099999999999E-3</v>
+        <v>2.9230800000000002E-3</v>
       </c>
       <c r="CI10" s="4" cm="1">
         <f t="array" aca="1" ref="CI10" ca="1">_xll.YCP($B10,CI$2)</f>
-        <v>3.7914999999999997E-4</v>
+        <v>3.1697000000000001E-3</v>
       </c>
       <c r="CJ10" s="4" cm="1">
         <f t="array" aca="1" ref="CJ10" ca="1">_xll.YCP($B10,CJ$2)</f>
-        <v>7.2307049999999998E-2</v>
+        <v>7.2271230000000006E-2</v>
       </c>
       <c r="CK10" s="4" cm="1">
         <f t="array" aca="1" ref="CK10" ca="1">_xll.YCP($B10,CK$2)</f>
-        <v>0.39497199999999999</v>
+        <v>0.39184608999999998</v>
       </c>
       <c r="CL10" s="4" cm="1">
         <f t="array" aca="1" ref="CL10" ca="1">_xll.YCP($B10,CL$2)</f>
-        <v>0.10253755000000001</v>
+        <v>0.10431243</v>
       </c>
       <c r="CM10" s="4" cm="1">
         <f t="array" aca="1" ref="CM10" ca="1">_xll.YCP($B10,CM$2)</f>
-        <v>0.18352347999999999</v>
+        <v>0.18438157999999999</v>
       </c>
       <c r="CN10" s="4" cm="1">
         <f t="array" aca="1" ref="CN10" ca="1">_xll.YCP($B10,CN$2)</f>
-        <v>3.8017670000000003E-2</v>
+        <v>3.7593550000000003E-2</v>
       </c>
       <c r="CO10" s="4" cm="1">
         <f t="array" aca="1" ref="CO10" ca="1">_xll.YCP($B10,CO$2)</f>
-        <v>3.1339470000000001E-2</v>
+        <v>3.094328E-2</v>
       </c>
       <c r="CP10" s="4" cm="1">
         <f t="array" aca="1" ref="CP10" ca="1">_xll.YCP($B10,CP$2)</f>
-        <v>7.4684699999999996E-3</v>
+        <v>7.3850499999999998E-3</v>
       </c>
       <c r="CQ10" s="4" cm="1">
         <f t="array" aca="1" ref="CQ10" ca="1">_xll.YCP($B10,CQ$2)</f>
-        <v>4.9504769999999997E-2</v>
+        <v>4.9958469999999998E-2</v>
       </c>
       <c r="CR10" s="4" cm="1">
         <f t="array" aca="1" ref="CR10" ca="1">_xll.YCP($B10,CR$2)</f>
-        <v>0.18115621000000001</v>
+        <v>0.17856486999999999</v>
       </c>
       <c r="CS10" s="4" cm="1">
         <f t="array" aca="1" ref="CS10" ca="1">_xll.YCP($B10,CS$2)</f>
-        <v>0.20036105000000001</v>
+        <v>0.19063986999999999</v>
       </c>
       <c r="CT10" s="4" cm="1">
         <f t="array" aca="1" ref="CT10" ca="1">_xll.YCP($B10,CT$2)</f>
-        <v>0.24647972000000001</v>
+        <v>0.24743944000000001</v>
       </c>
       <c r="CU10" s="4" cm="1">
         <f t="array" aca="1" ref="CU10" ca="1">_xll.YCP($B10,CU$2)</f>
-        <v>0.10708432</v>
+        <v>0.10714990000000001</v>
       </c>
       <c r="CV10" s="4" cm="1">
         <f t="array" aca="1" ref="CV10" ca="1">_xll.YCP($B10,CV$2)</f>
-        <v>0.17940160999999999</v>
+        <v>0.17932836999999999</v>
       </c>
       <c r="CW10" s="4" cm="1">
         <f t="array" aca="1" ref="CW10" ca="1">_xll.YCP($B10,CW$2)</f>
-        <v>5.7319670000000003E-2</v>
+        <v>7.2666019999999998E-2</v>
       </c>
       <c r="CX10" s="3" cm="1">
         <f t="array" aca="1" ref="CX10" ca="1">_xll.YCP($B10,CX$2)</f>
-        <v>4.8958279999999998</v>
+        <v>4.8973750000000003</v>
       </c>
       <c r="CY10" s="20" cm="1">
         <f t="array" aca="1" ref="CY10" ca="1">_xll.YCP($B10,CY$2)</f>
-        <v>6.0286429999999998</v>
+        <v>5.9716909999999999</v>
       </c>
       <c r="CZ10" s="4" cm="1">
         <f t="array" aca="1" ref="CZ10" ca="1">_xll.YCP($B10,CZ$2)</f>
-        <v>5.0269899999999999E-2</v>
+        <v>5.4507449999999999E-2</v>
       </c>
       <c r="DA10" s="4" cm="1">
         <f t="array" aca="1" ref="DA10" ca="1">_xll.YCP($B10,DA$2)</f>
-        <v>4.5866400000000002E-2</v>
+        <v>4.6097350000000002E-2</v>
       </c>
       <c r="DB10" s="4" cm="1">
         <f t="array" aca="1" ref="DB10" ca="1">_xll.YCP($B10,DB$2)</f>
-        <v>4.4122139999999997E-2</v>
+        <v>4.427292E-2</v>
       </c>
       <c r="DC10" s="4" cm="1">
         <f t="array" aca="1" ref="DC10" ca="1">_xll.YCP($B10,DC$2)</f>
-        <v>0.3681045</v>
+        <v>0.36529785999999997</v>
       </c>
       <c r="DD10" s="4" cm="1">
         <f t="array" aca="1" ref="DD10" ca="1">_xll.YCP($B10,DD$2)</f>
-        <v>0.38110545000000001</v>
+        <v>0.38304504</v>
       </c>
       <c r="DE10" s="4" cm="1">
         <f t="array" aca="1" ref="DE10" ca="1">_xll.YCP($B10,DE$2)</f>
-        <v>0.23322434</v>
+        <v>0.23428299999999999</v>
       </c>
       <c r="DF10" s="4" cm="1">
         <f t="array" aca="1" ref="DF10" ca="1">_xll.YCP($B10,DF$2)</f>
-        <v>5.9778399999999999E-3</v>
+        <v>5.8878100000000003E-3</v>
       </c>
       <c r="DG10" s="4" cm="1">
         <f t="array" aca="1" ref="DG10" ca="1">_xll.YCP($B10,DG$2)</f>
-        <v>1.158786E-2</v>
+        <v>1.14863E-2</v>
       </c>
       <c r="DH10" s="4" cm="1">
         <f t="array" aca="1" ref="DH10" ca="1">_xll.YCP($B10,DH$2)</f>
-        <v>0.51948563000000003</v>
+        <v>0.51942027000000002</v>
       </c>
       <c r="DI10" s="4" cm="1">
         <f t="array" aca="1" ref="DI10" ca="1">_xll.YCP($B10,DI$2)</f>
-        <v>0.54735778000000002</v>
+        <v>0.54821399999999998</v>
       </c>
       <c r="DJ10" s="4" cm="1">
         <f t="array" aca="1" ref="DJ10" ca="1">_xll.YCP($B10,DJ$2)</f>
-        <v>-7.4111799999999999E-3</v>
+        <v>-1.090026E-2</v>
       </c>
       <c r="DK10" s="4" cm="1">
         <f t="array" aca="1" ref="DK10" ca="1">_xll.YCP($B10,DK$2)</f>
-        <v>3.2315860000000002E-2</v>
+        <v>3.2747159999999997E-2</v>
       </c>
       <c r="DL10" s="4" cm="1">
         <f t="array" aca="1" ref="DL10" ca="1">_xll.YCP($B10,DL$2)</f>
-        <v>0.36960986000000001</v>
+        <v>0.36804866000000003</v>
       </c>
       <c r="DM10" s="4" cm="1">
         <f t="array" aca="1" ref="DM10" ca="1">_xll.YCP($B10,DM$2)</f>
-        <v>7.8300410000000001E-2</v>
+        <v>7.8674919999999995E-2</v>
       </c>
       <c r="DN10" s="4" cm="1">
         <f t="array" aca="1" ref="DN10" ca="1">_xll.YCP($B10,DN$2)</f>
-        <v>6.8461739999999993E-2</v>
+        <v>6.9253519999999999E-2</v>
       </c>
       <c r="DO10" s="4" cm="1">
         <f t="array" aca="1" ref="DO10" ca="1">_xll.YCP($B10,DO$2)</f>
-        <v>0.33432767000000002</v>
+        <v>0.33507440999999999</v>
       </c>
       <c r="DP10" s="4" cm="1">
         <f t="array" aca="1" ref="DP10" ca="1">_xll.YCP($B10,DP$2)</f>
-        <v>3.4094729999999997E-2</v>
+        <v>3.3792639999999999E-2</v>
       </c>
       <c r="DQ10" s="4" cm="1">
         <f t="array" aca="1" ref="DQ10" ca="1">_xll.YCP($B10,DQ$2)</f>
-        <v>1.20409E-2</v>
+        <v>1.1934510000000001E-2</v>
       </c>
       <c r="DR10" s="4" cm="1">
         <f t="array" aca="1" ref="DR10" ca="1">_xll.YCP($B10,DR$2)</f>
-        <v>0.96768414000000003</v>
+        <v>0.96725284</v>
       </c>
     </row>
     <row r="11" spans="2:122" x14ac:dyDescent="0.45">
@@ -5284,11 +5284,11 @@
       </c>
       <c r="H11" s="4" cm="1">
         <f t="array" aca="1" ref="H11" ca="1">_xll.YCP($B11,H$2)</f>
-        <v>5.3771799999999996E-3</v>
+        <v>5.37391E-3</v>
       </c>
       <c r="I11" s="4" cm="1">
         <f t="array" aca="1" ref="I11" ca="1">_xll.YCP($B11,I$2)</f>
-        <v>2.0116999999999999E-2</v>
+        <v>2.0400999999999999E-2</v>
       </c>
       <c r="J11" s="5" cm="1">
         <f t="array" aca="1" ref="J11" ca="1">_xll.YCP($B11,J$2)</f>
@@ -5296,23 +5296,23 @@
       </c>
       <c r="K11" s="4" cm="1">
         <f t="array" aca="1" ref="K11" ca="1">_xll.YCP($B11,K$2)</f>
-        <v>0.59648734000000003</v>
+        <v>0.59853778000000002</v>
       </c>
       <c r="L11" s="4" cm="1">
         <f t="array" aca="1" ref="L11" ca="1">_xll.YCP($B11,L$2)</f>
-        <v>1.5344E-2</v>
+        <v>-1.7798000000000001E-2</v>
       </c>
       <c r="M11" s="4" cm="1">
         <f t="array" aca="1" ref="M11" ca="1">_xll.YCP($B11,M$2)</f>
-        <v>6.3818E-2</v>
+        <v>2.2540999999999999E-2</v>
       </c>
       <c r="N11" s="4" cm="1">
         <f t="array" aca="1" ref="N11" ca="1">_xll.YCP($B11,N$2)</f>
-        <v>9.3635999999999997E-2</v>
+        <v>8.2737000000000005E-2</v>
       </c>
       <c r="O11" s="4" cm="1">
         <f t="array" aca="1" ref="O11" ca="1">_xll.YCP($B11,O$2)</f>
-        <v>0.155863</v>
+        <v>0.138013</v>
       </c>
       <c r="P11" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P11" ca="1">_xll.YCP($B11,P$2)</f>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="R11" s="4" cm="1">
         <f t="array" aca="1" ref="R11" ca="1">_xll.YCP($B11,R$2)</f>
-        <v>0.115799</v>
+        <v>0.107532</v>
       </c>
       <c r="S11" s="3" cm="1">
         <f t="array" aca="1" ref="S11" ca="1">_xll.YCP($B11,S$2)</f>
@@ -5468,279 +5468,279 @@
       </c>
       <c r="BB11" s="4" cm="1">
         <f t="array" aca="1" ref="BB11" ca="1">_xll.YCP($B11,BB$2)</f>
-        <v>0.80858768000000003</v>
+        <v>0.80985032999999995</v>
       </c>
       <c r="BC11" s="4" cm="1">
         <f t="array" aca="1" ref="BC11" ca="1">_xll.YCP($B11,BC$2)</f>
-        <v>1.3332170000000001E-2</v>
+        <v>1.1644069999999999E-2</v>
       </c>
       <c r="BD11" s="4" cm="1">
         <f t="array" aca="1" ref="BD11" ca="1">_xll.YCP($B11,BD$2)</f>
-        <v>2.5872570000000001E-2</v>
+        <v>2.56762E-2</v>
       </c>
       <c r="BE11" s="4" cm="1">
         <f t="array" aca="1" ref="BE11" ca="1">_xll.YCP($B11,BE$2)</f>
-        <v>5.4221459999999999E-2</v>
+        <v>5.4107379999999997E-2</v>
       </c>
       <c r="BF11" s="4" cm="1">
         <f t="array" aca="1" ref="BF11" ca="1">_xll.YCP($B11,BF$2)</f>
-        <v>2.1955400000000002E-3</v>
+        <v>2.2080699999999999E-3</v>
       </c>
       <c r="BG11" s="4" cm="1">
         <f t="array" aca="1" ref="BG11" ca="1">_xll.YCP($B11,BG$2)</f>
-        <v>8.5176999999999996E-3</v>
+        <v>7.5191199999999998E-3</v>
       </c>
       <c r="BH11" s="4" cm="1">
         <f t="array" aca="1" ref="BH11" ca="1">_xll.YCP($B11,BH$2)</f>
-        <v>3.2311899999999998E-2</v>
+        <v>3.5609250000000002E-2</v>
       </c>
       <c r="BI11" s="4" cm="1">
         <f t="array" aca="1" ref="BI11" ca="1">_xll.YCP($B11,BI$2)</f>
-        <v>2.2525099999999999E-2</v>
+        <v>1.9309030000000001E-2</v>
       </c>
       <c r="BJ11" s="4" cm="1">
         <f t="array" aca="1" ref="BJ11" ca="1">_xll.YCP($B11,BJ$2)</f>
-        <v>0.20823085999999999</v>
+        <v>0.21996992000000001</v>
       </c>
       <c r="BK11" s="4" cm="1">
         <f t="array" aca="1" ref="BK11" ca="1">_xll.YCP($B11,BK$2)</f>
-        <v>0.25903572000000002</v>
+        <v>0.23980767</v>
       </c>
       <c r="BL11" s="4" cm="1">
         <f t="array" aca="1" ref="BL11" ca="1">_xll.YCP($B11,BL$2)</f>
-        <v>0.20536782000000001</v>
+        <v>0.20975363</v>
       </c>
       <c r="BM11" s="4" cm="1">
         <f t="array" aca="1" ref="BM11" ca="1">_xll.YCP($B11,BM$2)</f>
-        <v>6.4936579999999994E-2</v>
+        <v>6.2021220000000002E-2</v>
       </c>
       <c r="BN11" s="4" cm="1">
         <f t="array" aca="1" ref="BN11" ca="1">_xll.YCP($B11,BN$2)</f>
-        <v>7.6166570000000003E-2</v>
+        <v>8.6223300000000003E-2</v>
       </c>
       <c r="BO11" s="4" cm="1">
         <f t="array" aca="1" ref="BO11" ca="1">_xll.YCP($B11,BO$2)</f>
-        <v>6.9398009999999996E-2</v>
+        <v>6.2734029999999996E-2</v>
       </c>
       <c r="BP11" s="4" cm="1">
         <f t="array" aca="1" ref="BP11" ca="1">_xll.YCP($B11,BP$2)</f>
-        <v>3.00307E-2</v>
+        <v>2.5665830000000001E-2</v>
       </c>
       <c r="BQ11" s="4" cm="1">
         <f t="array" aca="1" ref="BQ11" ca="1">_xll.YCP($B11,BQ$2)</f>
-        <v>4.6796030000000002E-2</v>
+        <v>5.3567549999999999E-2</v>
       </c>
       <c r="BR11" s="4" cm="1">
         <f t="array" aca="1" ref="BR11" ca="1">_xll.YCP($B11,BR$2)</f>
-        <v>4.0037709999999997E-2</v>
+        <v>4.025687E-2</v>
       </c>
       <c r="BS11" s="4" cm="1">
         <f t="array" aca="1" ref="BS11" ca="1">_xll.YCP($B11,BS$2)</f>
-        <v>2.9836350000000001E-2</v>
+        <v>2.9305089999999999E-2</v>
       </c>
       <c r="BT11" s="4" cm="1">
         <f t="array" aca="1" ref="BT11" ca="1">_xll.YCP($B11,BT$2)</f>
-        <v>6.4895659999999994E-2</v>
+        <v>6.2903360000000005E-2</v>
       </c>
       <c r="BU11" s="4" cm="1">
         <f t="array" aca="1" ref="BU11" ca="1">_xll.YCP($B11,BU$2)</f>
-        <v>8.6894570000000004E-2</v>
+        <v>8.6528949999999993E-2</v>
       </c>
       <c r="BV11" s="4" cm="1">
         <f t="array" aca="1" ref="BV11" ca="1">_xll.YCP($B11,BV$2)</f>
-        <v>4.9107730000000002E-2</v>
+        <v>4.924543E-2</v>
       </c>
       <c r="BW11" s="4" cm="1">
         <f t="array" aca="1" ref="BW11" ca="1">_xll.YCP($B11,BW$2)</f>
-        <v>7.370902E-2</v>
+        <v>7.3919890000000002E-2</v>
       </c>
       <c r="BX11" s="4" cm="1">
         <f t="array" aca="1" ref="BX11" ca="1">_xll.YCP($B11,BX$2)</f>
-        <v>0.14200238000000001</v>
+        <v>0.14303542</v>
       </c>
       <c r="BY11" s="4" cm="1">
         <f t="array" aca="1" ref="BY11" ca="1">_xll.YCP($B11,BY$2)</f>
-        <v>7.3402729999999999E-2</v>
+        <v>7.705737E-2</v>
       </c>
       <c r="BZ11" s="4" cm="1">
         <f t="array" aca="1" ref="BZ11" ca="1">_xll.YCP($B11,BZ$2)</f>
-        <v>0.12542329999999999</v>
+        <v>0.12640256</v>
       </c>
       <c r="CA11" s="4" cm="1">
         <f t="array" aca="1" ref="CA11" ca="1">_xll.YCP($B11,CA$2)</f>
-        <v>1.8213900000000002E-2</v>
+        <v>1.7954040000000001E-2</v>
       </c>
       <c r="CB11" s="4" cm="1">
         <f t="array" aca="1" ref="CB11" ca="1">_xll.YCP($B11,CB$2)</f>
-        <v>0.29902834</v>
+        <v>0.29680245</v>
       </c>
       <c r="CC11" s="4" cm="1">
         <f t="array" aca="1" ref="CC11" ca="1">_xll.YCP($B11,CC$2)</f>
-        <v>2.248352E-2</v>
+        <v>2.2267229999999999E-2</v>
       </c>
       <c r="CD11" s="4" cm="1">
         <f t="array" aca="1" ref="CD11" ca="1">_xll.YCP($B11,CD$2)</f>
-        <v>2.8134579999999999E-2</v>
+        <v>2.4581220000000001E-2</v>
       </c>
       <c r="CE11" s="4" cm="1">
         <f t="array" aca="1" ref="CE11" ca="1">_xll.YCP($B11,CE$2)</f>
-        <v>0.67511823000000004</v>
+        <v>0.67554431999999998</v>
       </c>
       <c r="CF11" s="4" cm="1">
         <f t="array" aca="1" ref="CF11" ca="1">_xll.YCP($B11,CF$2)</f>
-        <v>0.29310807</v>
+        <v>0.29458402</v>
       </c>
       <c r="CG11" s="4" cm="1">
         <f t="array" aca="1" ref="CG11" ca="1">_xll.YCP($B11,CG$2)</f>
-        <v>5.5088999999999995E-4</v>
+        <v>5.4799000000000004E-4</v>
       </c>
       <c r="CH11" s="4" cm="1">
         <f t="array" aca="1" ref="CH11" ca="1">_xll.YCP($B11,CH$2)</f>
-        <v>2.5198299999999998E-3</v>
+        <v>2.2507199999999999E-3</v>
       </c>
       <c r="CI11" s="4" cm="1">
         <f t="array" aca="1" ref="CI11" ca="1">_xll.YCP($B11,CI$2)</f>
-        <v>5.6837999999999995E-4</v>
+        <v>2.4916700000000001E-3</v>
       </c>
       <c r="CJ11" s="4" cm="1">
         <f t="array" aca="1" ref="CJ11" ca="1">_xll.YCP($B11,CJ$2)</f>
-        <v>6.8217539999999993E-2</v>
+        <v>6.8184209999999995E-2</v>
       </c>
       <c r="CK11" s="4" cm="1">
         <f t="array" aca="1" ref="CK11" ca="1">_xll.YCP($B11,CK$2)</f>
-        <v>0.40008842</v>
+        <v>0.39655737000000002</v>
       </c>
       <c r="CL11" s="4" cm="1">
         <f t="array" aca="1" ref="CL11" ca="1">_xll.YCP($B11,CL$2)</f>
-        <v>0.10080875</v>
+        <v>0.10277851</v>
       </c>
       <c r="CM11" s="4" cm="1">
         <f t="array" aca="1" ref="CM11" ca="1">_xll.YCP($B11,CM$2)</f>
-        <v>0.19341343999999999</v>
+        <v>0.19433244999999999</v>
       </c>
       <c r="CN11" s="4" cm="1">
         <f t="array" aca="1" ref="CN11" ca="1">_xll.YCP($B11,CN$2)</f>
-        <v>3.5138629999999997E-2</v>
+        <v>3.47014E-2</v>
       </c>
       <c r="CO11" s="4" cm="1">
         <f t="array" aca="1" ref="CO11" ca="1">_xll.YCP($B11,CO$2)</f>
-        <v>3.1414240000000003E-2</v>
+        <v>3.1001910000000001E-2</v>
       </c>
       <c r="CP11" s="4" cm="1">
         <f t="array" aca="1" ref="CP11" ca="1">_xll.YCP($B11,CP$2)</f>
-        <v>6.3569100000000003E-3</v>
+        <v>6.2731499999999999E-3</v>
       </c>
       <c r="CQ11" s="4" cm="1">
         <f t="array" aca="1" ref="CQ11" ca="1">_xll.YCP($B11,CQ$2)</f>
-        <v>4.6972119999999999E-2</v>
+        <v>4.7496410000000003E-2</v>
       </c>
       <c r="CR11" s="4" cm="1">
         <f t="array" aca="1" ref="CR11" ca="1">_xll.YCP($B11,CR$2)</f>
-        <v>0.18072104</v>
+        <v>0.1779366</v>
       </c>
       <c r="CS11" s="4" cm="1">
         <f t="array" aca="1" ref="CS11" ca="1">_xll.YCP($B11,CS$2)</f>
-        <v>0.20030648000000001</v>
+        <v>0.18983420000000001</v>
       </c>
       <c r="CT11" s="4" cm="1">
         <f t="array" aca="1" ref="CT11" ca="1">_xll.YCP($B11,CT$2)</f>
-        <v>0.25251040000000002</v>
+        <v>0.25356044999999999</v>
       </c>
       <c r="CU11" s="4" cm="1">
         <f t="array" aca="1" ref="CU11" ca="1">_xll.YCP($B11,CU$2)</f>
-        <v>0.10746462</v>
+        <v>0.1075243</v>
       </c>
       <c r="CV11" s="4" cm="1">
         <f t="array" aca="1" ref="CV11" ca="1">_xll.YCP($B11,CV$2)</f>
-        <v>0.17817400999999999</v>
+        <v>0.17807739</v>
       </c>
       <c r="CW11" s="4" cm="1">
         <f t="array" aca="1" ref="CW11" ca="1">_xll.YCP($B11,CW$2)</f>
-        <v>5.9108019999999997E-2</v>
+        <v>7.5529819999999998E-2</v>
       </c>
       <c r="CX11" s="3" cm="1">
         <f t="array" aca="1" ref="CX11" ca="1">_xll.YCP($B11,CX$2)</f>
-        <v>4.9964899999999997</v>
+        <v>4.9982490000000004</v>
       </c>
       <c r="CY11" s="20" cm="1">
         <f t="array" aca="1" ref="CY11" ca="1">_xll.YCP($B11,CY$2)</f>
-        <v>6.0734110000000001</v>
+        <v>6.0121180000000001</v>
       </c>
       <c r="CZ11" s="4" cm="1">
         <f t="array" aca="1" ref="CZ11" ca="1">_xll.YCP($B11,CZ$2)</f>
-        <v>4.833908E-2</v>
+        <v>5.3458949999999998E-2</v>
       </c>
       <c r="DA11" s="4" cm="1">
         <f t="array" aca="1" ref="DA11" ca="1">_xll.YCP($B11,DA$2)</f>
-        <v>4.5685740000000002E-2</v>
+        <v>4.5940290000000002E-2</v>
       </c>
       <c r="DB11" s="4" cm="1">
         <f t="array" aca="1" ref="DB11" ca="1">_xll.YCP($B11,DB$2)</f>
-        <v>4.4096700000000003E-2</v>
+        <v>4.4247889999999998E-2</v>
       </c>
       <c r="DC11" s="4" cm="1">
         <f t="array" aca="1" ref="DC11" ca="1">_xll.YCP($B11,DC$2)</f>
-        <v>0.36997465000000002</v>
+        <v>0.36647492999999998</v>
       </c>
       <c r="DD11" s="4" cm="1">
         <f t="array" aca="1" ref="DD11" ca="1">_xll.YCP($B11,DD$2)</f>
-        <v>0.38698296999999998</v>
+        <v>0.38938376000000002</v>
       </c>
       <c r="DE11" s="4" cm="1">
         <f t="array" aca="1" ref="DE11" ca="1">_xll.YCP($B11,DE$2)</f>
-        <v>0.22612492000000001</v>
+        <v>0.22744115000000001</v>
       </c>
       <c r="DF11" s="4" cm="1">
         <f t="array" aca="1" ref="DF11" ca="1">_xll.YCP($B11,DF$2)</f>
-        <v>6.4541399999999997E-3</v>
+        <v>6.3574800000000004E-3</v>
       </c>
       <c r="DG11" s="4" cm="1">
         <f t="array" aca="1" ref="DG11" ca="1">_xll.YCP($B11,DG$2)</f>
-        <v>1.046332E-2</v>
+        <v>1.034269E-2</v>
       </c>
       <c r="DH11" s="4" cm="1">
         <f t="array" aca="1" ref="DH11" ca="1">_xll.YCP($B11,DH$2)</f>
-        <v>0.67527000000000004</v>
+        <v>0.6756974</v>
       </c>
       <c r="DI11" s="4" cm="1">
         <f t="array" aca="1" ref="DI11" ca="1">_xll.YCP($B11,DI$2)</f>
-        <v>0.29343701999999999</v>
+        <v>0.29491245999999999</v>
       </c>
       <c r="DJ11" s="4" cm="1">
         <f t="array" aca="1" ref="DJ11" ca="1">_xll.YCP($B11,DJ$2)</f>
-        <v>2.8134579999999999E-2</v>
+        <v>2.4581220000000001E-2</v>
       </c>
       <c r="DK11" s="4" cm="1">
         <f t="array" aca="1" ref="DK11" ca="1">_xll.YCP($B11,DK$2)</f>
-        <v>5.3969740000000002E-2</v>
+        <v>4.7018530000000003E-2</v>
       </c>
       <c r="DL11" s="4" cm="1">
         <f t="array" aca="1" ref="DL11" ca="1">_xll.YCP($B11,DL$2)</f>
-        <v>0.46236644999999998</v>
+        <v>0.46231059000000002</v>
       </c>
       <c r="DM11" s="4" cm="1">
         <f t="array" aca="1" ref="DM11" ca="1">_xll.YCP($B11,DM$2)</f>
-        <v>0.10185333000000001</v>
+        <v>0.10199539000000001</v>
       </c>
       <c r="DN11" s="4" cm="1">
         <f t="array" aca="1" ref="DN11" ca="1">_xll.YCP($B11,DN$2)</f>
-        <v>0.10709141</v>
+        <v>0.10741172</v>
       </c>
       <c r="DO11" s="4" cm="1">
         <f t="array" aca="1" ref="DO11" ca="1">_xll.YCP($B11,DO$2)</f>
-        <v>0.22118879</v>
+        <v>0.22231983999999999</v>
       </c>
       <c r="DP11" s="4" cm="1">
         <f t="array" aca="1" ref="DP11" ca="1">_xll.YCP($B11,DP$2)</f>
-        <v>2.1149149999999999E-2</v>
+        <v>2.10038E-2</v>
       </c>
       <c r="DQ11" s="4" cm="1">
         <f t="array" aca="1" ref="DQ11" ca="1">_xll.YCP($B11,DQ$2)</f>
-        <v>1.077812E-2</v>
+        <v>1.065345E-2</v>
       </c>
       <c r="DR11" s="4" cm="1">
         <f t="array" aca="1" ref="DR11" ca="1">_xll.YCP($B11,DR$2)</f>
-        <v>0.94603026000000001</v>
+        <v>0.95298147</v>
       </c>
     </row>
     <row r="12" spans="2:122" x14ac:dyDescent="0.45">
@@ -5769,11 +5769,11 @@
       </c>
       <c r="H12" s="4" cm="1">
         <f t="array" aca="1" ref="H12" ca="1">_xll.YCP($B12,H$2)</f>
-        <v>5.5412600000000001E-3</v>
+        <v>5.5433100000000001E-3</v>
       </c>
       <c r="I12" s="4" cm="1">
         <f t="array" aca="1" ref="I12" ca="1">_xll.YCP($B12,I$2)</f>
-        <v>1.5036000000000001E-2</v>
+        <v>1.5269E-2</v>
       </c>
       <c r="J12" s="5" cm="1">
         <f t="array" aca="1" ref="J12" ca="1">_xll.YCP($B12,J$2)</f>
@@ -5781,23 +5781,23 @@
       </c>
       <c r="K12" s="4" cm="1">
         <f t="array" aca="1" ref="K12" ca="1">_xll.YCP($B12,K$2)</f>
-        <v>0.54029517999999999</v>
+        <v>0.54259190999999996</v>
       </c>
       <c r="L12" s="4" cm="1">
         <f t="array" aca="1" ref="L12" ca="1">_xll.YCP($B12,L$2)</f>
-        <v>1.8915999999999999E-2</v>
+        <v>-1.8806E-2</v>
       </c>
       <c r="M12" s="4" cm="1">
         <f t="array" aca="1" ref="M12" ca="1">_xll.YCP($B12,M$2)</f>
-        <v>7.7261999999999997E-2</v>
+        <v>2.8568E-2</v>
       </c>
       <c r="N12" s="4" cm="1">
         <f t="array" aca="1" ref="N12" ca="1">_xll.YCP($B12,N$2)</f>
-        <v>0.115576</v>
+        <v>0.103797</v>
       </c>
       <c r="O12" s="4" cm="1">
         <f t="array" aca="1" ref="O12" ca="1">_xll.YCP($B12,O$2)</f>
-        <v>0.185031</v>
+        <v>0.16578699999999999</v>
       </c>
       <c r="P12" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P12" ca="1">_xll.YCP($B12,P$2)</f>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="R12" s="4" cm="1">
         <f t="array" aca="1" ref="R12" ca="1">_xll.YCP($B12,R$2)</f>
-        <v>0.13039100000000001</v>
+        <v>0.121327</v>
       </c>
       <c r="S12" s="3" cm="1">
         <f t="array" aca="1" ref="S12" ca="1">_xll.YCP($B12,S$2)</f>
@@ -5953,279 +5953,279 @@
       </c>
       <c r="BB12" s="4" cm="1">
         <f t="array" aca="1" ref="BB12" ca="1">_xll.YCP($B12,BB$2)</f>
-        <v>0.80119890999999999</v>
+        <v>0.80258741</v>
       </c>
       <c r="BC12" s="4" cm="1">
         <f t="array" aca="1" ref="BC12" ca="1">_xll.YCP($B12,BC$2)</f>
-        <v>1.3461559999999999E-2</v>
+        <v>1.1716509999999999E-2</v>
       </c>
       <c r="BD12" s="4" cm="1">
         <f t="array" aca="1" ref="BD12" ca="1">_xll.YCP($B12,BD$2)</f>
-        <v>2.754477E-2</v>
+        <v>2.730927E-2</v>
       </c>
       <c r="BE12" s="4" cm="1">
         <f t="array" aca="1" ref="BE12" ca="1">_xll.YCP($B12,BE$2)</f>
-        <v>5.4857349999999999E-2</v>
+        <v>5.481896E-2</v>
       </c>
       <c r="BF12" s="4" cm="1">
         <f t="array" aca="1" ref="BF12" ca="1">_xll.YCP($B12,BF$2)</f>
-        <v>2.1962800000000001E-3</v>
+        <v>2.20951E-3</v>
       </c>
       <c r="BG12" s="4" cm="1">
         <f t="array" aca="1" ref="BG12" ca="1">_xll.YCP($B12,BG$2)</f>
-        <v>8.3415199999999998E-3</v>
+        <v>7.3783299999999998E-3</v>
       </c>
       <c r="BH12" s="4" cm="1">
         <f t="array" aca="1" ref="BH12" ca="1">_xll.YCP($B12,BH$2)</f>
-        <v>3.3791660000000001E-2</v>
+        <v>3.6956089999999997E-2</v>
       </c>
       <c r="BI12" s="4" cm="1">
         <f t="array" aca="1" ref="BI12" ca="1">_xll.YCP($B12,BI$2)</f>
-        <v>2.3906009999999998E-2</v>
+        <v>2.0750419999999999E-2</v>
       </c>
       <c r="BJ12" s="4" cm="1">
         <f t="array" aca="1" ref="BJ12" ca="1">_xll.YCP($B12,BJ$2)</f>
-        <v>0.21139268</v>
+        <v>0.22352045000000001</v>
       </c>
       <c r="BK12" s="4" cm="1">
         <f t="array" aca="1" ref="BK12" ca="1">_xll.YCP($B12,BK$2)</f>
-        <v>0.25960425999999998</v>
+        <v>0.24059343</v>
       </c>
       <c r="BL12" s="4" cm="1">
         <f t="array" aca="1" ref="BL12" ca="1">_xll.YCP($B12,BL$2)</f>
-        <v>0.20345425</v>
+        <v>0.20631687000000001</v>
       </c>
       <c r="BM12" s="4" cm="1">
         <f t="array" aca="1" ref="BM12" ca="1">_xll.YCP($B12,BM$2)</f>
-        <v>6.5050499999999997E-2</v>
+        <v>6.2412380000000003E-2</v>
       </c>
       <c r="BN12" s="4" cm="1">
         <f t="array" aca="1" ref="BN12" ca="1">_xll.YCP($B12,BN$2)</f>
-        <v>7.6001869999999999E-2</v>
+        <v>8.6800879999999997E-2</v>
       </c>
       <c r="BO12" s="4" cm="1">
         <f t="array" aca="1" ref="BO12" ca="1">_xll.YCP($B12,BO$2)</f>
-        <v>6.6696030000000003E-2</v>
+        <v>5.9697609999999998E-2</v>
       </c>
       <c r="BP12" s="4" cm="1">
         <f t="array" aca="1" ref="BP12" ca="1">_xll.YCP($B12,BP$2)</f>
-        <v>3.046977E-2</v>
+        <v>2.5967670000000002E-2</v>
       </c>
       <c r="BQ12" s="4" cm="1">
         <f t="array" aca="1" ref="BQ12" ca="1">_xll.YCP($B12,BQ$2)</f>
-        <v>4.7108610000000002E-2</v>
+        <v>5.4300830000000001E-2</v>
       </c>
       <c r="BR12" s="4" cm="1">
         <f t="array" aca="1" ref="BR12" ca="1">_xll.YCP($B12,BR$2)</f>
-        <v>4.0222029999999999E-2</v>
+        <v>4.0389889999999998E-2</v>
       </c>
       <c r="BS12" s="4" cm="1">
         <f t="array" aca="1" ref="BS12" ca="1">_xll.YCP($B12,BS$2)</f>
-        <v>2.87117E-2</v>
+        <v>2.8296290000000002E-2</v>
       </c>
       <c r="BT12" s="4" cm="1">
         <f t="array" aca="1" ref="BT12" ca="1">_xll.YCP($B12,BT$2)</f>
-        <v>6.5520919999999996E-2</v>
+        <v>6.3455670000000006E-2</v>
       </c>
       <c r="BU12" s="4" cm="1">
         <f t="array" aca="1" ref="BU12" ca="1">_xll.YCP($B12,BU$2)</f>
-        <v>8.737309E-2</v>
+        <v>8.7016590000000005E-2</v>
       </c>
       <c r="BV12" s="4" cm="1">
         <f t="array" aca="1" ref="BV12" ca="1">_xll.YCP($B12,BV$2)</f>
-        <v>4.962979E-2</v>
+        <v>4.9840200000000001E-2</v>
       </c>
       <c r="BW12" s="4" cm="1">
         <f t="array" aca="1" ref="BW12" ca="1">_xll.YCP($B12,BW$2)</f>
-        <v>7.4004920000000002E-2</v>
+        <v>7.4376280000000003E-2</v>
       </c>
       <c r="BX12" s="4" cm="1">
         <f t="array" aca="1" ref="BX12" ca="1">_xll.YCP($B12,BX$2)</f>
-        <v>0.13783430999999999</v>
+        <v>0.13935426000000001</v>
       </c>
       <c r="BY12" s="4" cm="1">
         <f t="array" aca="1" ref="BY12" ca="1">_xll.YCP($B12,BY$2)</f>
-        <v>7.4325479999999999E-2</v>
+        <v>7.8087569999999995E-2</v>
       </c>
       <c r="BZ12" s="4" cm="1">
         <f t="array" aca="1" ref="BZ12" ca="1">_xll.YCP($B12,BZ$2)</f>
-        <v>0.12592658000000001</v>
+        <v>0.12696489999999999</v>
       </c>
       <c r="CA12" s="4" cm="1">
         <f t="array" aca="1" ref="CA12" ca="1">_xll.YCP($B12,CA$2)</f>
-        <v>1.7773710000000002E-2</v>
+        <v>1.7616949999999999E-2</v>
       </c>
       <c r="CB12" s="4" cm="1">
         <f t="array" aca="1" ref="CB12" ca="1">_xll.YCP($B12,CB$2)</f>
-        <v>0.30183331000000002</v>
+        <v>0.29858073000000002</v>
       </c>
       <c r="CC12" s="4" cm="1">
         <f t="array" aca="1" ref="CC12" ca="1">_xll.YCP($B12,CC$2)</f>
-        <v>2.2413410000000002E-2</v>
+        <v>2.2245810000000001E-2</v>
       </c>
       <c r="CD12" s="4" cm="1">
         <f t="array" aca="1" ref="CD12" ca="1">_xll.YCP($B12,CD$2)</f>
-        <v>2.571381E-2</v>
+        <v>2.2698909999999999E-2</v>
       </c>
       <c r="CE12" s="4" cm="1">
         <f t="array" aca="1" ref="CE12" ca="1">_xll.YCP($B12,CE$2)</f>
-        <v>0.80512598999999996</v>
+        <v>0.80587885000000004</v>
       </c>
       <c r="CF12" s="4" cm="1">
         <f t="array" aca="1" ref="CF12" ca="1">_xll.YCP($B12,CF$2)</f>
-        <v>0.16753580000000001</v>
+        <v>0.16868332</v>
       </c>
       <c r="CG12" s="4" cm="1">
         <f t="array" aca="1" ref="CG12" ca="1">_xll.YCP($B12,CG$2)</f>
-        <v>7.1769999999999999E-5</v>
+        <v>7.1680000000000005E-5</v>
       </c>
       <c r="CH12" s="4" cm="1">
         <f t="array" aca="1" ref="CH12" ca="1">_xll.YCP($B12,CH$2)</f>
-        <v>8.6667000000000005E-4</v>
+        <v>6.1185999999999999E-4</v>
       </c>
       <c r="CI12" s="4" cm="1">
         <f t="array" aca="1" ref="CI12" ca="1">_xll.YCP($B12,CI$2)</f>
-        <v>6.8594000000000001E-4</v>
+        <v>2.0553300000000002E-3</v>
       </c>
       <c r="CJ12" s="4" cm="1">
         <f t="array" aca="1" ref="CJ12" ca="1">_xll.YCP($B12,CJ$2)</f>
-        <v>8.6057030000000007E-2</v>
+        <v>8.5840009999999994E-2</v>
       </c>
       <c r="CK12" s="4" cm="1">
         <f t="array" aca="1" ref="CK12" ca="1">_xll.YCP($B12,CK$2)</f>
-        <v>0.40986852000000001</v>
+        <v>0.40467679000000001</v>
       </c>
       <c r="CL12" s="4" cm="1">
         <f t="array" aca="1" ref="CL12" ca="1">_xll.YCP($B12,CL$2)</f>
-        <v>0.101054</v>
+        <v>0.10348116</v>
       </c>
       <c r="CM12" s="4" cm="1">
         <f t="array" aca="1" ref="CM12" ca="1">_xll.YCP($B12,CM$2)</f>
-        <v>0.20999752999999999</v>
+        <v>0.21099470000000001</v>
       </c>
       <c r="CN12" s="4" cm="1">
         <f t="array" aca="1" ref="CN12" ca="1">_xll.YCP($B12,CN$2)</f>
-        <v>8.23488E-3</v>
+        <v>8.1464199999999997E-3</v>
       </c>
       <c r="CO12" s="4" cm="1">
         <f t="array" aca="1" ref="CO12" ca="1">_xll.YCP($B12,CO$2)</f>
-        <v>7.2707000000000002E-4</v>
+        <v>7.2271E-4</v>
       </c>
       <c r="CP12" s="4" cm="1">
         <f t="array" aca="1" ref="CP12" ca="1">_xll.YCP($B12,CP$2)</f>
-        <v>9.9140000000000003E-5</v>
+        <v>9.857E-5</v>
       </c>
       <c r="CQ12" s="4" cm="1">
         <f t="array" aca="1" ref="CQ12" ca="1">_xll.YCP($B12,CQ$2)</f>
-        <v>2.403957E-2</v>
+        <v>2.4994700000000002E-2</v>
       </c>
       <c r="CR12" s="4" cm="1">
         <f t="array" aca="1" ref="CR12" ca="1">_xll.YCP($B12,CR$2)</f>
-        <v>0.17465137</v>
+        <v>0.17133633000000001</v>
       </c>
       <c r="CS12" s="4" cm="1">
         <f t="array" aca="1" ref="CS12" ca="1">_xll.YCP($B12,CS$2)</f>
-        <v>0.20064019</v>
+        <v>0.18721484999999999</v>
       </c>
       <c r="CT12" s="4" cm="1">
         <f t="array" aca="1" ref="CT12" ca="1">_xll.YCP($B12,CT$2)</f>
-        <v>0.24802597000000001</v>
+        <v>0.24940744000000001</v>
       </c>
       <c r="CU12" s="4" cm="1">
         <f t="array" aca="1" ref="CU12" ca="1">_xll.YCP($B12,CU$2)</f>
-        <v>0.10643809</v>
+        <v>0.10637956</v>
       </c>
       <c r="CV12" s="4" cm="1">
         <f t="array" aca="1" ref="CV12" ca="1">_xll.YCP($B12,CV$2)</f>
-        <v>0.19414454</v>
+        <v>0.19371047</v>
       </c>
       <c r="CW12" s="4" cm="1">
         <f t="array" aca="1" ref="CW12" ca="1">_xll.YCP($B12,CW$2)</f>
-        <v>5.5503419999999998E-2</v>
+        <v>7.6333760000000001E-2</v>
       </c>
       <c r="CX12" s="3" cm="1">
         <f t="array" aca="1" ref="CX12" ca="1">_xll.YCP($B12,CX$2)</f>
-        <v>4.8233600000000001</v>
+        <v>4.8243919999999996</v>
       </c>
       <c r="CY12" s="20" cm="1">
         <f t="array" aca="1" ref="CY12" ca="1">_xll.YCP($B12,CY$2)</f>
-        <v>5.9388009999999998</v>
+        <v>5.8513109999999999</v>
       </c>
       <c r="CZ12" s="4" cm="1">
         <f t="array" aca="1" ref="CZ12" ca="1">_xll.YCP($B12,CZ$2)</f>
-        <v>4.6699999999999998E-2</v>
+        <v>5.4800000000000001E-2</v>
       </c>
       <c r="DA12" s="4" cm="1">
         <f t="array" aca="1" ref="DA12" ca="1">_xll.YCP($B12,DA$2)</f>
-        <v>4.3543329999999998E-2</v>
+        <v>4.387775E-2</v>
       </c>
       <c r="DB12" s="4" cm="1">
         <f t="array" aca="1" ref="DB12" ca="1">_xll.YCP($B12,DB$2)</f>
-        <v>4.2849529999999997E-2</v>
+        <v>4.3021049999999998E-2</v>
       </c>
       <c r="DC12" s="4" cm="1">
         <f t="array" aca="1" ref="DC12" ca="1">_xll.YCP($B12,DC$2)</f>
-        <v>0.38226473999999999</v>
+        <v>0.37728624999999999</v>
       </c>
       <c r="DD12" s="4" cm="1">
         <f t="array" aca="1" ref="DD12" ca="1">_xll.YCP($B12,DD$2)</f>
-        <v>0.31990809999999997</v>
+        <v>0.32382538</v>
       </c>
       <c r="DE12" s="4" cm="1">
         <f t="array" aca="1" ref="DE12" ca="1">_xll.YCP($B12,DE$2)</f>
-        <v>0.28576286000000001</v>
+        <v>0.28702698999999998</v>
       </c>
       <c r="DF12" s="4" cm="1">
         <f t="array" aca="1" ref="DF12" ca="1">_xll.YCP($B12,DF$2)</f>
-        <v>8.2503200000000002E-3</v>
+        <v>8.1140299999999995E-3</v>
       </c>
       <c r="DG12" s="4" cm="1">
         <f t="array" aca="1" ref="DG12" ca="1">_xll.YCP($B12,DG$2)</f>
-        <v>3.8139799999999998E-3</v>
+        <v>3.74734E-3</v>
       </c>
       <c r="DH12" s="4" cm="1">
         <f t="array" aca="1" ref="DH12" ca="1">_xll.YCP($B12,DH$2)</f>
-        <v>0.80531428999999999</v>
+        <v>0.80606889000000004</v>
       </c>
       <c r="DI12" s="4" cm="1">
         <f t="array" aca="1" ref="DI12" ca="1">_xll.YCP($B12,DI$2)</f>
-        <v>0.16776731</v>
+        <v>0.1689146</v>
       </c>
       <c r="DJ12" s="4" cm="1">
         <f t="array" aca="1" ref="DJ12" ca="1">_xll.YCP($B12,DJ$2)</f>
-        <v>2.571381E-2</v>
+        <v>2.2698909999999999E-2</v>
       </c>
       <c r="DK12" s="4" cm="1">
         <f t="array" aca="1" ref="DK12" ca="1">_xll.YCP($B12,DK$2)</f>
-        <v>4.9047149999999998E-2</v>
+        <v>4.312382E-2</v>
       </c>
       <c r="DL12" s="4" cm="1">
         <f t="array" aca="1" ref="DL12" ca="1">_xll.YCP($B12,DL$2)</f>
-        <v>0.55117373999999997</v>
+        <v>0.55107746000000002</v>
       </c>
       <c r="DM12" s="4" cm="1">
         <f t="array" aca="1" ref="DM12" ca="1">_xll.YCP($B12,DM$2)</f>
-        <v>0.12202060000000001</v>
+        <v>0.12230824</v>
       </c>
       <c r="DN12" s="4" cm="1">
         <f t="array" aca="1" ref="DN12" ca="1">_xll.YCP($B12,DN$2)</f>
-        <v>0.12840908000000001</v>
+        <v>0.12905119000000001</v>
       </c>
       <c r="DO12" s="4" cm="1">
         <f t="array" aca="1" ref="DO12" ca="1">_xll.YCP($B12,DO$2)</f>
-        <v>0.13193024</v>
+        <v>0.13264607</v>
       </c>
       <c r="DP12" s="4" cm="1">
         <f t="array" aca="1" ref="DP12" ca="1">_xll.YCP($B12,DP$2)</f>
-        <v>1.4813700000000001E-3</v>
+        <v>1.47769E-3</v>
       </c>
       <c r="DQ12" s="4" cm="1">
         <f t="array" aca="1" ref="DQ12" ca="1">_xll.YCP($B12,DQ$2)</f>
-        <v>3.9598999999999997E-3</v>
+        <v>3.8903100000000001E-3</v>
       </c>
       <c r="DR12" s="4" cm="1">
         <f t="array" aca="1" ref="DR12" ca="1">_xll.YCP($B12,DR$2)</f>
-        <v>0.95095284999999996</v>
+        <v>0.95687617999999997</v>
       </c>
     </row>
     <row r="13" spans="2:122" x14ac:dyDescent="0.45">
@@ -6254,11 +6254,11 @@
       </c>
       <c r="H13" s="4" cm="1">
         <f t="array" aca="1" ref="H13" ca="1">_xll.YCP($B13,H$2)</f>
-        <v>5.8903000000000002E-3</v>
+        <v>5.8957999999999997E-3</v>
       </c>
       <c r="I13" s="4" cm="1">
         <f t="array" aca="1" ref="I13" ca="1">_xll.YCP($B13,I$2)</f>
-        <v>9.4579999999999994E-3</v>
+        <v>9.6380000000000007E-3</v>
       </c>
       <c r="J13" s="5" cm="1">
         <f t="array" aca="1" ref="J13" ca="1">_xll.YCP($B13,J$2)</f>
@@ -6266,23 +6266,23 @@
       </c>
       <c r="K13" s="4" cm="1">
         <f t="array" aca="1" ref="K13" ca="1">_xll.YCP($B13,K$2)</f>
-        <v>0.38773684000000003</v>
+        <v>0.38972067999999999</v>
       </c>
       <c r="L13" s="4" cm="1">
         <f t="array" aca="1" ref="L13" ca="1">_xll.YCP($B13,L$2)</f>
-        <v>2.2815999999999999E-2</v>
+        <v>-2.1177000000000001E-2</v>
       </c>
       <c r="M13" s="4" cm="1">
         <f t="array" aca="1" ref="M13" ca="1">_xll.YCP($B13,M$2)</f>
-        <v>9.4904000000000002E-2</v>
+        <v>3.5392E-2</v>
       </c>
       <c r="N13" s="4" cm="1">
         <f t="array" aca="1" ref="N13" ca="1">_xll.YCP($B13,N$2)</f>
-        <v>0.13763500000000001</v>
+        <v>0.123875</v>
       </c>
       <c r="O13" s="4" cm="1">
         <f t="array" aca="1" ref="O13" ca="1">_xll.YCP($B13,O$2)</f>
-        <v>0.21939700000000001</v>
+        <v>0.196156</v>
       </c>
       <c r="P13" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P13" ca="1">_xll.YCP($B13,P$2)</f>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="R13" s="4" cm="1">
         <f t="array" aca="1" ref="R13" ca="1">_xll.YCP($B13,R$2)</f>
-        <v>0.138348</v>
+        <v>0.124972</v>
       </c>
       <c r="S13" s="3" cm="1">
         <f t="array" aca="1" ref="S13" ca="1">_xll.YCP($B13,S$2)</f>
@@ -6438,127 +6438,127 @@
       </c>
       <c r="BB13" s="4" cm="1">
         <f t="array" aca="1" ref="BB13" ca="1">_xll.YCP($B13,BB$2)</f>
-        <v>0.78405926999999997</v>
+        <v>0.78573806999999996</v>
       </c>
       <c r="BC13" s="4" cm="1">
         <f t="array" aca="1" ref="BC13" ca="1">_xll.YCP($B13,BC$2)</f>
-        <v>1.497911E-2</v>
+        <v>1.286402E-2</v>
       </c>
       <c r="BD13" s="4" cm="1">
         <f t="array" aca="1" ref="BD13" ca="1">_xll.YCP($B13,BD$2)</f>
-        <v>2.920677E-2</v>
+        <v>2.8925909999999999E-2</v>
       </c>
       <c r="BE13" s="4" cm="1">
         <f t="array" aca="1" ref="BE13" ca="1">_xll.YCP($B13,BE$2)</f>
-        <v>5.8891159999999998E-2</v>
+        <v>5.9001789999999998E-2</v>
       </c>
       <c r="BF13" s="4" cm="1">
         <f t="array" aca="1" ref="BF13" ca="1">_xll.YCP($B13,BF$2)</f>
-        <v>2.6738500000000002E-3</v>
+        <v>2.69447E-3</v>
       </c>
       <c r="BG13" s="4" cm="1">
         <f t="array" aca="1" ref="BG13" ca="1">_xll.YCP($B13,BG$2)</f>
-        <v>1.010139E-2</v>
+        <v>8.9281199999999995E-3</v>
       </c>
       <c r="BH13" s="4" cm="1">
         <f t="array" aca="1" ref="BH13" ca="1">_xll.YCP($B13,BH$2)</f>
-        <v>4.0062189999999998E-2</v>
+        <v>4.4062740000000003E-2</v>
       </c>
       <c r="BI13" s="4" cm="1">
         <f t="array" aca="1" ref="BI13" ca="1">_xll.YCP($B13,BI$2)</f>
-        <v>2.8619510000000001E-2</v>
+        <v>2.4799129999999999E-2</v>
       </c>
       <c r="BJ13" s="4" cm="1">
         <f t="array" aca="1" ref="BJ13" ca="1">_xll.YCP($B13,BJ$2)</f>
-        <v>0.21170191999999999</v>
+        <v>0.22391158999999999</v>
       </c>
       <c r="BK13" s="4" cm="1">
         <f t="array" aca="1" ref="BK13" ca="1">_xll.YCP($B13,BK$2)</f>
-        <v>0.26071374000000003</v>
+        <v>0.24139905</v>
       </c>
       <c r="BL13" s="4" cm="1">
         <f t="array" aca="1" ref="BL13" ca="1">_xll.YCP($B13,BL$2)</f>
-        <v>0.20398516999999999</v>
+        <v>0.20713957999999999</v>
       </c>
       <c r="BM13" s="4" cm="1">
         <f t="array" aca="1" ref="BM13" ca="1">_xll.YCP($B13,BM$2)</f>
-        <v>6.5044030000000003E-2</v>
+        <v>6.2367600000000002E-2</v>
       </c>
       <c r="BN13" s="4" cm="1">
         <f t="array" aca="1" ref="BN13" ca="1">_xll.YCP($B13,BN$2)</f>
-        <v>7.5810859999999994E-2</v>
+        <v>8.6540809999999996E-2</v>
       </c>
       <c r="BO13" s="4" cm="1">
         <f t="array" aca="1" ref="BO13" ca="1">_xll.YCP($B13,BO$2)</f>
-        <v>6.6337569999999998E-2</v>
+        <v>5.9431699999999997E-2</v>
       </c>
       <c r="BP13" s="4" cm="1">
         <f t="array" aca="1" ref="BP13" ca="1">_xll.YCP($B13,BP$2)</f>
-        <v>3.0257630000000001E-2</v>
+        <v>2.5806490000000001E-2</v>
       </c>
       <c r="BQ13" s="4" cm="1">
         <f t="array" aca="1" ref="BQ13" ca="1">_xll.YCP($B13,BQ$2)</f>
-        <v>4.6537460000000003E-2</v>
+        <v>5.3614290000000002E-2</v>
       </c>
       <c r="BR13" s="4" cm="1">
         <f t="array" aca="1" ref="BR13" ca="1">_xll.YCP($B13,BR$2)</f>
-        <v>3.961162E-2</v>
+        <v>3.978889E-2</v>
       </c>
       <c r="BS13" s="4" cm="1">
         <f t="array" aca="1" ref="BS13" ca="1">_xll.YCP($B13,BS$2)</f>
-        <v>2.8533469999999998E-2</v>
+        <v>2.8092900000000001E-2</v>
       </c>
       <c r="BT13" s="4" cm="1">
         <f t="array" aca="1" ref="BT13" ca="1">_xll.YCP($B13,BT$2)</f>
-        <v>6.5859879999999996E-2</v>
+        <v>6.377265E-2</v>
       </c>
       <c r="BU13" s="4" cm="1">
         <f t="array" aca="1" ref="BU13" ca="1">_xll.YCP($B13,BU$2)</f>
-        <v>8.7101799999999993E-2</v>
+        <v>8.6732169999999997E-2</v>
       </c>
       <c r="BV13" s="4" cm="1">
         <f t="array" aca="1" ref="BV13" ca="1">_xll.YCP($B13,BV$2)</f>
-        <v>4.9692380000000001E-2</v>
+        <v>4.9898820000000003E-2</v>
       </c>
       <c r="BW13" s="4" cm="1">
         <f t="array" aca="1" ref="BW13" ca="1">_xll.YCP($B13,BW$2)</f>
-        <v>7.3727899999999999E-2</v>
+        <v>7.4060710000000002E-2</v>
       </c>
       <c r="BX13" s="4" cm="1">
         <f t="array" aca="1" ref="BX13" ca="1">_xll.YCP($B13,BX$2)</f>
-        <v>0.13788599000000001</v>
+        <v>0.13933796000000001</v>
       </c>
       <c r="BY13" s="4" cm="1">
         <f t="array" aca="1" ref="BY13" ca="1">_xll.YCP($B13,BY$2)</f>
-        <v>7.4341900000000002E-2</v>
+        <v>7.8095590000000006E-2</v>
       </c>
       <c r="BZ13" s="4" cm="1">
         <f t="array" aca="1" ref="BZ13" ca="1">_xll.YCP($B13,BZ$2)</f>
-        <v>0.12570397</v>
+        <v>0.12673897000000001</v>
       </c>
       <c r="CA13" s="4" cm="1">
         <f t="array" aca="1" ref="CA13" ca="1">_xll.YCP($B13,CA$2)</f>
-        <v>1.7694040000000001E-2</v>
+        <v>1.7526880000000002E-2</v>
       </c>
       <c r="CB13" s="4" cm="1">
         <f t="array" aca="1" ref="CB13" ca="1">_xll.YCP($B13,CB$2)</f>
-        <v>0.30227659000000001</v>
+        <v>0.29919818999999997</v>
       </c>
       <c r="CC13" s="4" cm="1">
         <f t="array" aca="1" ref="CC13" ca="1">_xll.YCP($B13,CC$2)</f>
-        <v>2.241493E-2</v>
+        <v>2.224721E-2</v>
       </c>
       <c r="CD13" s="4" cm="1">
         <f t="array" aca="1" ref="CD13" ca="1">_xll.YCP($B13,CD$2)</f>
-        <v>3.3565690000000002E-2</v>
+        <v>3.15222E-2</v>
       </c>
       <c r="CE13" s="4" cm="1">
         <f t="array" aca="1" ref="CE13" ca="1">_xll.YCP($B13,CE$2)</f>
-        <v>0.96463942000000003</v>
+        <v>0.96697056000000003</v>
       </c>
       <c r="CF13" s="4" cm="1">
         <f t="array" aca="1" ref="CF13" ca="1">_xll.YCP($B13,CF$2)</f>
-        <v>9.7969999999999999E-5</v>
+        <v>8.4489999999999999E-5</v>
       </c>
       <c r="CG13" s="4" cm="1">
         <f t="array" aca="1" ref="CG13" ca="1">_xll.YCP($B13,CG$2)</f>
@@ -6566,11 +6566,11 @@
       </c>
       <c r="CH13" s="4" cm="1">
         <f t="array" aca="1" ref="CH13" ca="1">_xll.YCP($B13,CH$2)</f>
-        <v>8.6507999999999995E-4</v>
+        <v>5.5332999999999999E-4</v>
       </c>
       <c r="CI13" s="4" cm="1">
         <f t="array" aca="1" ref="CI13" ca="1">_xll.YCP($B13,CI$2)</f>
-        <v>8.3182999999999998E-4</v>
+        <v>8.6941000000000004E-4</v>
       </c>
       <c r="CJ13" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="CJ13" ca="1">_xll.YCP($B13,CJ$2)</f>
@@ -6650,11 +6650,11 @@
       </c>
       <c r="DC13" s="4" cm="1">
         <f t="array" aca="1" ref="DC13" ca="1">_xll.YCP($B13,DC$2)</f>
-        <v>0.99014968999999997</v>
+        <v>0.99273268000000003</v>
       </c>
       <c r="DD13" s="4" cm="1">
         <f t="array" aca="1" ref="DD13" ca="1">_xll.YCP($B13,DD$2)</f>
-        <v>1.4445899999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="DE13" s="4" cm="1">
         <f t="array" aca="1" ref="DE13" ca="1">_xll.YCP($B13,DE$2)</f>
@@ -6666,35 +6666,35 @@
       </c>
       <c r="DG13" s="4" cm="1">
         <f t="array" aca="1" ref="DG13" ca="1">_xll.YCP($B13,DG$2)</f>
-        <v>8.4057100000000003E-3</v>
+        <v>7.2673199999999999E-3</v>
       </c>
       <c r="DH13" s="4" cm="1">
         <f t="array" aca="1" ref="DH13" ca="1">_xll.YCP($B13,DH$2)</f>
-        <v>0.96486742000000003</v>
+        <v>0.96720101999999997</v>
       </c>
       <c r="DI13" s="4" cm="1">
         <f t="array" aca="1" ref="DI13" ca="1">_xll.YCP($B13,DI$2)</f>
-        <v>9.7969999999999999E-5</v>
+        <v>8.4489999999999999E-5</v>
       </c>
       <c r="DJ13" s="4" cm="1">
         <f t="array" aca="1" ref="DJ13" ca="1">_xll.YCP($B13,DJ$2)</f>
-        <v>3.3565690000000002E-2</v>
+        <v>3.15222E-2</v>
       </c>
       <c r="DK13" s="4" cm="1">
         <f t="array" aca="1" ref="DK13" ca="1">_xll.YCP($B13,DK$2)</f>
-        <v>4.9276670000000002E-2</v>
+        <v>4.3212899999999999E-2</v>
       </c>
       <c r="DL13" s="4" cm="1">
         <f t="array" aca="1" ref="DL13" ca="1">_xll.YCP($B13,DL$2)</f>
-        <v>0.66220330999999999</v>
+        <v>0.66309954000000004</v>
       </c>
       <c r="DM13" s="4" cm="1">
         <f t="array" aca="1" ref="DM13" ca="1">_xll.YCP($B13,DM$2)</f>
-        <v>0.14606469</v>
+        <v>0.14662157000000001</v>
       </c>
       <c r="DN13" s="4" cm="1">
         <f t="array" aca="1" ref="DN13" ca="1">_xll.YCP($B13,DN$2)</f>
-        <v>0.15215693999999999</v>
+        <v>0.15312856</v>
       </c>
       <c r="DO13" s="4" cm="1">
         <f t="array" aca="1" ref="DO13" ca="1">_xll.YCP($B13,DO$2)</f>
@@ -6706,11 +6706,11 @@
       </c>
       <c r="DQ13" s="4" cm="1">
         <f t="array" aca="1" ref="DQ13" ca="1">_xll.YCP($B13,DQ$2)</f>
-        <v>8.4057100000000003E-3</v>
+        <v>7.2673199999999999E-3</v>
       </c>
       <c r="DR13" s="4" cm="1">
         <f t="array" aca="1" ref="DR13" ca="1">_xll.YCP($B13,DR$2)</f>
-        <v>0.95072332999999998</v>
+        <v>0.9567871</v>
       </c>
     </row>
     <row r="14" spans="2:122" x14ac:dyDescent="0.45">
@@ -7222,11 +7222,11 @@
       </c>
       <c r="H15" s="4" cm="1">
         <f t="array" aca="1" ref="H15" ca="1">_xll.YCP($B15,H$2)</f>
-        <v>5.1099999999999995E-4</v>
+        <v>5.1230999999999998E-4</v>
       </c>
       <c r="I15" s="4" cm="1">
         <f t="array" aca="1" ref="I15" ca="1">_xll.YCP($B15,I$2)</f>
-        <v>2.8705999999999999E-2</v>
+        <v>2.9005E-2</v>
       </c>
       <c r="J15" s="5" cm="1">
         <f t="array" aca="1" ref="J15" ca="1">_xll.YCP($B15,J$2)</f>
@@ -7234,23 +7234,23 @@
       </c>
       <c r="K15" s="4" cm="1">
         <f t="array" aca="1" ref="K15" ca="1">_xll.YCP($B15,K$2)</f>
-        <v>0.27760596999999998</v>
+        <v>0.27826710999999998</v>
       </c>
       <c r="L15" s="4" cm="1">
         <f t="array" aca="1" ref="L15" ca="1">_xll.YCP($B15,L$2)</f>
-        <v>1.0204E-2</v>
+        <v>-7.6140000000000001E-3</v>
       </c>
       <c r="M15" s="4" cm="1">
         <f t="array" aca="1" ref="M15" ca="1">_xll.YCP($B15,M$2)</f>
-        <v>4.2190999999999999E-2</v>
+        <v>1.4015E-2</v>
       </c>
       <c r="N15" s="4" cm="1">
         <f t="array" aca="1" ref="N15" ca="1">_xll.YCP($B15,N$2)</f>
-        <v>5.2463000000000003E-2</v>
+        <v>4.5755999999999998E-2</v>
       </c>
       <c r="O15" s="4" cm="1">
         <f t="array" aca="1" ref="O15" ca="1">_xll.YCP($B15,O$2)</f>
-        <v>0.113402</v>
+        <v>9.8899000000000001E-2</v>
       </c>
       <c r="P15" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P15" ca="1">_xll.YCP($B15,P$2)</f>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="R15" s="4" cm="1">
         <f t="array" aca="1" ref="R15" ca="1">_xll.YCP($B15,R$2)</f>
-        <v>9.5097000000000001E-2</v>
+        <v>8.7279999999999996E-2</v>
       </c>
       <c r="S15" s="3" cm="1">
         <f t="array" aca="1" ref="S15" ca="1">_xll.YCP($B15,S$2)</f>
@@ -7406,279 +7406,279 @@
       </c>
       <c r="BB15" s="4" cm="1">
         <f t="array" aca="1" ref="BB15" ca="1">_xll.YCP($B15,BB$2)</f>
-        <v>0.81644017999999996</v>
+        <v>0.81604893999999994</v>
       </c>
       <c r="BC15" s="4" cm="1">
         <f t="array" aca="1" ref="BC15" ca="1">_xll.YCP($B15,BC$2)</f>
-        <v>9.3002999999999992E-3</v>
+        <v>9.3891600000000006E-3</v>
       </c>
       <c r="BD15" s="4" cm="1">
         <f t="array" aca="1" ref="BD15" ca="1">_xll.YCP($B15,BD$2)</f>
-        <v>1.881418E-2</v>
+        <v>1.8928960000000002E-2</v>
       </c>
       <c r="BE15" s="4" cm="1">
         <f t="array" aca="1" ref="BE15" ca="1">_xll.YCP($B15,BE$2)</f>
-        <v>6.4665959999999995E-2</v>
+        <v>6.6048120000000002E-2</v>
       </c>
       <c r="BF15" s="4" cm="1">
         <f t="array" aca="1" ref="BF15" ca="1">_xll.YCP($B15,BF$2)</f>
-        <v>2.3609799999999999E-3</v>
+        <v>2.35455E-3</v>
       </c>
       <c r="BG15" s="4" cm="1">
         <f t="array" aca="1" ref="BG15" ca="1">_xll.YCP($B15,BG$2)</f>
-        <v>5.0951599999999996E-3</v>
+        <v>4.9148500000000001E-3</v>
       </c>
       <c r="BH15" s="4" cm="1">
         <f t="array" aca="1" ref="BH15" ca="1">_xll.YCP($B15,BH$2)</f>
-        <v>2.60839E-2</v>
+        <v>2.6092239999999999E-2</v>
       </c>
       <c r="BI15" s="4" cm="1">
         <f t="array" aca="1" ref="BI15" ca="1">_xll.YCP($B15,BI$2)</f>
-        <v>1.8294029999999999E-2</v>
+        <v>1.7911759999999999E-2</v>
       </c>
       <c r="BJ15" s="4" cm="1">
         <f t="array" aca="1" ref="BJ15" ca="1">_xll.YCP($B15,BJ$2)</f>
-        <v>0.18574889</v>
+        <v>0.18418938000000001</v>
       </c>
       <c r="BK15" s="4" cm="1">
         <f t="array" aca="1" ref="BK15" ca="1">_xll.YCP($B15,BK$2)</f>
-        <v>0.30977367</v>
+        <v>0.32145052000000002</v>
       </c>
       <c r="BL15" s="4" cm="1">
         <f t="array" aca="1" ref="BL15" ca="1">_xll.YCP($B15,BL$2)</f>
-        <v>0.20882559000000001</v>
+        <v>0.19563089</v>
       </c>
       <c r="BM15" s="4" cm="1">
         <f t="array" aca="1" ref="BM15" ca="1">_xll.YCP($B15,BM$2)</f>
-        <v>8.2210160000000004E-2</v>
+        <v>8.1970650000000006E-2</v>
       </c>
       <c r="BN15" s="4" cm="1">
         <f t="array" aca="1" ref="BN15" ca="1">_xll.YCP($B15,BN$2)</f>
-        <v>0.11769771</v>
+        <v>0.11953707</v>
       </c>
       <c r="BO15" s="4" cm="1">
         <f t="array" aca="1" ref="BO15" ca="1">_xll.YCP($B15,BO$2)</f>
-        <v>5.9733000000000001E-2</v>
+        <v>6.1656030000000001E-2</v>
       </c>
       <c r="BP15" s="4" cm="1">
         <f t="array" aca="1" ref="BP15" ca="1">_xll.YCP($B15,BP$2)</f>
-        <v>1.1764500000000001E-2</v>
+        <v>1.1747820000000001E-2</v>
       </c>
       <c r="BQ15" s="4" cm="1">
         <f t="array" aca="1" ref="BQ15" ca="1">_xll.YCP($B15,BQ$2)</f>
-        <v>1.7130570000000001E-2</v>
+        <v>1.6488610000000001E-2</v>
       </c>
       <c r="BR15" s="4" cm="1">
         <f t="array" aca="1" ref="BR15" ca="1">_xll.YCP($B15,BR$2)</f>
-        <v>7.1159200000000004E-3</v>
+        <v>7.3290100000000004E-3</v>
       </c>
       <c r="BS15" s="4" cm="1">
         <f t="array" aca="1" ref="BS15" ca="1">_xll.YCP($B15,BS$2)</f>
-        <v>3.4528749999999997E-2</v>
+        <v>3.3311019999999997E-2</v>
       </c>
       <c r="BT15" s="4" cm="1">
         <f t="array" aca="1" ref="BT15" ca="1">_xll.YCP($B15,BT$2)</f>
-        <v>7.8269149999999996E-2</v>
+        <v>7.7352710000000005E-2</v>
       </c>
       <c r="BU15" s="4" cm="1">
         <f t="array" aca="1" ref="BU15" ca="1">_xll.YCP($B15,BU$2)</f>
-        <v>9.4422450000000005E-2</v>
+        <v>9.3973319999999999E-2</v>
       </c>
       <c r="BV15" s="4" cm="1">
         <f t="array" aca="1" ref="BV15" ca="1">_xll.YCP($B15,BV$2)</f>
-        <v>4.3815170000000001E-2</v>
+        <v>4.3698689999999998E-2</v>
       </c>
       <c r="BW15" s="4" cm="1">
         <f t="array" aca="1" ref="BW15" ca="1">_xll.YCP($B15,BW$2)</f>
-        <v>3.9614900000000002E-2</v>
+        <v>3.8324080000000003E-2</v>
       </c>
       <c r="BX15" s="4" cm="1">
         <f t="array" aca="1" ref="BX15" ca="1">_xll.YCP($B15,BX$2)</f>
-        <v>0.13972388999999999</v>
+        <v>0.14222921999999999</v>
       </c>
       <c r="BY15" s="4" cm="1">
         <f t="array" aca="1" ref="BY15" ca="1">_xll.YCP($B15,BY$2)</f>
-        <v>7.9262529999999998E-2</v>
+        <v>8.0260890000000001E-2</v>
       </c>
       <c r="BZ15" s="4" cm="1">
         <f t="array" aca="1" ref="BZ15" ca="1">_xll.YCP($B15,BZ$2)</f>
-        <v>0.11337432</v>
+        <v>0.11485982</v>
       </c>
       <c r="CA15" s="4" cm="1">
         <f t="array" aca="1" ref="CA15" ca="1">_xll.YCP($B15,CA$2)</f>
-        <v>2.426362E-2</v>
+        <v>2.4198219999999999E-2</v>
       </c>
       <c r="CB15" s="4" cm="1">
         <f t="array" aca="1" ref="CB15" ca="1">_xll.YCP($B15,CB$2)</f>
-        <v>0.31358290999999999</v>
+        <v>0.31382195000000002</v>
       </c>
       <c r="CC15" s="4" cm="1">
         <f t="array" aca="1" ref="CC15" ca="1">_xll.YCP($B15,CC$2)</f>
-        <v>3.0576599999999999E-2</v>
+        <v>3.1323490000000002E-2</v>
       </c>
       <c r="CD15" s="4" cm="1">
         <f t="array" aca="1" ref="CD15" ca="1">_xll.YCP($B15,CD$2)</f>
-        <v>1.7661659999999999E-2</v>
+        <v>1.6096289999999999E-2</v>
       </c>
       <c r="CE15" s="4" cm="1">
         <f t="array" aca="1" ref="CE15" ca="1">_xll.YCP($B15,CE$2)</f>
-        <v>0.51394392</v>
+        <v>0.51323306999999996</v>
       </c>
       <c r="CF15" s="4" cm="1">
         <f t="array" aca="1" ref="CF15" ca="1">_xll.YCP($B15,CF$2)</f>
-        <v>0.46796890000000002</v>
+        <v>0.47023775000000001</v>
       </c>
       <c r="CG15" s="4" cm="1">
         <f t="array" aca="1" ref="CG15" ca="1">_xll.YCP($B15,CG$2)</f>
-        <v>1.1900000000000001E-4</v>
+        <v>1.1847E-4</v>
       </c>
       <c r="CH15" s="4" cm="1">
         <f t="array" aca="1" ref="CH15" ca="1">_xll.YCP($B15,CH$2)</f>
-        <v>4.2459999999999997E-5</v>
+        <v>4.087E-5</v>
       </c>
       <c r="CI15" s="4" cm="1">
         <f t="array" aca="1" ref="CI15" ca="1">_xll.YCP($B15,CI$2)</f>
-        <v>2.6405999999999999E-4</v>
+        <v>2.7349999999999998E-4</v>
       </c>
       <c r="CJ15" s="4" cm="1">
         <f t="array" aca="1" ref="CJ15" ca="1">_xll.YCP($B15,CJ$2)</f>
-        <v>2.968701E-2</v>
+        <v>2.9779079999999999E-2</v>
       </c>
       <c r="CK15" s="4" cm="1">
         <f t="array" aca="1" ref="CK15" ca="1">_xll.YCP($B15,CK$2)</f>
-        <v>0.49523486999999999</v>
+        <v>0.50511348</v>
       </c>
       <c r="CL15" s="4" cm="1">
         <f t="array" aca="1" ref="CL15" ca="1">_xll.YCP($B15,CL$2)</f>
-        <v>0.15629671000000001</v>
+        <v>0.15711294000000001</v>
       </c>
       <c r="CM15" s="4" cm="1">
         <f t="array" aca="1" ref="CM15" ca="1">_xll.YCP($B15,CM$2)</f>
-        <v>0.18705177000000001</v>
+        <v>0.18754512000000001</v>
       </c>
       <c r="CN15" s="4" cm="1">
         <f t="array" aca="1" ref="CN15" ca="1">_xll.YCP($B15,CN$2)</f>
-        <v>6.5837469999999995E-2</v>
+        <v>6.5799430000000006E-2</v>
       </c>
       <c r="CO15" s="4" cm="1">
         <f t="array" aca="1" ref="CO15" ca="1">_xll.YCP($B15,CO$2)</f>
-        <v>3.664456E-2</v>
+        <v>3.6625329999999998E-2</v>
       </c>
       <c r="CP15" s="4" cm="1">
         <f t="array" aca="1" ref="CP15" ca="1">_xll.YCP($B15,CP$2)</f>
-        <v>3.9853500000000004E-3</v>
+        <v>3.9832599999999998E-3</v>
       </c>
       <c r="CQ15" s="4" cm="1">
         <f t="array" aca="1" ref="CQ15" ca="1">_xll.YCP($B15,CQ$2)</f>
-        <v>2.2776099999999998E-3</v>
+        <v>2.2469E-3</v>
       </c>
       <c r="CR15" s="4" cm="1">
         <f t="array" aca="1" ref="CR15" ca="1">_xll.YCP($B15,CR$2)</f>
-        <v>4.5025290000000003E-2</v>
+        <v>4.5410350000000002E-2</v>
       </c>
       <c r="CS15" s="4" cm="1">
         <f t="array" aca="1" ref="CS15" ca="1">_xll.YCP($B15,CS$2)</f>
-        <v>5.8742320000000001E-2</v>
+        <v>5.8547950000000001E-2</v>
       </c>
       <c r="CT15" s="4" cm="1">
         <f t="array" aca="1" ref="CT15" ca="1">_xll.YCP($B15,CT$2)</f>
-        <v>0.85422969999999998</v>
+        <v>0.85407809999999995</v>
       </c>
       <c r="CU15" s="4" cm="1">
         <f t="array" aca="1" ref="CU15" ca="1">_xll.YCP($B15,CU$2)</f>
-        <v>2.8943920000000001E-2</v>
+        <v>2.9339879999999999E-2</v>
       </c>
       <c r="CV15" s="4" cm="1">
         <f t="array" aca="1" ref="CV15" ca="1">_xll.YCP($B15,CV$2)</f>
-        <v>1.0566570000000001E-2</v>
+        <v>1.057577E-2</v>
       </c>
       <c r="CW15" s="4" cm="1">
         <f t="array" aca="1" ref="CW15" ca="1">_xll.YCP($B15,CW$2)</f>
-        <v>2.2821899999999999E-3</v>
+        <v>2.61539E-3</v>
       </c>
       <c r="CX15" s="3" cm="1">
         <f t="array" aca="1" ref="CX15" ca="1">_xll.YCP($B15,CX$2)</f>
-        <v>5.6968529999999999</v>
+        <v>5.6741070000000002</v>
       </c>
       <c r="CY15" s="20" cm="1">
         <f t="array" aca="1" ref="CY15" ca="1">_xll.YCP($B15,CY$2)</f>
-        <v>6.9123919999999996</v>
+        <v>6.9029939999999996</v>
       </c>
       <c r="CZ15" s="4" cm="1">
         <f t="array" aca="1" ref="CZ15" ca="1">_xll.YCP($B15,CZ$2)</f>
-        <v>4.8755819999999998E-2</v>
+        <v>4.9153889999999999E-2</v>
       </c>
       <c r="DA15" s="4" cm="1">
         <f t="array" aca="1" ref="DA15" ca="1">_xll.YCP($B15,DA$2)</f>
-        <v>4.3411930000000001E-2</v>
-      </c>
-      <c r="DB15" s="4" cm="1">
+        <v>4.3605810000000002E-2</v>
+      </c>
+      <c r="DB15" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="DB15" ca="1">_xll.YCP($B15,DB$2)</f>
-        <v>6.0989700000000001E-2</v>
+        <v>ERR: NO DATA</v>
       </c>
       <c r="DC15" s="4" cm="1">
         <f t="array" aca="1" ref="DC15" ca="1">_xll.YCP($B15,DC$2)</f>
-        <v>0.53163859999999996</v>
+        <v>0.52955452000000003</v>
       </c>
       <c r="DD15" s="4" cm="1">
         <f t="array" aca="1" ref="DD15" ca="1">_xll.YCP($B15,DD$2)</f>
-        <v>0.45339547000000002</v>
+        <v>0.45483388000000002</v>
       </c>
       <c r="DE15" s="4" cm="1">
         <f t="array" aca="1" ref="DE15" ca="1">_xll.YCP($B15,DE$2)</f>
-        <v>6.9200000000000002E-5</v>
+        <v>4.8699999999999998E-5</v>
       </c>
       <c r="DF15" s="4" cm="1">
         <f t="array" aca="1" ref="DF15" ca="1">_xll.YCP($B15,DF$2)</f>
-        <v>8.9248899999999996E-3</v>
+        <v>9.1867000000000008E-3</v>
       </c>
       <c r="DG15" s="4" cm="1">
         <f t="array" aca="1" ref="DG15" ca="1">_xll.YCP($B15,DG$2)</f>
-        <v>5.97184E-3</v>
+        <v>6.3762100000000002E-3</v>
       </c>
       <c r="DH15" s="4" cm="1">
         <f t="array" aca="1" ref="DH15" ca="1">_xll.YCP($B15,DH$2)</f>
-        <v>0.51394392</v>
+        <v>0.51323306999999996</v>
       </c>
       <c r="DI15" s="4" cm="1">
         <f t="array" aca="1" ref="DI15" ca="1">_xll.YCP($B15,DI$2)</f>
-        <v>0.46796890000000002</v>
+        <v>0.47023775000000001</v>
       </c>
       <c r="DJ15" s="4" cm="1">
         <f t="array" aca="1" ref="DJ15" ca="1">_xll.YCP($B15,DJ$2)</f>
-        <v>1.7661659999999999E-2</v>
+        <v>1.6096289999999999E-2</v>
       </c>
       <c r="DK15" s="4" cm="1">
         <f t="array" aca="1" ref="DK15" ca="1">_xll.YCP($B15,DK$2)</f>
-        <v>3.5059640000000003E-2</v>
+        <v>3.4869039999999997E-2</v>
       </c>
       <c r="DL15" s="4" cm="1">
         <f t="array" aca="1" ref="DL15" ca="1">_xll.YCP($B15,DL$2)</f>
-        <v>0.35782175999999999</v>
+        <v>0.35608144000000003</v>
       </c>
       <c r="DM15" s="4" cm="1">
         <f t="array" aca="1" ref="DM15" ca="1">_xll.YCP($B15,DM$2)</f>
-        <v>0.10975703000000001</v>
+        <v>0.11115023</v>
       </c>
       <c r="DN15" s="4" cm="1">
         <f t="array" aca="1" ref="DN15" ca="1">_xll.YCP($B15,DN$2)</f>
-        <v>4.4987310000000003E-2</v>
+        <v>4.4572830000000001E-2</v>
       </c>
       <c r="DO15" s="4" cm="1">
         <f t="array" aca="1" ref="DO15" ca="1">_xll.YCP($B15,DO$2)</f>
-        <v>0.40650960000000003</v>
+        <v>0.41356427000000001</v>
       </c>
       <c r="DP15" s="4" cm="1">
         <f t="array" aca="1" ref="DP15" ca="1">_xll.YCP($B15,DP$2)</f>
-        <v>4.984624E-2</v>
+        <v>5.0033000000000001E-2</v>
       </c>
       <c r="DQ15" s="4" cm="1">
         <f t="array" aca="1" ref="DQ15" ca="1">_xll.YCP($B15,DQ$2)</f>
-        <v>5.9721000000000002E-3</v>
+        <v>6.3763800000000001E-3</v>
       </c>
       <c r="DR15" s="4" cm="1">
         <f t="array" aca="1" ref="DR15" ca="1">_xll.YCP($B15,DR$2)</f>
-        <v>0.96494036000000005</v>
+        <v>0.96513095999999998</v>
       </c>
     </row>
     <row r="16" spans="2:122" x14ac:dyDescent="0.45">
@@ -7707,11 +7707,11 @@
       </c>
       <c r="H16" s="4" cm="1">
         <f t="array" aca="1" ref="H16" ca="1">_xll.YCP($B16,H$2)</f>
-        <v>4.5811000000000002E-4</v>
+        <v>4.5884000000000002E-4</v>
       </c>
       <c r="I16" s="4" cm="1">
         <f t="array" aca="1" ref="I16" ca="1">_xll.YCP($B16,I$2)</f>
-        <v>2.3095999999999998E-2</v>
+        <v>2.3408999999999999E-2</v>
       </c>
       <c r="J16" s="5" cm="1">
         <f t="array" aca="1" ref="J16" ca="1">_xll.YCP($B16,J$2)</f>
@@ -7719,23 +7719,23 @@
       </c>
       <c r="K16" s="4" cm="1">
         <f t="array" aca="1" ref="K16" ca="1">_xll.YCP($B16,K$2)</f>
-        <v>0.20747492000000001</v>
+        <v>0.20829097999999999</v>
       </c>
       <c r="L16" s="4" cm="1">
         <f t="array" aca="1" ref="L16" ca="1">_xll.YCP($B16,L$2)</f>
-        <v>1.3468000000000001E-2</v>
+        <v>-8.4609999999999998E-3</v>
       </c>
       <c r="M16" s="4" cm="1">
         <f t="array" aca="1" ref="M16" ca="1">_xll.YCP($B16,M$2)</f>
-        <v>5.8852000000000002E-2</v>
+        <v>1.8912000000000002E-2</v>
       </c>
       <c r="N16" s="4" cm="1">
         <f t="array" aca="1" ref="N16" ca="1">_xll.YCP($B16,N$2)</f>
-        <v>7.3371000000000006E-2</v>
+        <v>6.4350000000000004E-2</v>
       </c>
       <c r="O16" s="4" cm="1">
         <f t="array" aca="1" ref="O16" ca="1">_xll.YCP($B16,O$2)</f>
-        <v>0.14411499999999999</v>
+        <v>0.124875</v>
       </c>
       <c r="P16" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P16" ca="1">_xll.YCP($B16,P$2)</f>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="R16" s="4" cm="1">
         <f t="array" aca="1" ref="R16" ca="1">_xll.YCP($B16,R$2)</f>
-        <v>0.115273</v>
+        <v>0.105199</v>
       </c>
       <c r="S16" s="3" cm="1">
         <f t="array" aca="1" ref="S16" ca="1">_xll.YCP($B16,S$2)</f>
@@ -7891,223 +7891,223 @@
       </c>
       <c r="BB16" s="4" cm="1">
         <f t="array" aca="1" ref="BB16" ca="1">_xll.YCP($B16,BB$2)</f>
-        <v>0.83021436999999998</v>
+        <v>0.83052890999999995</v>
       </c>
       <c r="BC16" s="4" cm="1">
         <f t="array" aca="1" ref="BC16" ca="1">_xll.YCP($B16,BC$2)</f>
-        <v>9.9764399999999996E-3</v>
+        <v>9.9010799999999996E-3</v>
       </c>
       <c r="BD16" s="4" cm="1">
         <f t="array" aca="1" ref="BD16" ca="1">_xll.YCP($B16,BD$2)</f>
-        <v>1.383263E-2</v>
+        <v>1.3864929999999999E-2</v>
       </c>
       <c r="BE16" s="4" cm="1">
         <f t="array" aca="1" ref="BE16" ca="1">_xll.YCP($B16,BE$2)</f>
-        <v>4.2769870000000001E-2</v>
+        <v>4.3745199999999998E-2</v>
       </c>
       <c r="BF16" s="4" cm="1">
         <f t="array" aca="1" ref="BF16" ca="1">_xll.YCP($B16,BF$2)</f>
-        <v>1.89924E-3</v>
+        <v>1.9134099999999999E-3</v>
       </c>
       <c r="BG16" s="4" cm="1">
         <f t="array" aca="1" ref="BG16" ca="1">_xll.YCP($B16,BG$2)</f>
-        <v>7.6244900000000003E-3</v>
+        <v>7.3481600000000003E-3</v>
       </c>
       <c r="BH16" s="4" cm="1">
         <f t="array" aca="1" ref="BH16" ca="1">_xll.YCP($B16,BH$2)</f>
-        <v>3.5127140000000001E-2</v>
+        <v>3.5140749999999998E-2</v>
       </c>
       <c r="BI16" s="4" cm="1">
         <f t="array" aca="1" ref="BI16" ca="1">_xll.YCP($B16,BI$2)</f>
-        <v>3.2836499999999998E-2</v>
+        <v>3.1760990000000003E-2</v>
       </c>
       <c r="BJ16" s="4" cm="1">
         <f t="array" aca="1" ref="BJ16" ca="1">_xll.YCP($B16,BJ$2)</f>
-        <v>0.17893597</v>
+        <v>0.17663075</v>
       </c>
       <c r="BK16" s="4" cm="1">
         <f t="array" aca="1" ref="BK16" ca="1">_xll.YCP($B16,BK$2)</f>
-        <v>0.30051875</v>
+        <v>0.30758725999999997</v>
       </c>
       <c r="BL16" s="4" cm="1">
         <f t="array" aca="1" ref="BL16" ca="1">_xll.YCP($B16,BL$2)</f>
-        <v>0.20380793</v>
+        <v>0.19570001000000001</v>
       </c>
       <c r="BM16" s="4" cm="1">
         <f t="array" aca="1" ref="BM16" ca="1">_xll.YCP($B16,BM$2)</f>
-        <v>8.3258990000000005E-2</v>
+        <v>8.3094730000000006E-2</v>
       </c>
       <c r="BN16" s="4" cm="1">
         <f t="array" aca="1" ref="BN16" ca="1">_xll.YCP($B16,BN$2)</f>
-        <v>0.11888911000000001</v>
+        <v>0.12111271999999999</v>
       </c>
       <c r="BO16" s="4" cm="1">
         <f t="array" aca="1" ref="BO16" ca="1">_xll.YCP($B16,BO$2)</f>
-        <v>6.3104679999999996E-2</v>
+        <v>6.4646159999999994E-2</v>
       </c>
       <c r="BP16" s="4" cm="1">
         <f t="array" aca="1" ref="BP16" ca="1">_xll.YCP($B16,BP$2)</f>
-        <v>1.6934069999999999E-2</v>
+        <v>1.6965500000000001E-2</v>
       </c>
       <c r="BQ16" s="4" cm="1">
         <f t="array" aca="1" ref="BQ16" ca="1">_xll.YCP($B16,BQ$2)</f>
-        <v>2.3900890000000001E-2</v>
+        <v>2.3210080000000001E-2</v>
       </c>
       <c r="BR16" s="4" cm="1">
         <f t="array" aca="1" ref="BR16" ca="1">_xll.YCP($B16,BR$2)</f>
-        <v>1.064962E-2</v>
+        <v>1.105279E-2</v>
       </c>
       <c r="BS16" s="4" cm="1">
         <f t="array" aca="1" ref="BS16" ca="1">_xll.YCP($B16,BS$2)</f>
-        <v>3.3725449999999997E-2</v>
+        <v>3.2667380000000003E-2</v>
       </c>
       <c r="BT16" s="4" cm="1">
         <f t="array" aca="1" ref="BT16" ca="1">_xll.YCP($B16,BT$2)</f>
-        <v>7.9898960000000005E-2</v>
+        <v>7.9196139999999998E-2</v>
       </c>
       <c r="BU16" s="4" cm="1">
         <f t="array" aca="1" ref="BU16" ca="1">_xll.YCP($B16,BU$2)</f>
-        <v>9.5558030000000002E-2</v>
+        <v>9.5177040000000004E-2</v>
       </c>
       <c r="BV16" s="4" cm="1">
         <f t="array" aca="1" ref="BV16" ca="1">_xll.YCP($B16,BV$2)</f>
-        <v>4.2467230000000002E-2</v>
+        <v>4.23078E-2</v>
       </c>
       <c r="BW16" s="4" cm="1">
         <f t="array" aca="1" ref="BW16" ca="1">_xll.YCP($B16,BW$2)</f>
-        <v>3.9176219999999998E-2</v>
+        <v>3.796223E-2</v>
       </c>
       <c r="BX16" s="4" cm="1">
         <f t="array" aca="1" ref="BX16" ca="1">_xll.YCP($B16,BX$2)</f>
-        <v>0.13444327</v>
+        <v>0.13669079000000001</v>
       </c>
       <c r="BY16" s="4" cm="1">
         <f t="array" aca="1" ref="BY16" ca="1">_xll.YCP($B16,BY$2)</f>
-        <v>7.8564490000000001E-2</v>
+        <v>7.9799819999999994E-2</v>
       </c>
       <c r="BZ16" s="4" cm="1">
         <f t="array" aca="1" ref="BZ16" ca="1">_xll.YCP($B16,BZ$2)</f>
-        <v>0.10982952999999999</v>
+        <v>0.11139483</v>
       </c>
       <c r="CA16" s="4" cm="1">
         <f t="array" aca="1" ref="CA16" ca="1">_xll.YCP($B16,CA$2)</f>
-        <v>2.5311569999999999E-2</v>
+        <v>2.5352800000000002E-2</v>
       </c>
       <c r="CB16" s="4" cm="1">
         <f t="array" aca="1" ref="CB16" ca="1">_xll.YCP($B16,CB$2)</f>
-        <v>0.32095804</v>
+        <v>0.32047779999999998</v>
       </c>
       <c r="CC16" s="4" cm="1">
         <f t="array" aca="1" ref="CC16" ca="1">_xll.YCP($B16,CC$2)</f>
-        <v>3.02791E-2</v>
+        <v>3.099756E-2</v>
       </c>
       <c r="CD16" s="4" cm="1">
         <f t="array" aca="1" ref="CD16" ca="1">_xll.YCP($B16,CD$2)</f>
-        <v>1.72327E-2</v>
+        <v>1.606142E-2</v>
       </c>
       <c r="CE16" s="4" cm="1">
         <f t="array" aca="1" ref="CE16" ca="1">_xll.YCP($B16,CE$2)</f>
-        <v>0.67889809999999995</v>
+        <v>0.67807779000000001</v>
       </c>
       <c r="CF16" s="4" cm="1">
         <f t="array" aca="1" ref="CF16" ca="1">_xll.YCP($B16,CF$2)</f>
-        <v>0.3033747</v>
+        <v>0.30535934999999997</v>
       </c>
       <c r="CG16" s="4" cm="1">
         <f t="array" aca="1" ref="CG16" ca="1">_xll.YCP($B16,CG$2)</f>
-        <v>8.2299999999999995E-5</v>
+        <v>8.2109999999999998E-5</v>
       </c>
       <c r="CH16" s="4" cm="1">
         <f t="array" aca="1" ref="CH16" ca="1">_xll.YCP($B16,CH$2)</f>
-        <v>4.384E-5</v>
+        <v>4.2979999999999998E-5</v>
       </c>
       <c r="CI16" s="4" cm="1">
         <f t="array" aca="1" ref="CI16" ca="1">_xll.YCP($B16,CI$2)</f>
-        <v>3.6834999999999998E-4</v>
+        <v>3.7631999999999997E-4</v>
       </c>
       <c r="CJ16" s="4" cm="1">
         <f t="array" aca="1" ref="CJ16" ca="1">_xll.YCP($B16,CJ$2)</f>
-        <v>1.8241980000000001E-2</v>
+        <v>1.8287009999999999E-2</v>
       </c>
       <c r="CK16" s="4" cm="1">
         <f t="array" aca="1" ref="CK16" ca="1">_xll.YCP($B16,CK$2)</f>
-        <v>0.51953411000000005</v>
+        <v>0.53004472999999996</v>
       </c>
       <c r="CL16" s="4" cm="1">
         <f t="array" aca="1" ref="CL16" ca="1">_xll.YCP($B16,CL$2)</f>
-        <v>0.14791149000000001</v>
+        <v>0.1489144</v>
       </c>
       <c r="CM16" s="4" cm="1">
         <f t="array" aca="1" ref="CM16" ca="1">_xll.YCP($B16,CM$2)</f>
-        <v>0.19165537999999999</v>
+        <v>0.19237990999999999</v>
       </c>
       <c r="CN16" s="4" cm="1">
         <f t="array" aca="1" ref="CN16" ca="1">_xll.YCP($B16,CN$2)</f>
-        <v>6.6494979999999995E-2</v>
+        <v>6.6470280000000007E-2</v>
       </c>
       <c r="CO16" s="4" cm="1">
         <f t="array" aca="1" ref="CO16" ca="1">_xll.YCP($B16,CO$2)</f>
-        <v>3.7005950000000003E-2</v>
+        <v>3.6993770000000002E-2</v>
       </c>
       <c r="CP16" s="4" cm="1">
         <f t="array" aca="1" ref="CP16" ca="1">_xll.YCP($B16,CP$2)</f>
-        <v>4.0246500000000003E-3</v>
+        <v>4.0233300000000003E-3</v>
       </c>
       <c r="CQ16" s="4" cm="1">
         <f t="array" aca="1" ref="CQ16" ca="1">_xll.YCP($B16,CQ$2)</f>
-        <v>2.2417600000000002E-3</v>
+        <v>2.2410300000000002E-3</v>
       </c>
       <c r="CR16" s="4" cm="1">
         <f t="array" aca="1" ref="CR16" ca="1">_xll.YCP($B16,CR$2)</f>
-        <v>3.2356509999999998E-2</v>
+        <v>3.2716120000000001E-2</v>
       </c>
       <c r="CS16" s="4" cm="1">
         <f t="array" aca="1" ref="CS16" ca="1">_xll.YCP($B16,CS$2)</f>
-        <v>4.7369099999999997E-2</v>
+        <v>4.7179449999999998E-2</v>
       </c>
       <c r="CT16" s="4" cm="1">
         <f t="array" aca="1" ref="CT16" ca="1">_xll.YCP($B16,CT$2)</f>
-        <v>0.89159305</v>
+        <v>0.89127979999999996</v>
       </c>
       <c r="CU16" s="4" cm="1">
         <f t="array" aca="1" ref="CU16" ca="1">_xll.YCP($B16,CU$2)</f>
-        <v>2.136499E-2</v>
+        <v>2.1895020000000001E-2</v>
       </c>
       <c r="CV16" s="4" cm="1">
         <f t="array" aca="1" ref="CV16" ca="1">_xll.YCP($B16,CV$2)</f>
-        <v>5.7946500000000001E-3</v>
+        <v>5.7727100000000003E-3</v>
       </c>
       <c r="CW16" s="4" cm="1">
         <f t="array" aca="1" ref="CW16" ca="1">_xll.YCP($B16,CW$2)</f>
-        <v>1.1951799999999999E-3</v>
+        <v>1.60604E-3</v>
       </c>
       <c r="CX16" s="3" cm="1">
         <f t="array" aca="1" ref="CX16" ca="1">_xll.YCP($B16,CX$2)</f>
-        <v>5.657</v>
+        <v>5.6329890000000002</v>
       </c>
       <c r="CY16" s="20" cm="1">
         <f t="array" aca="1" ref="CY16" ca="1">_xll.YCP($B16,CY$2)</f>
-        <v>6.8404499999999997</v>
+        <v>6.8314779999999997</v>
       </c>
       <c r="CZ16" s="4" cm="1">
         <f t="array" aca="1" ref="CZ16" ca="1">_xll.YCP($B16,CZ$2)</f>
-        <v>4.8641589999999998E-2</v>
+        <v>4.9130279999999998E-2</v>
       </c>
       <c r="DA16" s="4" cm="1">
         <f t="array" aca="1" ref="DA16" ca="1">_xll.YCP($B16,DA$2)</f>
-        <v>4.4198630000000003E-2</v>
-      </c>
-      <c r="DB16" s="4" cm="1">
+        <v>4.4393630000000003E-2</v>
+      </c>
+      <c r="DB16" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="DB16" ca="1">_xll.YCP($B16,DB$2)</f>
-        <v>6.0989700000000001E-2</v>
+        <v>ERR: NO DATA</v>
       </c>
       <c r="DC16" s="4" cm="1">
         <f t="array" aca="1" ref="DC16" ca="1">_xll.YCP($B16,DC$2)</f>
-        <v>0.52571292999999997</v>
+        <v>0.52344155000000003</v>
       </c>
       <c r="DD16" s="4" cm="1">
         <f t="array" aca="1" ref="DD16" ca="1">_xll.YCP($B16,DD$2)</f>
-        <v>0.46105571000000001</v>
+        <v>0.46256908000000002</v>
       </c>
       <c r="DE16" s="4" cm="1">
         <f t="array" aca="1" ref="DE16" ca="1">_xll.YCP($B16,DE$2)</f>
@@ -8115,55 +8115,55 @@
       </c>
       <c r="DF16" s="4" cm="1">
         <f t="array" aca="1" ref="DF16" ca="1">_xll.YCP($B16,DF$2)</f>
-        <v>7.1542899999999998E-3</v>
+        <v>7.4634599999999999E-3</v>
       </c>
       <c r="DG16" s="4" cm="1">
         <f t="array" aca="1" ref="DG16" ca="1">_xll.YCP($B16,DG$2)</f>
-        <v>6.0770599999999996E-3</v>
+        <v>6.5259100000000002E-3</v>
       </c>
       <c r="DH16" s="4" cm="1">
         <f t="array" aca="1" ref="DH16" ca="1">_xll.YCP($B16,DH$2)</f>
-        <v>0.67889809999999995</v>
+        <v>0.67807779000000001</v>
       </c>
       <c r="DI16" s="4" cm="1">
         <f t="array" aca="1" ref="DI16" ca="1">_xll.YCP($B16,DI$2)</f>
-        <v>0.3033747</v>
+        <v>0.30535934999999997</v>
       </c>
       <c r="DJ16" s="4" cm="1">
         <f t="array" aca="1" ref="DJ16" ca="1">_xll.YCP($B16,DJ$2)</f>
-        <v>1.72327E-2</v>
+        <v>1.606142E-2</v>
       </c>
       <c r="DK16" s="4" cm="1">
         <f t="array" aca="1" ref="DK16" ca="1">_xll.YCP($B16,DK$2)</f>
-        <v>5.7759489999999997E-2</v>
+        <v>5.6507689999999999E-2</v>
       </c>
       <c r="DL16" s="4" cm="1">
         <f t="array" aca="1" ref="DL16" ca="1">_xll.YCP($B16,DL$2)</f>
-        <v>0.46045363</v>
+        <v>0.45822123999999997</v>
       </c>
       <c r="DM16" s="4" cm="1">
         <f t="array" aca="1" ref="DM16" ca="1">_xll.YCP($B16,DM$2)</f>
-        <v>0.14343433999999999</v>
+        <v>0.14531181000000001</v>
       </c>
       <c r="DN16" s="4" cm="1">
         <f t="array" aca="1" ref="DN16" ca="1">_xll.YCP($B16,DN$2)</f>
-        <v>7.292179E-2</v>
+        <v>7.2487460000000004E-2</v>
       </c>
       <c r="DO16" s="4" cm="1">
         <f t="array" aca="1" ref="DO16" ca="1">_xll.YCP($B16,DO$2)</f>
-        <v>0.26633648999999998</v>
+        <v>0.27168354</v>
       </c>
       <c r="DP16" s="4" cm="1">
         <f t="array" aca="1" ref="DP16" ca="1">_xll.YCP($B16,DP$2)</f>
-        <v>3.2641719999999999E-2</v>
+        <v>3.2825649999999998E-2</v>
       </c>
       <c r="DQ16" s="4" cm="1">
         <f t="array" aca="1" ref="DQ16" ca="1">_xll.YCP($B16,DQ$2)</f>
-        <v>6.0770599999999996E-3</v>
+        <v>6.5259100000000002E-3</v>
       </c>
       <c r="DR16" s="4" cm="1">
         <f t="array" aca="1" ref="DR16" ca="1">_xll.YCP($B16,DR$2)</f>
-        <v>0.94224050999999998</v>
+        <v>0.94349231</v>
       </c>
     </row>
     <row r="17" spans="2:122" x14ac:dyDescent="0.45">
@@ -8192,11 +8192,11 @@
       </c>
       <c r="H17" s="4" cm="1">
         <f t="array" aca="1" ref="H17" ca="1">_xll.YCP($B17,H$2)</f>
-        <v>3.9048000000000002E-4</v>
+        <v>3.9110000000000002E-4</v>
       </c>
       <c r="I17" s="4" cm="1">
         <f t="array" aca="1" ref="I17" ca="1">_xll.YCP($B17,I$2)</f>
-        <v>1.8185E-2</v>
+        <v>1.8471999999999999E-2</v>
       </c>
       <c r="J17" s="5" cm="1">
         <f t="array" aca="1" ref="J17" ca="1">_xll.YCP($B17,J$2)</f>
@@ -8204,23 +8204,23 @@
       </c>
       <c r="K17" s="4" cm="1">
         <f t="array" aca="1" ref="K17" ca="1">_xll.YCP($B17,K$2)</f>
-        <v>0.14588788999999999</v>
+        <v>0.14651924999999999</v>
       </c>
       <c r="L17" s="4" cm="1">
         <f t="array" aca="1" ref="L17" ca="1">_xll.YCP($B17,L$2)</f>
-        <v>1.6139000000000001E-2</v>
+        <v>-8.4480000000000006E-3</v>
       </c>
       <c r="M17" s="4" cm="1">
         <f t="array" aca="1" ref="M17" ca="1">_xll.YCP($B17,M$2)</f>
-        <v>7.2958999999999996E-2</v>
+        <v>2.4275000000000001E-2</v>
       </c>
       <c r="N17" s="4" cm="1">
         <f t="array" aca="1" ref="N17" ca="1">_xll.YCP($B17,N$2)</f>
-        <v>8.9796000000000001E-2</v>
+        <v>7.9663999999999999E-2</v>
       </c>
       <c r="O17" s="4" cm="1">
         <f t="array" aca="1" ref="O17" ca="1">_xll.YCP($B17,O$2)</f>
-        <v>0.16997399999999999</v>
+        <v>0.147649</v>
       </c>
       <c r="P17" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P17" ca="1">_xll.YCP($B17,P$2)</f>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="R17" s="4" cm="1">
         <f t="array" aca="1" ref="R17" ca="1">_xll.YCP($B17,R$2)</f>
-        <v>0.131379</v>
+        <v>0.11996800000000001</v>
       </c>
       <c r="S17" s="3" cm="1">
         <f t="array" aca="1" ref="S17" ca="1">_xll.YCP($B17,S$2)</f>
@@ -8376,159 +8376,159 @@
       </c>
       <c r="BB17" s="4" cm="1">
         <f t="array" aca="1" ref="BB17" ca="1">_xll.YCP($B17,BB$2)</f>
-        <v>0.83254382999999998</v>
+        <v>0.83269263999999998</v>
       </c>
       <c r="BC17" s="4" cm="1">
         <f t="array" aca="1" ref="BC17" ca="1">_xll.YCP($B17,BC$2)</f>
-        <v>8.7556000000000005E-3</v>
+        <v>8.6355300000000006E-3</v>
       </c>
       <c r="BD17" s="4" cm="1">
         <f t="array" aca="1" ref="BD17" ca="1">_xll.YCP($B17,BD$2)</f>
-        <v>1.322832E-2</v>
+        <v>1.3225550000000001E-2</v>
       </c>
       <c r="BE17" s="4" cm="1">
         <f t="array" aca="1" ref="BE17" ca="1">_xll.YCP($B17,BE$2)</f>
-        <v>4.3025149999999998E-2</v>
+        <v>4.4017889999999997E-2</v>
       </c>
       <c r="BF17" s="4" cm="1">
         <f t="array" aca="1" ref="BF17" ca="1">_xll.YCP($B17,BF$2)</f>
-        <v>1.6993900000000001E-3</v>
+        <v>1.7147499999999999E-3</v>
       </c>
       <c r="BG17" s="4" cm="1">
         <f t="array" aca="1" ref="BG17" ca="1">_xll.YCP($B17,BG$2)</f>
-        <v>7.41598E-3</v>
+        <v>7.1413900000000001E-3</v>
       </c>
       <c r="BH17" s="4" cm="1">
         <f t="array" aca="1" ref="BH17" ca="1">_xll.YCP($B17,BH$2)</f>
-        <v>3.6705300000000003E-2</v>
+        <v>3.6631249999999997E-2</v>
       </c>
       <c r="BI17" s="4" cm="1">
         <f t="array" aca="1" ref="BI17" ca="1">_xll.YCP($B17,BI$2)</f>
-        <v>3.3327349999999999E-2</v>
+        <v>3.2247390000000001E-2</v>
       </c>
       <c r="BJ17" s="4" cm="1">
         <f t="array" aca="1" ref="BJ17" ca="1">_xll.YCP($B17,BJ$2)</f>
-        <v>0.17729929</v>
+        <v>0.17524408</v>
       </c>
       <c r="BK17" s="4" cm="1">
         <f t="array" aca="1" ref="BK17" ca="1">_xll.YCP($B17,BK$2)</f>
-        <v>0.30039378999999999</v>
+        <v>0.30680128000000001</v>
       </c>
       <c r="BL17" s="4" cm="1">
         <f t="array" aca="1" ref="BL17" ca="1">_xll.YCP($B17,BL$2)</f>
-        <v>0.20120183999999999</v>
+        <v>0.19350186</v>
       </c>
       <c r="BM17" s="4" cm="1">
         <f t="array" aca="1" ref="BM17" ca="1">_xll.YCP($B17,BM$2)</f>
-        <v>8.4238750000000001E-2</v>
+        <v>8.401256E-2</v>
       </c>
       <c r="BN17" s="4" cm="1">
         <f t="array" aca="1" ref="BN17" ca="1">_xll.YCP($B17,BN$2)</f>
-        <v>0.12071214</v>
+        <v>0.12292384000000001</v>
       </c>
       <c r="BO17" s="4" cm="1">
         <f t="array" aca="1" ref="BO17" ca="1">_xll.YCP($B17,BO$2)</f>
-        <v>6.3764230000000005E-2</v>
+        <v>6.5398049999999999E-2</v>
       </c>
       <c r="BP17" s="4" cm="1">
         <f t="array" aca="1" ref="BP17" ca="1">_xll.YCP($B17,BP$2)</f>
-        <v>1.7219709999999999E-2</v>
+        <v>1.7258389999999998E-2</v>
       </c>
       <c r="BQ17" s="4" cm="1">
         <f t="array" aca="1" ref="BQ17" ca="1">_xll.YCP($B17,BQ$2)</f>
-        <v>2.437539E-2</v>
+        <v>2.3643299999999999E-2</v>
       </c>
       <c r="BR17" s="4" cm="1">
         <f t="array" aca="1" ref="BR17" ca="1">_xll.YCP($B17,BR$2)</f>
-        <v>1.079487E-2</v>
+        <v>1.121663E-2</v>
       </c>
       <c r="BS17" s="4" cm="1">
         <f t="array" aca="1" ref="BS17" ca="1">_xll.YCP($B17,BS$2)</f>
-        <v>3.2746039999999997E-2</v>
+        <v>3.178537E-2</v>
       </c>
       <c r="BT17" s="4" cm="1">
         <f t="array" aca="1" ref="BT17" ca="1">_xll.YCP($B17,BT$2)</f>
-        <v>8.0583989999999994E-2</v>
+        <v>7.9903779999999994E-2</v>
       </c>
       <c r="BU17" s="4" cm="1">
         <f t="array" aca="1" ref="BU17" ca="1">_xll.YCP($B17,BU$2)</f>
-        <v>9.5777420000000002E-2</v>
+        <v>9.5533229999999997E-2</v>
       </c>
       <c r="BV17" s="4" cm="1">
         <f t="array" aca="1" ref="BV17" ca="1">_xll.YCP($B17,BV$2)</f>
-        <v>4.2468819999999997E-2</v>
+        <v>4.2313389999999999E-2</v>
       </c>
       <c r="BW17" s="4" cm="1">
         <f t="array" aca="1" ref="BW17" ca="1">_xll.YCP($B17,BW$2)</f>
-        <v>3.9175590000000003E-2</v>
+        <v>3.8012120000000003E-2</v>
       </c>
       <c r="BX17" s="4" cm="1">
         <f t="array" aca="1" ref="BX17" ca="1">_xll.YCP($B17,BX$2)</f>
-        <v>0.13264055</v>
+        <v>0.13480397</v>
       </c>
       <c r="BY17" s="4" cm="1">
         <f t="array" aca="1" ref="BY17" ca="1">_xll.YCP($B17,BY$2)</f>
-        <v>7.9261330000000005E-2</v>
+        <v>8.0510090000000006E-2</v>
       </c>
       <c r="BZ17" s="4" cm="1">
         <f t="array" aca="1" ref="BZ17" ca="1">_xll.YCP($B17,BZ$2)</f>
-        <v>0.10979434</v>
+        <v>0.11142139</v>
       </c>
       <c r="CA17" s="4" cm="1">
         <f t="array" aca="1" ref="CA17" ca="1">_xll.YCP($B17,CA$2)</f>
-        <v>2.5504929999999999E-2</v>
+        <v>2.5561670000000002E-2</v>
       </c>
       <c r="CB17" s="4" cm="1">
         <f t="array" aca="1" ref="CB17" ca="1">_xll.YCP($B17,CB$2)</f>
-        <v>0.32252134999999998</v>
+        <v>0.32163275000000002</v>
       </c>
       <c r="CC17" s="4" cm="1">
         <f t="array" aca="1" ref="CC17" ca="1">_xll.YCP($B17,CC$2)</f>
-        <v>3.0336180000000001E-2</v>
+        <v>3.1084090000000002E-2</v>
       </c>
       <c r="CD17" s="4" cm="1">
         <f t="array" aca="1" ref="CD17" ca="1">_xll.YCP($B17,CD$2)</f>
-        <v>1.5304969999999999E-2</v>
+        <v>1.4519839999999999E-2</v>
       </c>
       <c r="CE17" s="4" cm="1">
         <f t="array" aca="1" ref="CE17" ca="1">_xll.YCP($B17,CE$2)</f>
-        <v>0.81167840999999996</v>
+        <v>0.81127987999999995</v>
       </c>
       <c r="CF17" s="4" cm="1">
         <f t="array" aca="1" ref="CF17" ca="1">_xll.YCP($B17,CF$2)</f>
-        <v>0.17250834000000001</v>
+        <v>0.17368401</v>
       </c>
       <c r="CG17" s="4" cm="1">
         <f t="array" aca="1" ref="CG17" ca="1">_xll.YCP($B17,CG$2)</f>
-        <v>5.3109999999999998E-5</v>
+        <v>5.3029999999999999E-5</v>
       </c>
       <c r="CH17" s="4" cm="1">
         <f t="array" aca="1" ref="CH17" ca="1">_xll.YCP($B17,CH$2)</f>
-        <v>2.6230000000000001E-5</v>
+        <v>2.5170000000000001E-5</v>
       </c>
       <c r="CI17" s="4" cm="1">
         <f t="array" aca="1" ref="CI17" ca="1">_xll.YCP($B17,CI$2)</f>
-        <v>4.2893E-4</v>
+        <v>4.3804E-4</v>
       </c>
       <c r="CJ17" s="4" cm="1">
         <f t="array" aca="1" ref="CJ17" ca="1">_xll.YCP($B17,CJ$2)</f>
-        <v>2.079897E-2</v>
+        <v>2.0849349999999999E-2</v>
       </c>
       <c r="CK17" s="4" cm="1">
         <f t="array" aca="1" ref="CK17" ca="1">_xll.YCP($B17,CK$2)</f>
-        <v>0.58377937999999996</v>
+        <v>0.59573860999999995</v>
       </c>
       <c r="CL17" s="4" cm="1">
         <f t="array" aca="1" ref="CL17" ca="1">_xll.YCP($B17,CL$2)</f>
-        <v>0.16864434</v>
+        <v>0.16977998999999999</v>
       </c>
       <c r="CM17" s="4" cm="1">
         <f t="array" aca="1" ref="CM17" ca="1">_xll.YCP($B17,CM$2)</f>
-        <v>0.21165655</v>
+        <v>0.21247509000000001</v>
       </c>
       <c r="CN17" s="4" cm="1">
         <f t="array" aca="1" ref="CN17" ca="1">_xll.YCP($B17,CN$2)</f>
-        <v>8.7852000000000004E-4</v>
+        <v>8.7498999999999997E-4</v>
       </c>
       <c r="CO17" s="4" cm="1">
         <f t="array" aca="1" ref="CO17" ca="1">_xll.YCP($B17,CO$2)</f>
@@ -8548,39 +8548,39 @@
       </c>
       <c r="CS17" s="4" cm="1">
         <f t="array" aca="1" ref="CS17" ca="1">_xll.YCP($B17,CS$2)</f>
-        <v>5.5199999999999997E-3</v>
+        <v>4.8000500000000001E-3</v>
       </c>
       <c r="CT17" s="4" cm="1">
         <f t="array" aca="1" ref="CT17" ca="1">_xll.YCP($B17,CT$2)</f>
-        <v>0.96539808000000005</v>
+        <v>0.96501323999999999</v>
       </c>
       <c r="CU17" s="4" cm="1">
         <f t="array" aca="1" ref="CU17" ca="1">_xll.YCP($B17,CU$2)</f>
-        <v>2.2884669999999999E-2</v>
+        <v>2.34884E-2</v>
       </c>
       <c r="CV17" s="4" cm="1">
         <f t="array" aca="1" ref="CV17" ca="1">_xll.YCP($B17,CV$2)</f>
-        <v>5.0338800000000001E-3</v>
+        <v>5.0091500000000004E-3</v>
       </c>
       <c r="CW17" s="4" cm="1">
         <f t="array" aca="1" ref="CW17" ca="1">_xll.YCP($B17,CW$2)</f>
-        <v>1.1199999999999999E-3</v>
+        <v>1.5900199999999999E-3</v>
       </c>
       <c r="CX17" s="3" cm="1">
         <f t="array" aca="1" ref="CX17" ca="1">_xll.YCP($B17,CX$2)</f>
-        <v>6.06</v>
+        <v>6.03</v>
       </c>
       <c r="CY17" s="20" cm="1">
         <f t="array" aca="1" ref="CY17" ca="1">_xll.YCP($B17,CY$2)</f>
-        <v>7.31</v>
+        <v>7.3</v>
       </c>
       <c r="CZ17" s="4" cm="1">
         <f t="array" aca="1" ref="CZ17" ca="1">_xll.YCP($B17,CZ$2)</f>
-        <v>4.6300000000000001E-2</v>
+        <v>4.6800000000000001E-2</v>
       </c>
       <c r="DA17" s="4" cm="1">
         <f t="array" aca="1" ref="DA17" ca="1">_xll.YCP($B17,DA$2)</f>
-        <v>4.1854000000000002E-2</v>
+        <v>4.2068099999999997E-2</v>
       </c>
       <c r="DB17" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="DB17" ca="1">_xll.YCP($B17,DB$2)</f>
@@ -8588,11 +8588,11 @@
       </c>
       <c r="DC17" s="4" cm="1">
         <f t="array" aca="1" ref="DC17" ca="1">_xll.YCP($B17,DC$2)</f>
-        <v>0.59094402999999995</v>
+        <v>0.58832952999999999</v>
       </c>
       <c r="DD17" s="4" cm="1">
         <f t="array" aca="1" ref="DD17" ca="1">_xll.YCP($B17,DD$2)</f>
-        <v>0.39600263000000002</v>
+        <v>0.39775312000000002</v>
       </c>
       <c r="DE17" s="4" cm="1">
         <f t="array" aca="1" ref="DE17" ca="1">_xll.YCP($B17,DE$2)</f>
@@ -8600,55 +8600,55 @@
       </c>
       <c r="DF17" s="4" cm="1">
         <f t="array" aca="1" ref="DF17" ca="1">_xll.YCP($B17,DF$2)</f>
-        <v>8.1538200000000009E-3</v>
+        <v>8.5058200000000007E-3</v>
       </c>
       <c r="DG17" s="4" cm="1">
         <f t="array" aca="1" ref="DG17" ca="1">_xll.YCP($B17,DG$2)</f>
-        <v>4.89953E-3</v>
+        <v>5.4115200000000004E-3</v>
       </c>
       <c r="DH17" s="4" cm="1">
         <f t="array" aca="1" ref="DH17" ca="1">_xll.YCP($B17,DH$2)</f>
-        <v>0.81167840999999996</v>
+        <v>0.81127987999999995</v>
       </c>
       <c r="DI17" s="4" cm="1">
         <f t="array" aca="1" ref="DI17" ca="1">_xll.YCP($B17,DI$2)</f>
-        <v>0.17250834000000001</v>
+        <v>0.17368401</v>
       </c>
       <c r="DJ17" s="4" cm="1">
         <f t="array" aca="1" ref="DJ17" ca="1">_xll.YCP($B17,DJ$2)</f>
-        <v>1.5304969999999999E-2</v>
+        <v>1.4519839999999999E-2</v>
       </c>
       <c r="DK17" s="4" cm="1">
         <f t="array" aca="1" ref="DK17" ca="1">_xll.YCP($B17,DK$2)</f>
-        <v>5.2705960000000003E-2</v>
+        <v>5.1716730000000002E-2</v>
       </c>
       <c r="DL17" s="4" cm="1">
         <f t="array" aca="1" ref="DL17" ca="1">_xll.YCP($B17,DL$2)</f>
-        <v>0.54731291999999998</v>
+        <v>0.5450526</v>
       </c>
       <c r="DM17" s="4" cm="1">
         <f t="array" aca="1" ref="DM17" ca="1">_xll.YCP($B17,DM$2)</f>
-        <v>0.17332507999999999</v>
+        <v>0.17577119999999999</v>
       </c>
       <c r="DN17" s="4" cm="1">
         <f t="array" aca="1" ref="DN17" ca="1">_xll.YCP($B17,DN$2)</f>
-        <v>8.881899E-2</v>
+        <v>8.8347480000000006E-2</v>
       </c>
       <c r="DO17" s="4" cm="1">
         <f t="array" aca="1" ref="DO17" ca="1">_xll.YCP($B17,DO$2)</f>
-        <v>0.17003051999999999</v>
+        <v>0.17361536999999999</v>
       </c>
       <c r="DP17" s="4" cm="1">
         <f t="array" aca="1" ref="DP17" ca="1">_xll.YCP($B17,DP$2)</f>
-        <v>1.5166999999999999E-4</v>
+        <v>1.5208999999999999E-4</v>
       </c>
       <c r="DQ17" s="4" cm="1">
         <f t="array" aca="1" ref="DQ17" ca="1">_xll.YCP($B17,DQ$2)</f>
-        <v>4.89953E-3</v>
+        <v>5.4115200000000004E-3</v>
       </c>
       <c r="DR17" s="4" cm="1">
         <f t="array" aca="1" ref="DR17" ca="1">_xll.YCP($B17,DR$2)</f>
-        <v>0.94729403999999995</v>
+        <v>0.94828327000000001</v>
       </c>
     </row>
     <row r="18" spans="2:122" x14ac:dyDescent="0.45">
@@ -8677,11 +8677,11 @@
       </c>
       <c r="H18" s="4" cm="1">
         <f t="array" aca="1" ref="H18" ca="1">_xll.YCP($B18,H$2)</f>
-        <v>3.4345000000000003E-4</v>
+        <v>3.4391000000000001E-4</v>
       </c>
       <c r="I18" s="4" cm="1">
         <f t="array" aca="1" ref="I18" ca="1">_xll.YCP($B18,I$2)</f>
-        <v>1.3021E-2</v>
+        <v>1.3278999999999999E-2</v>
       </c>
       <c r="J18" s="5" cm="1">
         <f t="array" aca="1" ref="J18" ca="1">_xll.YCP($B18,J$2)</f>
@@ -8689,23 +8689,23 @@
       </c>
       <c r="K18" s="4" cm="1">
         <f t="array" aca="1" ref="K18" ca="1">_xll.YCP($B18,K$2)</f>
-        <v>5.9298539999999997E-2</v>
+        <v>5.952284E-2</v>
       </c>
       <c r="L18" s="4" cm="1">
         <f t="array" aca="1" ref="L18" ca="1">_xll.YCP($B18,L$2)</f>
-        <v>1.9612999999999998E-2</v>
+        <v>-8.3549999999999996E-3</v>
       </c>
       <c r="M18" s="4" cm="1">
         <f t="array" aca="1" ref="M18" ca="1">_xll.YCP($B18,M$2)</f>
-        <v>9.1927999999999996E-2</v>
+        <v>3.1384000000000002E-2</v>
       </c>
       <c r="N18" s="4" cm="1">
         <f t="array" aca="1" ref="N18" ca="1">_xll.YCP($B18,N$2)</f>
-        <v>0.11292199999999999</v>
+        <v>0.101242</v>
       </c>
       <c r="O18" s="4" cm="1">
         <f t="array" aca="1" ref="O18" ca="1">_xll.YCP($B18,O$2)</f>
-        <v>0.205737</v>
+        <v>0.17913299999999999</v>
       </c>
       <c r="P18" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P18" ca="1">_xll.YCP($B18,P$2)</f>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="R18" s="4" cm="1">
         <f t="array" aca="1" ref="R18" ca="1">_xll.YCP($B18,R$2)</f>
-        <v>0.15542500000000001</v>
+        <v>0.142066</v>
       </c>
       <c r="S18" s="3" cm="1">
         <f t="array" aca="1" ref="S18" ca="1">_xll.YCP($B18,S$2)</f>
@@ -8861,123 +8861,123 @@
       </c>
       <c r="BB18" s="4" cm="1">
         <f t="array" aca="1" ref="BB18" ca="1">_xll.YCP($B18,BB$2)</f>
-        <v>0.81578552999999998</v>
+        <v>0.81564585000000001</v>
       </c>
       <c r="BC18" s="4" cm="1">
         <f t="array" aca="1" ref="BC18" ca="1">_xll.YCP($B18,BC$2)</f>
-        <v>7.8137199999999997E-3</v>
+        <v>7.57064E-3</v>
       </c>
       <c r="BD18" s="4" cm="1">
         <f t="array" aca="1" ref="BD18" ca="1">_xll.YCP($B18,BD$2)</f>
-        <v>1.302329E-2</v>
+        <v>1.296951E-2</v>
       </c>
       <c r="BE18" s="4" cm="1">
         <f t="array" aca="1" ref="BE18" ca="1">_xll.YCP($B18,BE$2)</f>
-        <v>4.742499E-2</v>
+        <v>4.8430090000000002E-2</v>
       </c>
       <c r="BF18" s="4" cm="1">
         <f t="array" aca="1" ref="BF18" ca="1">_xll.YCP($B18,BF$2)</f>
-        <v>1.5572800000000001E-3</v>
+        <v>1.57661E-3</v>
       </c>
       <c r="BG18" s="4" cm="1">
         <f t="array" aca="1" ref="BG18" ca="1">_xll.YCP($B18,BG$2)</f>
-        <v>8.5288399999999993E-3</v>
+        <v>8.2115499999999998E-3</v>
       </c>
       <c r="BH18" s="4" cm="1">
         <f t="array" aca="1" ref="BH18" ca="1">_xll.YCP($B18,BH$2)</f>
-        <v>4.333352E-2</v>
+        <v>4.3313270000000001E-2</v>
       </c>
       <c r="BI18" s="4" cm="1">
         <f t="array" aca="1" ref="BI18" ca="1">_xll.YCP($B18,BI$2)</f>
-        <v>3.8982759999999998E-2</v>
+        <v>3.7710069999999998E-2</v>
       </c>
       <c r="BJ18" s="4" cm="1">
         <f t="array" aca="1" ref="BJ18" ca="1">_xll.YCP($B18,BJ$2)</f>
-        <v>0.17832391</v>
+        <v>0.17628880999999999</v>
       </c>
       <c r="BK18" s="4" cm="1">
         <f t="array" aca="1" ref="BK18" ca="1">_xll.YCP($B18,BK$2)</f>
-        <v>0.30252813000000001</v>
+        <v>0.30873937000000001</v>
       </c>
       <c r="BL18" s="4" cm="1">
         <f t="array" aca="1" ref="BL18" ca="1">_xll.YCP($B18,BL$2)</f>
-        <v>0.20188906000000001</v>
+        <v>0.19444359</v>
       </c>
       <c r="BM18" s="4" cm="1">
         <f t="array" aca="1" ref="BM18" ca="1">_xll.YCP($B18,BM$2)</f>
-        <v>8.3495390000000003E-2</v>
+        <v>8.3285509999999993E-2</v>
       </c>
       <c r="BN18" s="4" cm="1">
         <f t="array" aca="1" ref="BN18" ca="1">_xll.YCP($B18,BN$2)</f>
-        <v>0.11968054</v>
+        <v>0.12183537</v>
       </c>
       <c r="BO18" s="4" cm="1">
         <f t="array" aca="1" ref="BO18" ca="1">_xll.YCP($B18,BO$2)</f>
-        <v>6.2903009999999995E-2</v>
+        <v>6.4485200000000006E-2</v>
       </c>
       <c r="BP18" s="4" cm="1">
         <f t="array" aca="1" ref="BP18" ca="1">_xll.YCP($B18,BP$2)</f>
-        <v>1.683314E-2</v>
+        <v>1.68711E-2</v>
       </c>
       <c r="BQ18" s="4" cm="1">
         <f t="array" aca="1" ref="BQ18" ca="1">_xll.YCP($B18,BQ$2)</f>
-        <v>2.3841950000000001E-2</v>
+        <v>2.313722E-2</v>
       </c>
       <c r="BR18" s="4" cm="1">
         <f t="array" aca="1" ref="BR18" ca="1">_xll.YCP($B18,BR$2)</f>
-        <v>1.0504869999999999E-2</v>
+        <v>1.0913829999999999E-2</v>
       </c>
       <c r="BS18" s="4" cm="1">
         <f t="array" aca="1" ref="BS18" ca="1">_xll.YCP($B18,BS$2)</f>
-        <v>3.2406339999999999E-2</v>
+        <v>3.146798E-2</v>
       </c>
       <c r="BT18" s="4" cm="1">
         <f t="array" aca="1" ref="BT18" ca="1">_xll.YCP($B18,BT$2)</f>
-        <v>8.1219459999999993E-2</v>
+        <v>8.0558119999999997E-2</v>
       </c>
       <c r="BU18" s="4" cm="1">
         <f t="array" aca="1" ref="BU18" ca="1">_xll.YCP($B18,BU$2)</f>
-        <v>9.5846650000000005E-2</v>
+        <v>9.5596600000000004E-2</v>
       </c>
       <c r="BV18" s="4" cm="1">
         <f t="array" aca="1" ref="BV18" ca="1">_xll.YCP($B18,BV$2)</f>
-        <v>4.2489739999999998E-2</v>
+        <v>4.2336800000000001E-2</v>
       </c>
       <c r="BW18" s="4" cm="1">
         <f t="array" aca="1" ref="BW18" ca="1">_xll.YCP($B18,BW$2)</f>
-        <v>3.8946719999999997E-2</v>
+        <v>3.7813920000000001E-2</v>
       </c>
       <c r="BX18" s="4" cm="1">
         <f t="array" aca="1" ref="BX18" ca="1">_xll.YCP($B18,BX$2)</f>
-        <v>0.13216469</v>
+        <v>0.13427296999999999</v>
       </c>
       <c r="BY18" s="4" cm="1">
         <f t="array" aca="1" ref="BY18" ca="1">_xll.YCP($B18,BY$2)</f>
-        <v>7.9284950000000007E-2</v>
+        <v>8.0497310000000002E-2</v>
       </c>
       <c r="BZ18" s="4" cm="1">
         <f t="array" aca="1" ref="BZ18" ca="1">_xll.YCP($B18,BZ$2)</f>
-        <v>0.10890012</v>
+        <v>0.11048188</v>
       </c>
       <c r="CA18" s="4" cm="1">
         <f t="array" aca="1" ref="CA18" ca="1">_xll.YCP($B18,CA$2)</f>
-        <v>2.5280569999999999E-2</v>
+        <v>2.5335400000000001E-2</v>
       </c>
       <c r="CB18" s="4" cm="1">
         <f t="array" aca="1" ref="CB18" ca="1">_xll.YCP($B18,CB$2)</f>
-        <v>0.32433448999999998</v>
+        <v>0.32349468999999997</v>
       </c>
       <c r="CC18" s="4" cm="1">
         <f t="array" aca="1" ref="CC18" ca="1">_xll.YCP($B18,CC$2)</f>
-        <v>3.0065359999999999E-2</v>
+        <v>3.0789839999999999E-2</v>
       </c>
       <c r="CD18" s="4" cm="1">
         <f t="array" aca="1" ref="CD18" ca="1">_xll.YCP($B18,CD$2)</f>
-        <v>1.528906E-2</v>
+        <v>1.470481E-2</v>
       </c>
       <c r="CE18" s="4" cm="1">
         <f t="array" aca="1" ref="CE18" ca="1">_xll.YCP($B18,CE$2)</f>
-        <v>0.98417228999999995</v>
+        <v>0.98474634000000005</v>
       </c>
       <c r="CF18" s="4" cm="1">
         <f t="array" aca="1" ref="CF18" ca="1">_xll.YCP($B18,CF$2)</f>
@@ -8989,11 +8989,11 @@
       </c>
       <c r="CH18" s="4" cm="1">
         <f t="array" aca="1" ref="CH18" ca="1">_xll.YCP($B18,CH$2)</f>
-        <v>3.15E-5</v>
+        <v>3.0320000000000001E-5</v>
       </c>
       <c r="CI18" s="4" cm="1">
         <f t="array" aca="1" ref="CI18" ca="1">_xll.YCP($B18,CI$2)</f>
-        <v>5.0715000000000005E-4</v>
+        <v>5.1851000000000002E-4</v>
       </c>
       <c r="CJ18" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="CJ18" ca="1">_xll.YCP($B18,CJ$2)</f>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="DH18" s="4" cm="1">
         <f t="array" aca="1" ref="DH18" ca="1">_xll.YCP($B18,DH$2)</f>
-        <v>0.98417228999999995</v>
+        <v>0.98474634000000005</v>
       </c>
       <c r="DI18" s="4" cm="1">
         <f t="array" aca="1" ref="DI18" ca="1">_xll.YCP($B18,DI$2)</f>
@@ -9101,23 +9101,23 @@
       </c>
       <c r="DJ18" s="4" cm="1">
         <f t="array" aca="1" ref="DJ18" ca="1">_xll.YCP($B18,DJ$2)</f>
-        <v>1.528906E-2</v>
+        <v>1.470481E-2</v>
       </c>
       <c r="DK18" s="4" cm="1">
         <f t="array" aca="1" ref="DK18" ca="1">_xll.YCP($B18,DK$2)</f>
-        <v>5.23437E-2</v>
+        <v>5.1367910000000003E-2</v>
       </c>
       <c r="DL18" s="4" cm="1">
         <f t="array" aca="1" ref="DL18" ca="1">_xll.YCP($B18,DL$2)</f>
-        <v>0.66758930999999999</v>
+        <v>0.66562080999999995</v>
       </c>
       <c r="DM18" s="4" cm="1">
         <f t="array" aca="1" ref="DM18" ca="1">_xll.YCP($B18,DM$2)</f>
-        <v>0.20822555000000001</v>
+        <v>0.21133589999999999</v>
       </c>
       <c r="DN18" s="4" cm="1">
         <f t="array" aca="1" ref="DN18" ca="1">_xll.YCP($B18,DN$2)</f>
-        <v>0.1056723</v>
+        <v>0.10523904000000001</v>
       </c>
       <c r="DO18" s="4" cm="1">
         <f t="array" aca="1" ref="DO18" ca="1">_xll.YCP($B18,DO$2)</f>
@@ -9133,7 +9133,7 @@
       </c>
       <c r="DR18" s="4" cm="1">
         <f t="array" aca="1" ref="DR18" ca="1">_xll.YCP($B18,DR$2)</f>
-        <v>0.94765630000000001</v>
+        <v>0.94863209000000004</v>
       </c>
     </row>
     <row r="19" spans="2:122" x14ac:dyDescent="0.45">
@@ -9645,11 +9645,11 @@
       </c>
       <c r="H20" s="4" cm="1">
         <f t="array" aca="1" ref="H20" ca="1">_xll.YCP($B20,H$2)</f>
-        <v>4.4027399999999996E-3</v>
+        <v>4.3911499999999999E-3</v>
       </c>
       <c r="I20" s="4" cm="1">
         <f t="array" aca="1" ref="I20" ca="1">_xll.YCP($B20,I$2)</f>
-        <v>4.3284000000000003E-2</v>
+        <v>4.3597999999999998E-2</v>
       </c>
       <c r="J20" s="5" cm="1">
         <f t="array" aca="1" ref="J20" ca="1">_xll.YCP($B20,J$2)</f>
@@ -9657,23 +9657,23 @@
       </c>
       <c r="K20" s="4" cm="1">
         <f t="array" aca="1" ref="K20" ca="1">_xll.YCP($B20,K$2)</f>
-        <v>0.61979616999999998</v>
+        <v>0.60139083999999998</v>
       </c>
       <c r="L20" s="4" cm="1">
         <f t="array" aca="1" ref="L20" ca="1">_xll.YCP($B20,L$2)</f>
-        <v>2.2100000000000001E-4</v>
+        <v>-6.6930000000000002E-3</v>
       </c>
       <c r="M20" s="4" cm="1">
         <f t="array" aca="1" ref="M20" ca="1">_xll.YCP($B20,M$2)</f>
-        <v>5.5099999999999995E-4</v>
+        <v>-3.5530000000000002E-3</v>
       </c>
       <c r="N20" s="4" cm="1">
         <f t="array" aca="1" ref="N20" ca="1">_xll.YCP($B20,N$2)</f>
-        <v>2.6329999999999999E-3</v>
+        <v>-1.1069999999999999E-3</v>
       </c>
       <c r="O20" s="4" cm="1">
         <f t="array" aca="1" ref="O20" ca="1">_xll.YCP($B20,O$2)</f>
-        <v>3.0002999999999998E-2</v>
+        <v>2.4344000000000001E-2</v>
       </c>
       <c r="P20" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="P20" ca="1">_xll.YCP($B20,P$2)</f>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="R20" s="4" cm="1">
         <f t="array" aca="1" ref="R20" ca="1">_xll.YCP($B20,R$2)</f>
-        <v>3.6818999999999998E-2</v>
+        <v>3.2985E-2</v>
       </c>
       <c r="S20" s="3" cm="1">
         <f t="array" aca="1" ref="S20" ca="1">_xll.YCP($B20,S$2)</f>
@@ -9829,71 +9829,71 @@
       </c>
       <c r="BB20" s="4" cm="1">
         <f t="array" aca="1" ref="BB20" ca="1">_xll.YCP($B20,BB$2)</f>
-        <v>0.81097847999999995</v>
+        <v>0.80137862999999998</v>
       </c>
       <c r="BC20" s="4" cm="1">
         <f t="array" aca="1" ref="BC20" ca="1">_xll.YCP($B20,BC$2)</f>
-        <v>1.4806049999999999E-2</v>
+        <v>1.474434E-2</v>
       </c>
       <c r="BD20" s="4" cm="1">
         <f t="array" aca="1" ref="BD20" ca="1">_xll.YCP($B20,BD$2)</f>
-        <v>3.022787E-2</v>
+        <v>2.9651090000000001E-2</v>
       </c>
       <c r="BE20" s="4" cm="1">
         <f t="array" aca="1" ref="BE20" ca="1">_xll.YCP($B20,BE$2)</f>
-        <v>4.2655699999999998E-2</v>
+        <v>4.1763790000000002E-2</v>
       </c>
       <c r="BF20" s="4" cm="1">
         <f t="array" aca="1" ref="BF20" ca="1">_xll.YCP($B20,BF$2)</f>
-        <v>3.1345E-4</v>
+        <v>3.1290000000000002E-4</v>
       </c>
       <c r="BG20" s="4" cm="1">
         <f t="array" aca="1" ref="BG20" ca="1">_xll.YCP($B20,BG$2)</f>
-        <v>2.2347700000000001E-3</v>
+        <v>2.2270300000000001E-3</v>
       </c>
       <c r="BH20" s="4" cm="1">
         <f t="array" aca="1" ref="BH20" ca="1">_xll.YCP($B20,BH$2)</f>
-        <v>2.11408E-3</v>
+        <v>2.0847399999999999E-3</v>
       </c>
       <c r="BI20" s="4" cm="1">
         <f t="array" aca="1" ref="BI20" ca="1">_xll.YCP($B20,BI$2)</f>
-        <v>6.1779999999999995E-5</v>
+        <v>6.1660000000000003E-5</v>
       </c>
       <c r="BJ20" s="4" cm="1">
         <f t="array" aca="1" ref="BJ20" ca="1">_xll.YCP($B20,BJ$2)</f>
-        <v>3.1543149999999999E-2</v>
+        <v>3.1541569999999998E-2</v>
       </c>
       <c r="BK20" s="4" cm="1">
         <f t="array" aca="1" ref="BK20" ca="1">_xll.YCP($B20,BK$2)</f>
-        <v>0.21635275000000001</v>
+        <v>0.21634191</v>
       </c>
       <c r="BL20" s="4" cm="1">
         <f t="array" aca="1" ref="BL20" ca="1">_xll.YCP($B20,BL$2)</f>
-        <v>0.29227926999999998</v>
+        <v>0.29226461999999997</v>
       </c>
       <c r="BM20" s="4" cm="1">
         <f t="array" aca="1" ref="BM20" ca="1">_xll.YCP($B20,BM$2)</f>
-        <v>5.0863200000000001E-3</v>
+        <v>5.0860699999999998E-3</v>
       </c>
       <c r="BN20" s="4" cm="1">
         <f t="array" aca="1" ref="BN20" ca="1">_xll.YCP($B20,BN$2)</f>
-        <v>8.6706329999999998E-2</v>
+        <v>8.6701990000000007E-2</v>
       </c>
       <c r="BO20" s="4" cm="1">
         <f t="array" aca="1" ref="BO20" ca="1">_xll.YCP($B20,BO$2)</f>
-        <v>0.24737830999999999</v>
+        <v>0.24736590999999999</v>
       </c>
       <c r="BP20" s="4" cm="1">
         <f t="array" aca="1" ref="BP20" ca="1">_xll.YCP($B20,BP$2)</f>
-        <v>2.477027E-2</v>
+        <v>2.4819150000000002E-2</v>
       </c>
       <c r="BQ20" s="4" cm="1">
         <f t="array" aca="1" ref="BQ20" ca="1">_xll.YCP($B20,BQ$2)</f>
-        <v>4.9549320000000001E-2</v>
+        <v>4.9546840000000002E-2</v>
       </c>
       <c r="BR20" s="4" cm="1">
         <f t="array" aca="1" ref="BR20" ca="1">_xll.YCP($B20,BR$2)</f>
-        <v>4.633429E-2</v>
+        <v>4.6331959999999998E-2</v>
       </c>
       <c r="BS20" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="BS20" ca="1">_xll.YCP($B20,BS$2)</f>
@@ -9941,139 +9941,139 @@
       </c>
       <c r="CD20" s="4" cm="1">
         <f t="array" aca="1" ref="CD20" ca="1">_xll.YCP($B20,CD$2)</f>
-        <v>1.134277E-2</v>
+        <v>1.3524950000000001E-2</v>
       </c>
       <c r="CE20" s="4" cm="1">
         <f t="array" aca="1" ref="CE20" ca="1">_xll.YCP($B20,CE$2)</f>
-        <v>1.9328149999999999E-2</v>
+        <v>1.909228E-2</v>
       </c>
       <c r="CF20" s="4" cm="1">
         <f t="array" aca="1" ref="CF20" ca="1">_xll.YCP($B20,CF$2)</f>
-        <v>0.95780069000000001</v>
+        <v>0.95591457999999996</v>
       </c>
       <c r="CG20" s="4" cm="1">
         <f t="array" aca="1" ref="CG20" ca="1">_xll.YCP($B20,CG$2)</f>
-        <v>8.5274000000000005E-4</v>
+        <v>8.4228999999999999E-4</v>
       </c>
       <c r="CH20" s="4" cm="1">
         <f t="array" aca="1" ref="CH20" ca="1">_xll.YCP($B20,CH$2)</f>
-        <v>9.3706199999999996E-3</v>
+        <v>9.32294E-3</v>
       </c>
       <c r="CI20" s="4" cm="1">
         <f t="array" aca="1" ref="CI20" ca="1">_xll.YCP($B20,CI$2)</f>
-        <v>1.3050500000000001E-3</v>
+        <v>1.30299E-3</v>
       </c>
       <c r="CJ20" s="4" cm="1">
         <f t="array" aca="1" ref="CJ20" ca="1">_xll.YCP($B20,CJ$2)</f>
-        <v>0.10786903</v>
+        <v>0.10775661</v>
       </c>
       <c r="CK20" s="4" cm="1">
         <f t="array" aca="1" ref="CK20" ca="1">_xll.YCP($B20,CK$2)</f>
-        <v>0.38645611000000002</v>
+        <v>0.37972064999999999</v>
       </c>
       <c r="CL20" s="4" cm="1">
         <f t="array" aca="1" ref="CL20" ca="1">_xll.YCP($B20,CL$2)</f>
-        <v>0.11136172</v>
+        <v>0.11341010999999999</v>
       </c>
       <c r="CM20" s="4" cm="1">
         <f t="array" aca="1" ref="CM20" ca="1">_xll.YCP($B20,CM$2)</f>
-        <v>0.22667345</v>
+        <v>0.22937577000000001</v>
       </c>
       <c r="CN20" s="4" cm="1">
         <f t="array" aca="1" ref="CN20" ca="1">_xll.YCP($B20,CN$2)</f>
-        <v>3.8617680000000001E-2</v>
+        <v>3.8055770000000003E-2</v>
       </c>
       <c r="CO20" s="4" cm="1">
         <f t="array" aca="1" ref="CO20" ca="1">_xll.YCP($B20,CO$2)</f>
-        <v>2.1787689999999998E-2</v>
+        <v>2.131659E-2</v>
       </c>
       <c r="CP20" s="4" cm="1">
         <f t="array" aca="1" ref="CP20" ca="1">_xll.YCP($B20,CP$2)</f>
-        <v>8.0413499999999992E-3</v>
+        <v>8.0305299999999993E-3</v>
       </c>
       <c r="CQ20" s="4" cm="1">
         <f t="array" aca="1" ref="CQ20" ca="1">_xll.YCP($B20,CQ$2)</f>
-        <v>3.6927910000000001E-2</v>
+        <v>3.6275439999999999E-2</v>
       </c>
       <c r="CR20" s="4" cm="1">
         <f t="array" aca="1" ref="CR20" ca="1">_xll.YCP($B20,CR$2)</f>
-        <v>0.19173871000000001</v>
+        <v>0.19175830999999999</v>
       </c>
       <c r="CS20" s="4" cm="1">
         <f t="array" aca="1" ref="CS20" ca="1">_xll.YCP($B20,CS$2)</f>
-        <v>0.22625902000000001</v>
+        <v>0.22270361</v>
       </c>
       <c r="CT20" s="4" cm="1">
         <f t="array" aca="1" ref="CT20" ca="1">_xll.YCP($B20,CT$2)</f>
-        <v>0.27854217999999997</v>
+        <v>0.27825845999999999</v>
       </c>
       <c r="CU20" s="4" cm="1">
         <f t="array" aca="1" ref="CU20" ca="1">_xll.YCP($B20,CU$2)</f>
-        <v>8.8582859999999999E-2</v>
+        <v>8.7501430000000005E-2</v>
       </c>
       <c r="CV20" s="4" cm="1">
         <f t="array" aca="1" ref="CV20" ca="1">_xll.YCP($B20,CV$2)</f>
-        <v>8.8969240000000005E-2</v>
+        <v>9.1474079999999999E-2</v>
       </c>
       <c r="CW20" s="4" cm="1">
         <f t="array" aca="1" ref="CW20" ca="1">_xll.YCP($B20,CW$2)</f>
-        <v>5.2786550000000002E-2</v>
+        <v>5.5326800000000002E-2</v>
       </c>
       <c r="CX20" s="3" cm="1">
         <f t="array" aca="1" ref="CX20" ca="1">_xll.YCP($B20,CX$2)</f>
-        <v>4.565766</v>
+        <v>4.5598609999999997</v>
       </c>
       <c r="CY20" s="20" cm="1">
         <f t="array" aca="1" ref="CY20" ca="1">_xll.YCP($B20,CY$2)</f>
-        <v>6.2108449999999999</v>
+        <v>6.211042</v>
       </c>
       <c r="CZ20" s="4" cm="1">
         <f t="array" aca="1" ref="CZ20" ca="1">_xll.YCP($B20,CZ$2)</f>
-        <v>5.9973430000000001E-2</v>
+        <v>5.997342E-2</v>
       </c>
       <c r="DA20" s="4" cm="1">
         <f t="array" aca="1" ref="DA20" ca="1">_xll.YCP($B20,DA$2)</f>
-        <v>4.581499E-2</v>
+        <v>4.601558E-2</v>
       </c>
       <c r="DB20" s="4" cm="1">
         <f t="array" aca="1" ref="DB20" ca="1">_xll.YCP($B20,DB$2)</f>
-        <v>4.495072E-2</v>
+        <v>4.5175439999999997E-2</v>
       </c>
       <c r="DC20" s="4" cm="1">
         <f t="array" aca="1" ref="DC20" ca="1">_xll.YCP($B20,DC$2)</f>
-        <v>0.35155225000000001</v>
+        <v>0.34611199999999998</v>
       </c>
       <c r="DD20" s="4" cm="1">
         <f t="array" aca="1" ref="DD20" ca="1">_xll.YCP($B20,DD$2)</f>
-        <v>0.38547429999999999</v>
+        <v>0.38686155999999999</v>
       </c>
       <c r="DE20" s="4" cm="1">
         <f t="array" aca="1" ref="DE20" ca="1">_xll.YCP($B20,DE$2)</f>
-        <v>0.2199314</v>
+        <v>0.22227870999999999</v>
       </c>
       <c r="DF20" s="4" cm="1">
         <f t="array" aca="1" ref="DF20" ca="1">_xll.YCP($B20,DF$2)</f>
-        <v>5.3050299999999996E-3</v>
+        <v>5.2061299999999998E-3</v>
       </c>
       <c r="DG20" s="4" cm="1">
         <f t="array" aca="1" ref="DG20" ca="1">_xll.YCP($B20,DG$2)</f>
-        <v>3.7737020000000003E-2</v>
+        <v>3.9541600000000003E-2</v>
       </c>
       <c r="DH20" s="4" cm="1">
         <f t="array" aca="1" ref="DH20" ca="1">_xll.YCP($B20,DH$2)</f>
-        <v>1.9362839999999999E-2</v>
+        <v>1.9126899999999999E-2</v>
       </c>
       <c r="DI20" s="4" cm="1">
         <f t="array" aca="1" ref="DI20" ca="1">_xll.YCP($B20,DI$2)</f>
-        <v>1.02510743</v>
+        <v>1.0230906200000001</v>
       </c>
       <c r="DJ20" s="4" cm="1">
         <f t="array" aca="1" ref="DJ20" ca="1">_xll.YCP($B20,DJ$2)</f>
-        <v>1.134277E-2</v>
+        <v>1.3524950000000001E-2</v>
       </c>
       <c r="DK20" s="4" cm="1">
         <f t="array" aca="1" ref="DK20" ca="1">_xll.YCP($B20,DK$2)</f>
-        <v>7.6589999999999997E-5</v>
+        <v>7.593E-5</v>
       </c>
       <c r="DL20" s="4" cm="1">
         <f t="array" aca="1" ref="DL20" ca="1">_xll.YCP($B20,DL$2)</f>
@@ -10089,19 +10089,19 @@
       </c>
       <c r="DO20" s="4" cm="1">
         <f t="array" aca="1" ref="DO20" ca="1">_xll.YCP($B20,DO$2)</f>
-        <v>0.79330420000000001</v>
+        <v>0.78775253000000001</v>
       </c>
       <c r="DP20" s="4" cm="1">
         <f t="array" aca="1" ref="DP20" ca="1">_xll.YCP($B20,DP$2)</f>
-        <v>6.5235050000000003E-2</v>
+        <v>6.3951770000000005E-2</v>
       </c>
       <c r="DQ20" s="4" cm="1">
         <f t="array" aca="1" ref="DQ20" ca="1">_xll.YCP($B20,DQ$2)</f>
-        <v>3.8865179999999999E-2</v>
+        <v>4.0719770000000002E-2</v>
       </c>
       <c r="DR20" s="4" cm="1">
         <f t="array" aca="1" ref="DR20" ca="1">_xll.YCP($B20,DR$2)</f>
-        <v>0.99992340999999996</v>
+        <v>0.99992407000000005</v>
       </c>
     </row>
     <row r="21" spans="2:122" x14ac:dyDescent="0.45">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="I22" s="4" cm="1">
         <f t="array" aca="1" ref="I22" ca="1">_xll.YCP($B22,I$2)</f>
-        <v>2.9139999999999999E-3</v>
+        <v>3.0349999999999999E-3</v>
       </c>
       <c r="J22" s="5" cm="1">
         <f t="array" aca="1" ref="J22" ca="1">_xll.YCP($B22,J$2)</f>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="R22" s="4" cm="1">
         <f t="array" aca="1" ref="R22" ca="1">_xll.YCP($B22,R$2)</f>
-        <v>0.28207300000000002</v>
+        <v>0.22934499999999999</v>
       </c>
       <c r="S22" s="3" cm="1">
         <f t="array" aca="1" ref="S22" ca="1">_xll.YCP($B22,S$2)</f>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="BB22" s="4" cm="1">
         <f t="array" aca="1" ref="BB22" ca="1">_xll.YCP($B22,BB$2)</f>
-        <v>0.97981748000000002</v>
+        <v>0.98059326000000002</v>
       </c>
       <c r="BC22" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="BC22" ca="1">_xll.YCP($B22,BC$2)</f>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="BH22" s="4" cm="1">
         <f t="array" aca="1" ref="BH22" ca="1">_xll.YCP($B22,BH$2)</f>
-        <v>2.0182519999999999E-2</v>
+        <v>1.9406739999999999E-2</v>
       </c>
       <c r="BI22" s="4" cm="1">
         <f t="array" aca="1" ref="BI22" ca="1">_xll.YCP($B22,BI$2)</f>
@@ -10801,11 +10801,11 @@
       </c>
       <c r="BK22" s="4" cm="1">
         <f t="array" aca="1" ref="BK22" ca="1">_xll.YCP($B22,BK$2)</f>
-        <v>0.18902838999999999</v>
+        <v>0.18330080000000001</v>
       </c>
       <c r="BL22" s="4" cm="1">
         <f t="array" aca="1" ref="BL22" ca="1">_xll.YCP($B22,BL$2)</f>
-        <v>0.66574800000000001</v>
+        <v>0.66230876999999999</v>
       </c>
       <c r="BM22" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="BM22" ca="1">_xll.YCP($B22,BM$2)</f>
@@ -10813,11 +10813,11 @@
       </c>
       <c r="BN22" s="4" cm="1">
         <f t="array" aca="1" ref="BN22" ca="1">_xll.YCP($B22,BN$2)</f>
-        <v>3.05753E-2</v>
+        <v>3.3997609999999998E-2</v>
       </c>
       <c r="BO22" s="4" cm="1">
         <f t="array" aca="1" ref="BO22" ca="1">_xll.YCP($B22,BO$2)</f>
-        <v>8.7843489999999996E-2</v>
+        <v>8.7929549999999995E-2</v>
       </c>
       <c r="BP22" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="BP22" ca="1">_xll.YCP($B22,BP$2)</f>
@@ -10825,11 +10825,11 @@
       </c>
       <c r="BQ22" s="4" cm="1">
         <f t="array" aca="1" ref="BQ22" ca="1">_xll.YCP($B22,BQ$2)</f>
-        <v>1.5065800000000001E-2</v>
+        <v>1.9183800000000001E-2</v>
       </c>
       <c r="BR22" s="4" cm="1">
         <f t="array" aca="1" ref="BR22" ca="1">_xll.YCP($B22,BR$2)</f>
-        <v>1.1739019999999999E-2</v>
+        <v>1.327946E-2</v>
       </c>
       <c r="BS22" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="BS22" ca="1">_xll.YCP($B22,BS$2)</f>
@@ -10837,15 +10837,15 @@
       </c>
       <c r="BT22" s="4" cm="1">
         <f t="array" aca="1" ref="BT22" ca="1">_xll.YCP($B22,BT$2)</f>
-        <v>0.16218927999999999</v>
+        <v>0.15238196000000001</v>
       </c>
       <c r="BU22" s="4" cm="1">
         <f t="array" aca="1" ref="BU22" ca="1">_xll.YCP($B22,BU$2)</f>
-        <v>6.6448850000000004E-2</v>
+        <v>6.103066E-2</v>
       </c>
       <c r="BV22" s="4" cm="1">
         <f t="array" aca="1" ref="BV22" ca="1">_xll.YCP($B22,BV$2)</f>
-        <v>1.1739019999999999E-2</v>
+        <v>1.327946E-2</v>
       </c>
       <c r="BW22" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="BW22" ca="1">_xll.YCP($B22,BW$2)</f>
@@ -10853,15 +10853,15 @@
       </c>
       <c r="BX22" s="4" cm="1">
         <f t="array" aca="1" ref="BX22" ca="1">_xll.YCP($B22,BX$2)</f>
-        <v>0.11722684</v>
+        <v>0.12212083999999999</v>
       </c>
       <c r="BY22" s="4" cm="1">
         <f t="array" aca="1" ref="BY22" ca="1">_xll.YCP($B22,BY$2)</f>
-        <v>8.0105880000000004E-2</v>
+        <v>8.2762619999999995E-2</v>
       </c>
       <c r="BZ22" s="4" cm="1">
         <f t="array" aca="1" ref="BZ22" ca="1">_xll.YCP($B22,BZ$2)</f>
-        <v>0.11023345</v>
+        <v>0.10887265</v>
       </c>
       <c r="CA22" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="CA22" ca="1">_xll.YCP($B22,CA$2)</f>
@@ -10869,7 +10869,7 @@
       </c>
       <c r="CB22" s="4" cm="1">
         <f t="array" aca="1" ref="CB22" ca="1">_xll.YCP($B22,CB$2)</f>
-        <v>0.45205666999999999</v>
+        <v>0.45955180000000001</v>
       </c>
       <c r="CC22" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="CC22" ca="1">_xll.YCP($B22,CC$2)</f>
@@ -10877,11 +10877,11 @@
       </c>
       <c r="CD22" s="4" cm="1">
         <f t="array" aca="1" ref="CD22" ca="1">_xll.YCP($B22,CD$2)</f>
-        <v>8.3490100000000005E-3</v>
+        <v>8.6949999999999996E-3</v>
       </c>
       <c r="CE22" s="4" cm="1">
         <f t="array" aca="1" ref="CE22" ca="1">_xll.YCP($B22,CE$2)</f>
-        <v>0.99165099000000001</v>
+        <v>0.99130499999999999</v>
       </c>
       <c r="CF22" s="4" cm="1">
         <f t="array" aca="1" ref="CF22" ca="1">_xll.YCP($B22,CF$2)</f>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="DH22" s="4" cm="1">
         <f t="array" aca="1" ref="DH22" ca="1">_xll.YCP($B22,DH$2)</f>
-        <v>0.99165099000000001</v>
+        <v>0.99130499999999999</v>
       </c>
       <c r="DI22" s="4" cm="1">
         <f t="array" aca="1" ref="DI22" ca="1">_xll.YCP($B22,DI$2)</f>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="DJ22" s="4" cm="1">
         <f t="array" aca="1" ref="DJ22" ca="1">_xll.YCP($B22,DJ$2)</f>
-        <v>8.3490100000000005E-3</v>
+        <v>8.6949999999999996E-3</v>
       </c>
       <c r="DK22" s="4" cm="1">
         <f t="array" aca="1" ref="DK22" ca="1">_xll.YCP($B22,DK$2)</f>
@@ -11013,15 +11013,15 @@
       </c>
       <c r="DL22" s="4" cm="1">
         <f t="array" aca="1" ref="DL22" ca="1">_xll.YCP($B22,DL$2)</f>
-        <v>0.89052589000000004</v>
+        <v>0.88533899999999999</v>
       </c>
       <c r="DM22" s="4" cm="1">
         <f t="array" aca="1" ref="DM22" ca="1">_xll.YCP($B22,DM$2)</f>
-        <v>8.9484090000000002E-2</v>
+        <v>9.2801999999999996E-2</v>
       </c>
       <c r="DN22" s="4" cm="1">
         <f t="array" aca="1" ref="DN22" ca="1">_xll.YCP($B22,DN$2)</f>
-        <v>1.164101E-2</v>
+        <v>1.3164E-2</v>
       </c>
       <c r="DO22" s="4" cm="1">
         <f t="array" aca="1" ref="DO22" ca="1">_xll.YCP($B22,DO$2)</f>
@@ -11062,7 +11062,7 @@
       </c>
       <c r="I23" s="4" cm="1">
         <f t="array" aca="1" ref="I23" ca="1">_xll.YCP($B23,I$2)</f>
-        <v>1.4657999999999999E-2</v>
+        <v>1.502E-2</v>
       </c>
       <c r="J23" s="5" cm="1">
         <f t="array" aca="1" ref="J23" ca="1">_xll.YCP($B23,J$2)</f>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="R23" s="4" cm="1">
         <f t="array" aca="1" ref="R23" ca="1">_xll.YCP($B23,R$2)</f>
-        <v>0.26803399999999999</v>
+        <v>0.238958</v>
       </c>
       <c r="S23" s="3" cm="1">
         <f t="array" aca="1" ref="S23" ca="1">_xll.YCP($B23,S$2)</f>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="BB23" s="4" cm="1">
         <f t="array" aca="1" ref="BB23" ca="1">_xll.YCP($B23,BB$2)</f>
-        <v>0.94109838999999995</v>
+        <v>0.94661496000000001</v>
       </c>
       <c r="BC23" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="BC23" ca="1">_xll.YCP($B23,BC$2)</f>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="BE23" s="4" cm="1">
         <f t="array" aca="1" ref="BE23" ca="1">_xll.YCP($B23,BE$2)</f>
-        <v>5.890161E-2</v>
+        <v>5.3385040000000002E-2</v>
       </c>
       <c r="BF23" s="4" cm="1">
         <f t="array" aca="1" ref="BF23" ca="1">_xll.YCP($B23,BF$2)</f>
@@ -11250,15 +11250,15 @@
       </c>
       <c r="BJ23" s="4" cm="1">
         <f t="array" aca="1" ref="BJ23" ca="1">_xll.YCP($B23,BJ$2)</f>
-        <v>0.14198005999999999</v>
+        <v>0.14312643</v>
       </c>
       <c r="BK23" s="4" cm="1">
         <f t="array" aca="1" ref="BK23" ca="1">_xll.YCP($B23,BK$2)</f>
-        <v>0.54799023999999996</v>
+        <v>0.53903999000000002</v>
       </c>
       <c r="BL23" s="4" cm="1">
         <f t="array" aca="1" ref="BL23" ca="1">_xll.YCP($B23,BL$2)</f>
-        <v>0.24583542999999999</v>
+        <v>0.25687720000000003</v>
       </c>
       <c r="BM23" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="BM23" ca="1">_xll.YCP($B23,BM$2)</f>
@@ -11266,11 +11266,11 @@
       </c>
       <c r="BN23" s="4" cm="1">
         <f t="array" aca="1" ref="BN23" ca="1">_xll.YCP($B23,BN$2)</f>
-        <v>3.4068630000000003E-2</v>
+        <v>2.9275700000000002E-2</v>
       </c>
       <c r="BO23" s="4" cm="1">
         <f t="array" aca="1" ref="BO23" ca="1">_xll.YCP($B23,BO$2)</f>
-        <v>3.0125639999999999E-2</v>
+        <v>3.1680680000000003E-2</v>
       </c>
       <c r="BP23" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="BP23" ca="1">_xll.YCP($B23,BP$2)</f>
@@ -11290,51 +11290,51 @@
       </c>
       <c r="BT23" s="4" cm="1">
         <f t="array" aca="1" ref="BT23" ca="1">_xll.YCP($B23,BT$2)</f>
-        <v>0.10579255</v>
+        <v>0.10407332</v>
       </c>
       <c r="BU23" s="4" cm="1">
         <f t="array" aca="1" ref="BU23" ca="1">_xll.YCP($B23,BU$2)</f>
-        <v>8.1386570000000005E-2</v>
+        <v>8.3808709999999995E-2</v>
       </c>
       <c r="BV23" s="4" cm="1">
         <f t="array" aca="1" ref="BV23" ca="1">_xll.YCP($B23,BV$2)</f>
-        <v>5.0171710000000001E-2</v>
+        <v>5.0521679999999999E-2</v>
       </c>
       <c r="BW23" s="4" cm="1">
         <f t="array" aca="1" ref="BW23" ca="1">_xll.YCP($B23,BW$2)</f>
-        <v>2.742934E-2</v>
+        <v>3.0864880000000001E-2</v>
       </c>
       <c r="BX23" s="4" cm="1">
         <f t="array" aca="1" ref="BX23" ca="1">_xll.YCP($B23,BX$2)</f>
-        <v>0.10737439</v>
+        <v>0.11712905</v>
       </c>
       <c r="BY23" s="4" cm="1">
         <f t="array" aca="1" ref="BY23" ca="1">_xll.YCP($B23,BY$2)</f>
-        <v>8.4541169999999999E-2</v>
+        <v>8.5957240000000004E-2</v>
       </c>
       <c r="BZ23" s="4" cm="1">
         <f t="array" aca="1" ref="BZ23" ca="1">_xll.YCP($B23,BZ$2)</f>
-        <v>8.1591490000000003E-2</v>
+        <v>8.0405190000000001E-2</v>
       </c>
       <c r="CA23" s="4" cm="1">
         <f t="array" aca="1" ref="CA23" ca="1">_xll.YCP($B23,CA$2)</f>
-        <v>3.1519720000000001E-2</v>
+        <v>3.2585320000000001E-2</v>
       </c>
       <c r="CB23" s="4" cm="1">
         <f t="array" aca="1" ref="CB23" ca="1">_xll.YCP($B23,CB$2)</f>
-        <v>0.40218327999999998</v>
+        <v>0.38589888</v>
       </c>
       <c r="CC23" s="4" cm="1">
         <f t="array" aca="1" ref="CC23" ca="1">_xll.YCP($B23,CC$2)</f>
-        <v>2.800979E-2</v>
+        <v>2.875573E-2</v>
       </c>
       <c r="CD23" s="4" cm="1">
         <f t="array" aca="1" ref="CD23" ca="1">_xll.YCP($B23,CD$2)</f>
-        <v>9.3839800000000001E-3</v>
+        <v>9.554E-3</v>
       </c>
       <c r="CE23" s="4" cm="1">
         <f t="array" aca="1" ref="CE23" ca="1">_xll.YCP($B23,CE$2)</f>
-        <v>0.99061602000000004</v>
+        <v>0.99044600000000005</v>
       </c>
       <c r="CF23" s="4" cm="1">
         <f t="array" aca="1" ref="CF23" ca="1">_xll.YCP($B23,CF$2)</f>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="DH23" s="4" cm="1">
         <f t="array" aca="1" ref="DH23" ca="1">_xll.YCP($B23,DH$2)</f>
-        <v>0.99061602000000004</v>
+        <v>0.99044600000000005</v>
       </c>
       <c r="DI23" s="4" cm="1">
         <f t="array" aca="1" ref="DI23" ca="1">_xll.YCP($B23,DI$2)</f>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="DJ23" s="4" cm="1">
         <f t="array" aca="1" ref="DJ23" ca="1">_xll.YCP($B23,DJ$2)</f>
-        <v>9.3839800000000001E-3</v>
+        <v>9.554E-3</v>
       </c>
       <c r="DK23" s="4" cm="1">
         <f t="array" aca="1" ref="DK23" ca="1">_xll.YCP($B23,DK$2)</f>
@@ -11466,11 +11466,11 @@
       </c>
       <c r="DL23" s="4" cm="1">
         <f t="array" aca="1" ref="DL23" ca="1">_xll.YCP($B23,DL$2)</f>
-        <v>0.99061602000000004</v>
+        <v>0.96145000000000003</v>
       </c>
       <c r="DM23" s="4" cm="1">
         <f t="array" aca="1" ref="DM23" ca="1">_xll.YCP($B23,DM$2)</f>
-        <v>0</v>
+        <v>2.8996000000000001E-2</v>
       </c>
       <c r="DN23" s="4" cm="1">
         <f t="array" aca="1" ref="DN23" ca="1">_xll.YCP($B23,DN$2)</f>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="I24" s="4" cm="1">
         <f t="array" aca="1" ref="I24" ca="1">_xll.YCP($B24,I$2)</f>
-        <v>8.8649999999999996E-3</v>
+        <v>9.1760000000000001E-3</v>
       </c>
       <c r="J24" s="5">
         <f ca="1">J22+J23</f>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="R24" s="4" cm="1">
         <f t="array" aca="1" ref="R24" ca="1">_xll.YCP($B24,R$2)</f>
-        <v>0.28251399999999999</v>
+        <v>0.24068999999999999</v>
       </c>
       <c r="S24" s="3" cm="1">
         <f t="array" aca="1" ref="S24" ca="1">_xll.YCP($B24,S$2)</f>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="BB24" s="4" cm="1">
         <f t="array" aca="1" ref="BB24" ca="1">_xll.YCP($B24,BB$2)</f>
-        <v>0.96019588</v>
+        <v>0.96318280999999994</v>
       </c>
       <c r="BC24" s="4" cm="1">
         <f t="array" aca="1" ref="BC24" ca="1">_xll.YCP($B24,BC$2)</f>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="BE24" s="4" cm="1">
         <f t="array" aca="1" ref="BE24" ca="1">_xll.YCP($B24,BE$2)</f>
-        <v>2.984945E-2</v>
+        <v>2.7354440000000001E-2</v>
       </c>
       <c r="BF24" s="4" cm="1">
         <f t="array" aca="1" ref="BF24" ca="1">_xll.YCP($B24,BF$2)</f>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="BH24" s="4" cm="1">
         <f t="array" aca="1" ref="BH24" ca="1">_xll.YCP($B24,BH$2)</f>
-        <v>9.9546600000000006E-3</v>
+        <v>9.4627500000000007E-3</v>
       </c>
       <c r="BI24" s="4" cm="1">
         <f t="array" aca="1" ref="BI24" ca="1">_xll.YCP($B24,BI$2)</f>
@@ -11703,15 +11703,15 @@
       </c>
       <c r="BJ24" s="4" cm="1">
         <f t="array" aca="1" ref="BJ24" ca="1">_xll.YCP($B24,BJ$2)</f>
-        <v>7.195095E-2</v>
+        <v>7.3337840000000001E-2</v>
       </c>
       <c r="BK24" s="4" cm="1">
         <f t="array" aca="1" ref="BK24" ca="1">_xll.YCP($B24,BK$2)</f>
-        <v>0.37093876999999997</v>
+        <v>0.36558120999999999</v>
       </c>
       <c r="BL24" s="4" cm="1">
         <f t="array" aca="1" ref="BL24" ca="1">_xll.YCP($B24,BL$2)</f>
-        <v>0.45294974999999998</v>
+        <v>0.45456604</v>
       </c>
       <c r="BM24" s="4" cm="1">
         <f t="array" aca="1" ref="BM24" ca="1">_xll.YCP($B24,BM$2)</f>
@@ -11719,11 +11719,11 @@
       </c>
       <c r="BN24" s="4" cm="1">
         <f t="array" aca="1" ref="BN24" ca="1">_xll.YCP($B24,BN$2)</f>
-        <v>3.2345609999999997E-2</v>
+        <v>3.157811E-2</v>
       </c>
       <c r="BO24" s="4" cm="1">
         <f t="array" aca="1" ref="BO24" ca="1">_xll.YCP($B24,BO$2)</f>
-        <v>5.8593930000000002E-2</v>
+        <v>5.9107689999999997E-2</v>
       </c>
       <c r="BP24" s="4" cm="1">
         <f t="array" aca="1" ref="BP24" ca="1">_xll.YCP($B24,BP$2)</f>
@@ -11731,11 +11731,11 @@
       </c>
       <c r="BQ24" s="4" cm="1">
         <f t="array" aca="1" ref="BQ24" ca="1">_xll.YCP($B24,BQ$2)</f>
-        <v>7.4309299999999997E-3</v>
+        <v>9.3540399999999992E-3</v>
       </c>
       <c r="BR24" s="4" cm="1">
         <f t="array" aca="1" ref="BR24" ca="1">_xll.YCP($B24,BR$2)</f>
-        <v>5.7900599999999997E-3</v>
+        <v>6.4750800000000002E-3</v>
       </c>
       <c r="BS24" s="4" cm="1">
         <f t="array" aca="1" ref="BS24" ca="1">_xll.YCP($B24,BS$2)</f>
@@ -11743,51 +11743,51 @@
       </c>
       <c r="BT24" s="4" cm="1">
         <f t="array" aca="1" ref="BT24" ca="1">_xll.YCP($B24,BT$2)</f>
-        <v>0.13360922</v>
+        <v>0.12762866</v>
       </c>
       <c r="BU24" s="4" cm="1">
         <f t="array" aca="1" ref="BU24" ca="1">_xll.YCP($B24,BU$2)</f>
-        <v>7.4018810000000004E-2</v>
+        <v>7.270211E-2</v>
       </c>
       <c r="BV24" s="4" cm="1">
         <f t="array" aca="1" ref="BV24" ca="1">_xll.YCP($B24,BV$2)</f>
-        <v>3.121548E-2</v>
+        <v>3.2362340000000003E-2</v>
       </c>
       <c r="BW24" s="4" cm="1">
         <f t="array" aca="1" ref="BW24" ca="1">_xll.YCP($B24,BW$2)</f>
-        <v>1.3900310000000001E-2</v>
+        <v>1.581513E-2</v>
       </c>
       <c r="BX24" s="4" cm="1">
         <f t="array" aca="1" ref="BX24" ca="1">_xll.YCP($B24,BX$2)</f>
-        <v>0.11223393</v>
+        <v>0.11956305</v>
       </c>
       <c r="BY24" s="4" cm="1">
         <f t="array" aca="1" ref="BY24" ca="1">_xll.YCP($B24,BY$2)</f>
-        <v>8.2353540000000003E-2</v>
+        <v>8.4399539999999995E-2</v>
       </c>
       <c r="BZ24" s="4" cm="1">
         <f t="array" aca="1" ref="BZ24" ca="1">_xll.YCP($B24,BZ$2)</f>
-        <v>9.5718620000000004E-2</v>
+        <v>9.4285949999999993E-2</v>
       </c>
       <c r="CA24" s="4" cm="1">
         <f t="array" aca="1" ref="CA24" ca="1">_xll.YCP($B24,CA$2)</f>
-        <v>1.5973190000000002E-2</v>
+        <v>1.669669E-2</v>
       </c>
       <c r="CB24" s="4" cm="1">
         <f t="array" aca="1" ref="CB24" ca="1">_xll.YCP($B24,CB$2)</f>
-        <v>0.42678242999999999</v>
+        <v>0.42181212000000001</v>
       </c>
       <c r="CC24" s="4" cm="1">
         <f t="array" aca="1" ref="CC24" ca="1">_xll.YCP($B24,CC$2)</f>
-        <v>1.4194470000000001E-2</v>
+        <v>1.473441E-2</v>
       </c>
       <c r="CD24" s="4" cm="1">
         <f t="array" aca="1" ref="CD24" ca="1">_xll.YCP($B24,CD$2)</f>
-        <v>8.8734999999999994E-3</v>
+        <v>9.1351499999999999E-3</v>
       </c>
       <c r="CE24" s="4" cm="1">
         <f t="array" aca="1" ref="CE24" ca="1">_xll.YCP($B24,CE$2)</f>
-        <v>0.99112650000000002</v>
+        <v>0.99086485000000002</v>
       </c>
       <c r="CF24" s="4" cm="1">
         <f t="array" aca="1" ref="CF24" ca="1">_xll.YCP($B24,CF$2)</f>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="DH24" s="4" cm="1">
         <f t="array" aca="1" ref="DH24" ca="1">_xll.YCP($B24,DH$2)</f>
-        <v>0.99112650000000002</v>
+        <v>0.99086485000000002</v>
       </c>
       <c r="DI24" s="4" cm="1">
         <f t="array" aca="1" ref="DI24" ca="1">_xll.YCP($B24,DI$2)</f>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="DJ24" s="4" cm="1">
         <f t="array" aca="1" ref="DJ24" ca="1">_xll.YCP($B24,DJ$2)</f>
-        <v>8.8734999999999994E-3</v>
+        <v>9.1351499999999999E-3</v>
       </c>
       <c r="DK24" s="4" cm="1">
         <f t="array" aca="1" ref="DK24" ca="1">_xll.YCP($B24,DK$2)</f>
@@ -11919,15 +11919,15 @@
       </c>
       <c r="DL24" s="4" cm="1">
         <f t="array" aca="1" ref="DL24" ca="1">_xll.YCP($B24,DL$2)</f>
-        <v>0.94127475000000005</v>
+        <v>0.92435486</v>
       </c>
       <c r="DM24" s="4" cm="1">
         <f t="array" aca="1" ref="DM24" ca="1">_xll.YCP($B24,DM$2)</f>
-        <v>4.4113069999999997E-2</v>
+        <v>6.0094059999999998E-2</v>
       </c>
       <c r="DN24" s="4" cm="1">
         <f t="array" aca="1" ref="DN24" ca="1">_xll.YCP($B24,DN$2)</f>
-        <v>5.7386800000000003E-3</v>
+        <v>6.4159300000000002E-3</v>
       </c>
       <c r="DO24" s="4" cm="1">
         <f t="array" aca="1" ref="DO24" ca="1">_xll.YCP($B24,DO$2)</f>
